--- a/workspaces/nasdaq_hourly_24hrs/ma/ma_ratio_20.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/ma/ma_ratio_20.xlsx
@@ -618,575 +618,575 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.02659</t>
+          <t>X ≈ -0.02658</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>17</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-6.570078987640528</v>
+        <v>-6.537093382248081</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.905333105277514</v>
+        <v>-6.871940871370519</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-20.02917040681301</v>
+        <v>-19.99419326219503</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-20.74487912839913</v>
+        <v>-20.7090545763041</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.416847094220721</v>
+        <v>-9.351618587773139</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-9.233140318015792</v>
+        <v>-9.1680853847908</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-21.70934642841199</v>
+        <v>-21.64343261380758</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-21.99312861349055</v>
+        <v>-21.92684667594756</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-16.1024862386182</v>
+        <v>-16.03617285663318</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-11.0198851725926</v>
+        <v>-10.95260498014934</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-4.890518691515581</v>
+        <v>-4.823483390994369</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.6905930432331004</v>
+        <v>0.7580193771025989</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.4298843351408763</v>
+        <v>-0.3611175002793274</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.515620381331679</v>
+        <v>-6.446576561352032</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-1.307726844238843</v>
+        <v>-1.237857999850597</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>5.153517113515555</v>
+        <v>5.222755701355368</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.8482731868688234</v>
+        <v>-0.7788551947713316</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>4.918412302026766</v>
+        <v>4.988007011499775</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>5.135659212998668</v>
+        <v>5.205042673124289</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.5511220731156854</v>
+        <v>-0.4819253288073995</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>10.66021743451845</v>
+        <v>10.73010125830977</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>4.708773711355796</v>
+        <v>4.778779822711378</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>4.98491280907745</v>
+        <v>5.054638526225375</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.9717922256608631</v>
+        <v>-0.9019378779562572</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.02477</t>
+          <t>X ≈ -0.02476</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>20</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6.281894963374313</v>
+        <v>6.314984761621069</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>15.88418955410048</v>
+        <v>15.91776132025109</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>14.45832464691588</v>
+        <v>14.49356070414516</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.813329839342444</v>
+        <v>3.84932824935548</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>13.39338673057276</v>
+        <v>13.45876813732808</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.611105669127426</v>
+        <v>8.676272810416421</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.870956523347125</v>
+        <v>2.937016484767845</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.594539751731503</v>
+        <v>2.660959270970729</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.636543257067608</v>
+        <v>2.702954242896155</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>11.82474334972715</v>
+        <v>11.89213624760062</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>12.10147376533732</v>
+        <v>12.1685865268223</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.82646805257495</v>
+        <v>11.89394069585687</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>20.67613114216686</v>
+        <v>20.74498051132316</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>20.46153699726846</v>
+        <v>20.53067691804371</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>19.81109205799761</v>
+        <v>19.88102840895861</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>20.41044307705788</v>
+        <v>20.47972492404077</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>20.28332029682326</v>
+        <v>20.35279089176045</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>15.1937147657172</v>
+        <v>15.26333093222749</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>10.42166376188172</v>
+        <v>10.4910559589531</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>15.60573863718901</v>
+        <v>15.67495817016716</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>10.07240708285878</v>
+        <v>10.14228980026336</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>14.99661368087836</v>
+        <v>15.06662695531926</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>10.27740639068187</v>
+        <v>10.34713385726043</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>10.2046783625731</v>
+        <v>10.27453271028038</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.02296</t>
+          <t>X ≈ -0.02295</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>32</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.102086995362001</v>
+        <v>7.136259094497454</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-7.087625880702298</v>
+        <v>-5.622090209804412</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.415250034681264</v>
+        <v>-3.991544657345905</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.020165966954927</v>
+        <v>-1.617436210369746</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.828651890566277</v>
+        <v>1.149912517469787</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.124060280532859</v>
+        <v>6.189206780589771</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>14.68416699996268</v>
+        <v>14.75029696425552</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>14.41138681874781</v>
+        <v>14.47787219044788</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.235602707840641</v>
+        <v>8.302040629165234</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.35598159379699</v>
+        <v>4.423332711826802</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>10.85566821757985</v>
+        <v>10.92277247567917</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>13.69389663622589</v>
+        <v>13.76137537045763</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>15.69181826356856</v>
+        <v>15.76064609884873</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>21.70671307246496</v>
+        <v>21.77585668936898</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>21.05678355607601</v>
+        <v>21.12672310970238</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>9.187155309437991</v>
+        <v>9.256402767846964</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>18.41164237622417</v>
+        <v>18.48110734256311</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>8.95473888614049</v>
+        <v>9.024340054935067</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>6.053098215061915</v>
+        <v>6.122481144834758</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>12.48425819921337</v>
+        <v>12.55347242913213</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>18.18979428113423</v>
+        <v>18.2596854536475</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>18.119552423778</v>
+        <v>18.18956770436241</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>21.52390850704736</v>
+        <v>21.59363997184961</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>21.4546783625731</v>
+        <v>21.52453271028038</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.02116</t>
+          <t>X ≈ -0.02115</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>39</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.923447352871676</v>
+        <v>-4.890448348317371</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.70942286864031</v>
+        <v>-2.676893632572025</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.9542608215597923</v>
+        <v>0.989643701435547</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.890104693509322</v>
+        <v>7.928526028486615</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-7.76636252658956</v>
+        <v>-7.703314926479834</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.032372409165099</v>
+        <v>-4.967308891061933</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.7011478331784957</v>
+        <v>-0.6351215123971912</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.57289030005132</v>
+        <v>1.639293575720458</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.9373129141820513</v>
+        <v>-0.8709324617602618</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.707857036426851</v>
+        <v>-1.640543902300216</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-9.096899358060689</v>
+        <v>-9.029898065859861</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.269228525745795</v>
+        <v>-4.201835141303825</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-10.50205810286443</v>
+        <v>-10.43334293588364</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-18.39476070007837</v>
+        <v>-18.32577183506206</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-16.49993169027081</v>
+        <v>-16.43012285730725</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-13.35358930497916</v>
+        <v>-13.28441352820221</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-10.93258098901975</v>
+        <v>-10.86319600073389</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-18.71849548486814</v>
+        <v>-18.64895998643354</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-15.94825408717049</v>
+        <v>-15.87891524474914</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-13.20536933110186</v>
+        <v>-13.13619561601972</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-11.1902927068812</v>
+        <v>-11.12043591507496</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-6.144490273035082</v>
+        <v>-6.074493993913578</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-5.871588080495954</v>
+        <v>-5.801867262285207</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-5.949167791273055</v>
+        <v>-5.879313443565195</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.01935</t>
+          <t>X ≈ -0.01933</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>32</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8.764987989719842</v>
+        <v>7.137743785876715</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>23.95017816569008</v>
+        <v>23.99119723200832</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>22.52692333819905</v>
+        <v>22.56919148150735</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>24.92967160076505</v>
+        <v>24.97357635835799</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>12.14812326855926</v>
+        <v>12.21745535598053</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>21.66064062272298</v>
+        <v>21.72588166282999</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>20.89861188614278</v>
+        <v>20.9647732734122</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>17.51840038731024</v>
+        <v>17.5848961142356</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>17.56555299095147</v>
+        <v>17.63203446196046</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>16.80085308186695</v>
+        <v>16.8682602699062</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>17.07933250666647</v>
+        <v>17.14645850732307</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>19.91899559702337</v>
+        <v>19.9864958327572</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>18.80475157531836</v>
+        <v>18.87358546198477</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>18.58995068293356</v>
+        <v>18.65907618462442</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>24.17163849386277</v>
+        <v>24.24158351577913</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>15.42115148832521</v>
+        <v>15.4904116090413</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>15.29246312308325</v>
+        <v>15.36191521499676</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>18.31201421118038</v>
+        <v>18.38163180049324</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>18.53352437262453</v>
+        <v>18.60292690252761</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>21.84721007362</v>
+        <v>21.91643584574346</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>18.18936763120107</v>
+        <v>18.25925690062225</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>21.24227435708342</v>
+        <v>21.31229090390757</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>24.64773332490696</v>
+        <v>24.71746551737603</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>18.3296783625731</v>
+        <v>18.39953271027967</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.01754</t>
+          <t>X ≈ -0.01752</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>42</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.544151417911124</v>
+        <v>3.314649947866009</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-7.620125609214696</v>
+        <v>-8.860028910568069</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-16.18397486653548</v>
+        <v>-16.15282557639097</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-7.446808857721777</v>
+        <v>-7.411933693529186</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-12.55728766577234</v>
+        <v>-12.49458324829797</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-5.264639263155068</v>
+        <v>-5.197923104050965</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-8.422206921445976</v>
+        <v>-8.35455107751509</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-11.07800763306959</v>
+        <v>-11.00999191416077</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-11.0401858042806</v>
+        <v>-10.97217120616747</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-7.091292528762722</v>
+        <v>-7.022290146902122</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-11.55703827908966</v>
+        <v>-11.48833790582571</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-11.83940012824485</v>
+        <v>-11.77032753939627</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-5.870660972097284</v>
+        <v>-5.800178015300503</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-10.84565249861573</v>
+        <v>-10.77487871667205</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-11.52343036146392</v>
+        <v>-11.45182332640082</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-13.29510822018072</v>
+        <v>-13.22416595544323</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-11.06130150232157</v>
+        <v>-10.99014246494055</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-5.007480907147134</v>
+        <v>-6.349185569948965</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.416056595854094</v>
+        <v>-3.75132824095067</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1479214069902284</v>
+        <v>-1.180123701325698</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>4.362840525263486</v>
+        <v>3.023286032670534</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>4.28843419427016</v>
+        <v>4.358436818182163</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>4.56463792919434</v>
+        <v>4.634361966863693</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>2.109440267335003</v>
+        <v>2.179294615042281</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.01572</t>
+          <t>X ≈ -0.01571</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>58</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-7.198595222920986</v>
+        <v>-6.373596312313246</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.116324932952246</v>
+        <v>-5.007696810572781</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-9.791466111910083</v>
+        <v>-11.66014295789398</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.657296091445374</v>
+        <v>-5.536366540990883</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.600305990985639</v>
+        <v>-1.499546742784993</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>6.452118049156041</v>
+        <v>5.561880487505633</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.955685164037391</v>
+        <v>4.022987657667656</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-4.907140425122947</v>
+        <v>-4.83951983553532</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-8.301171021407775</v>
+        <v>-8.233572049883229</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-10.80540436226161</v>
+        <v>-10.73685799520893</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-12.24926655257379</v>
+        <v>-12.18100213218419</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.657729306141668</v>
+        <v>-5.589062881431786</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.360791632549464</v>
+        <v>-3.290741773791915</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.306243317502812</v>
+        <v>-5.235891898462171</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-7.698110567218613</v>
+        <v>-7.626937636337594</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-8.817761925540509</v>
+        <v>-8.747247625888896</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-10.6786810656376</v>
+        <v>-10.60796233300381</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-9.064781448930169</v>
+        <v>-8.997004114864872</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-2.661863295559449</v>
+        <v>-3.611663166003609</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-4.197881051351061</v>
+        <v>-5.143409224145316</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.019310678463732</v>
+        <v>-3.972211536093276</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-6.5420997645518</v>
+        <v>-7.494684037702001</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-6.269351470013113</v>
+        <v>-6.199632572316936</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-4.622907844323457</v>
+        <v>-4.55305349661618</v>
       </c>
     </row>
     <row r="13">
@@ -1199,76 +1199,76 @@
         <v>74</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-4.994595987075343</v>
+        <v>-5.688208015212965</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-8.013755740072845</v>
+        <v>-8.714799087509256</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.728915968143774</v>
+        <v>-3.443102732089365</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.441415738077552</v>
+        <v>-3.408427858896466</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-7.836440138126044</v>
+        <v>-7.776026401997029</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.965959392579833</v>
+        <v>-4.902246581940908</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-7.080732981095352</v>
+        <v>-7.014744367502523</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-7.359313879618469</v>
+        <v>-7.292961049573762</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.283123678938281</v>
+        <v>-3.216750655792453</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.40073954373927</v>
+        <v>-5.333436895627052</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.089559795386187</v>
+        <v>-1.022508637780433</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.716371758855011</v>
+        <v>-2.64895589646386</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.143925540121572</v>
+        <v>-1.075152450156487</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.712531318544585</v>
+        <v>-2.643461824588478</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-4.718590266229931</v>
+        <v>-4.648715796724588</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-2.777358320598196</v>
+        <v>-2.70812344121034</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.562811449840943</v>
+        <v>-1.493371731341576</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-4.365813711622849</v>
+        <v>-4.297572892609665</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-4.150384827650498</v>
+        <v>-4.083446248739008</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-2.615429646706112</v>
+        <v>-2.547580135998054</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-3.158864665459781</v>
+        <v>-3.090660616712483</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.88518828866917</v>
+        <v>-1.815591568828012</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-5.663697288187002</v>
+        <v>-5.593979377590081</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-3.038564880670144</v>
+        <v>-2.968710532962866</v>
       </c>
     </row>
     <row r="14">
@@ -1281,76 +1281,76 @@
         <v>91</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.104323811005884</v>
+        <v>-3.075333107169996</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-6.712604810445967</v>
+        <v>-6.688183350717289</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-8.142749000821595</v>
+        <v>-8.118657973134447</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-6.672645499254102</v>
+        <v>-6.643156040491363</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-7.036761477463607</v>
+        <v>-6.976096396318873</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-6.855105032368115</v>
+        <v>-6.792147980866631</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-5.438933163578966</v>
+        <v>-5.372958249876255</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-6.810627305357926</v>
+        <v>-6.744294863666923</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-10.0535921269995</v>
+        <v>-9.987279686545534</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-6.4495958104633</v>
+        <v>-6.382318765238345</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-9.462976702493911</v>
+        <v>-9.395984074444279</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-14.12632342400167</v>
+        <v>-14.05897547501202</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-13.06144021559339</v>
+        <v>-12.99272986398361</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-11.09439631188659</v>
+        <v>-11.02537016187197</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-6.273550684290278</v>
+        <v>-6.20369281387817</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-5.681727185967596</v>
+        <v>-5.612509673298234</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-3.623316065914935</v>
+        <v>-3.553888606660664</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.4368796521621618</v>
+        <v>-0.3673742865490794</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.415544079580243</v>
+        <v>-2.347562306878956</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-4.424500598402673</v>
+        <v>-4.35796888136688</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-3.870790315134862</v>
+        <v>-3.803170586321308</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-5.046033239867555</v>
+        <v>-4.977542850894999</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-3.674383113948672</v>
+        <v>-3.604665940617735</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-3.751365593470858</v>
+        <v>-3.681511245763581</v>
       </c>
     </row>
     <row r="15">
@@ -1363,1060 +1363,1060 @@
         <v>95</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.171593443207776</v>
+        <v>-4.144391519734612</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-7.640451421062316</v>
+        <v>-7.617948102059117</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.750656681952258</v>
+        <v>-1.718277032223597</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.417155812498805</v>
+        <v>-1.382530370284883</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.779351784475573</v>
+        <v>-1.715284783736379</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.642926990054143</v>
+        <v>-2.57862660442445</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.553327541884805</v>
+        <v>-6.487390563462746</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.594273850319709</v>
+        <v>-1.527934476694149</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.638319846245921</v>
+        <v>2.704684267191986</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8203688757701642</v>
+        <v>0.8876639278423966</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.003038192348754</v>
+        <v>-0.9360244974199574</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.429310640263907</v>
+        <v>-4.361940016771115</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.601702689989821</v>
+        <v>-6.532985982580783</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-5.774944747874784</v>
+        <v>-5.705916633623616</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-6.43414830437829</v>
+        <v>-6.364305944367764</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-7.943405799473268</v>
+        <v>-7.874207544200424</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-3.876962352957008</v>
+        <v>-3.80754536604573</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.8294362551584129</v>
+        <v>-0.7600836907437696</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.436802092447131</v>
+        <v>0.5067018435634552</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.674818758473229</v>
+        <v>1.745480159947533</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.08129396592301674</v>
+        <v>0.1515534780419117</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>2.109323207836269</v>
+        <v>2.180240622801101</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>3.437112837460276</v>
+        <v>3.506831613376519</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>3.362573099415201</v>
+        <v>3.432427447122478</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.008478</t>
+          <t>X ≈ -0.00848</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>105</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-7.47012379449265</v>
+        <v>-7.448205550951521</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-6.86089506953023</v>
+        <v>-6.838067479355786</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2107563319102965</v>
+        <v>0.2457948365230394</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-7.129461748479187</v>
+        <v>-7.101052289893694</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-6.552750426143028</v>
+        <v>-6.491927892495418</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.471421209422047</v>
+        <v>-4.407305668198902</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.40770471398892</v>
+        <v>-2.34098023517307</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.636797128440101</v>
+        <v>-3.569705310579209</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-5.492842375965999</v>
+        <v>-5.425759863562824</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.427621398630492</v>
+        <v>-3.359568156157216</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.204795789635199</v>
+        <v>-2.137005343069141</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.53636189359716</v>
+        <v>-1.46819031715382</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1806830014732057</v>
+        <v>0.2502321373680019</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.04225216939206433</v>
+        <v>0.02760712207480509</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>2.144332736834009</v>
+        <v>2.215025369400927</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.8430045914663253</v>
+        <v>0.9130450131041314</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-3.094691478790359</v>
+        <v>-3.024451895023418</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.248688861512413</v>
+        <v>-2.179261116265018</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-4.882120825683486</v>
+        <v>-4.815681241826987</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-3.180421193359329</v>
+        <v>-3.675454102452093</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-5.626749355642225</v>
+        <v>-6.128875433003266</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-4.752942755659184</v>
+        <v>-5.25200474201246</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-5.431918104794775</v>
+        <v>-5.925546881671437</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-8.366750208855478</v>
+        <v>-8.296895861148201</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.006668</t>
+          <t>X ≈ -0.006671</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>128</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.714061811041979</v>
+        <v>-3.687380855469591</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.725313047405386</v>
+        <v>-1.695553812139586</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-5.504365414133574</v>
+        <v>-5.478151109645893</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.118917961708704</v>
+        <v>-3.086436942188605</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.7166241164357743</v>
+        <v>-1.095623573056059</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2487507361109564</v>
+        <v>-0.1234032790206641</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.081367594432926</v>
+        <v>-2.460667572379791</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.02916158075746722</v>
+        <v>-0.4107906248898558</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.123965514538654</v>
+        <v>3.190990292553245</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.348202897190724</v>
+        <v>2.416178185681098</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.40272637272497</v>
+        <v>3.470437759305476</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.345462357602599</v>
+        <v>2.413545932569882</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.554443518327076</v>
+        <v>3.623900761771772</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.450895408893111</v>
+        <v>6.520674225344138</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>5.010866144897598</v>
+        <v>5.081464243675008</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>3.270738998939706</v>
+        <v>3.340686385843753</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>3.602821632577232</v>
+        <v>3.207107547474962</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>5.057880872458043</v>
+        <v>4.664833959482593</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>5.273497620306124</v>
+        <v>4.884777576454603</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>6.239971926316912</v>
+        <v>5.857738639547449</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>7.260674832785632</v>
+        <v>7.339236212430698</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>6.406903686827455</v>
+        <v>6.482140251021598</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>5.903162985171285</v>
+        <v>5.975364963503651</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>8.173428362573098</v>
+        <v>8.243282710280376</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.004858</t>
+          <t>X ≈ -0.004861</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.152872839133465</v>
+        <v>1.610579223191074</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>7.693236421794694</v>
+        <v>7.442043807083628</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.6802630117794166</v>
+        <v>-0.9968790889662102</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.741256574296038</v>
+        <v>-2.49791116722605</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.5879171240702732</v>
+        <v>-1.305500057686345</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.147567771656256</v>
+        <v>-1.86413791320679</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.32208908732472</v>
+        <v>1.191953070848655</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.350845370708235</v>
+        <v>-2.517100378587557</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.6658839830792402</v>
+        <v>-0.9253001866689843</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.1109733850821897</v>
+        <v>-1.721142771141125</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6024300665970372</v>
+        <v>-1.764268126548835</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.1155046428660285</v>
+        <v>-0.8223598943316048</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.2900695852524393</v>
+        <v>0.04670623184590994</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.603653046382071</v>
+        <v>1.372380917933313</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.1731378514751682</v>
+        <v>-0.06342627602118256</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.228225617005002</v>
+        <v>0.5336100717064838</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>2.630291463896747</v>
+        <v>1.948076953996804</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>5.597067882168943</v>
+        <v>4.944212107760691</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>6.58061835995678</v>
+        <v>5.939866106384379</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>6.766916491960558</v>
+        <v>6.585755248613779</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>5.459078027363056</v>
+        <v>5.268015282198142</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>6.154162150981385</v>
+        <v>5.967363119238648</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>4.124780399443381</v>
+        <v>3.916256436372045</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.512370670265405</v>
+        <v>2.290036586249364</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.003047</t>
+          <t>X ≈ -0.003052</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7637831276127685</v>
+        <v>0.7971040041372959</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1740631165709345</v>
+        <v>0.4616537318077434</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.438787570756375</v>
+        <v>-2.762967882947926</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.559295975916704</v>
+        <v>-2.883844880245185</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-7.532964158203526</v>
+        <v>-6.783277153728868</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-5.195224832647881</v>
+        <v>-4.81267168741806</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-4.174701247217818</v>
+        <v>-3.806503577728968</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.3448573748819896</v>
+        <v>0.06938746304820853</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.8122069888744363</v>
+        <v>-0.4820105459582535</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-4.59688200987631</v>
+        <v>-3.879285906139025</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-4.322588465591259</v>
+        <v>-3.605854124229438</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-4.00363675449622</v>
+        <v>-3.29070088122976</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.537141318738193</v>
+        <v>-3.81807672088172</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-4.760677868215922</v>
+        <v>-4.040707587661927</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-3.624732807734944</v>
+        <v>-2.916474976476565</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-3.024704272131295</v>
+        <v>-2.32382002586241</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.955475766051478</v>
+        <v>-1.269242498566371</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-5.066732120271197</v>
+        <v>-4.349614690927048</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-5.44797909228739</v>
+        <v>-4.730658667666532</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-5.857402070527243</v>
+        <v>-5.139050952936607</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-7.85806519002675</v>
+        <v>-7.467311406616915</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-6.732426334441023</v>
+        <v>-6.352681177549833</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-7.30702719139952</v>
+        <v>-7.268682655544097</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-7.988092721764254</v>
+        <v>-7.939753004005333</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.001237</t>
+          <t>X ≈ -0.001242</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.1992598054620913</v>
+        <v>-0.199080440207446</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.733039086785837</v>
+        <v>0.7665211854859777</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.015559182112455</v>
+        <v>0.6174844419484771</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.2966900054558863</v>
+        <v>-0.09868386734159174</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.972992727386277</v>
+        <v>2.598183539316224</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.9921540507370494</v>
+        <v>0.621845863636814</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.967634498427671</v>
+        <v>-1.891440728621696</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.812865351294825</v>
+        <v>-1.3035124457938</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.333872514423462</v>
+        <v>-1.69451071133367</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.185999998847691</v>
+        <v>0.5628938264913899</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7170004145032038</v>
+        <v>-1.331025723810541</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.177530403432243</v>
+        <v>-3.779799776898095</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.437858268986602</v>
+        <v>-4.040620822356424</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.788247761102177</v>
+        <v>-3.136353813372573</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.880875245263958</v>
+        <v>-2.495604062290518</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.847491468124602</v>
+        <v>-1.466541990281542</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-2.727299807648521</v>
+        <v>-3.339470907899148</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-4.141358644866791</v>
+        <v>-4.750010755540046</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-4.796660976846155</v>
+        <v>-5.144737342614782</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-6.790118097259992</v>
+        <v>-7.131804576124914</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-7.336350612136862</v>
+        <v>-7.674350744091043</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-7.589048135761757</v>
+        <v>-7.750196705500144</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-7.750869245212883</v>
+        <v>-7.91050460171364</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-8.266937357950923</v>
+        <v>-8.855902072328327</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0005736</t>
+          <t>X ≈ 0.0005674</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.48160758177135</v>
+        <v>-3.677403976712746</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.462581742214375</v>
+        <v>-3.554736226910677</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.657769455322409</v>
+        <v>-2.259366168255497</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.471973452977842</v>
+        <v>-2.060153411000506</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.840811668294521</v>
+        <v>-2.399832911556345</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.454609901509158</v>
+        <v>-3.580922439105194</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.687797560695117</v>
+        <v>-5.278260594922386</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.967779578330592</v>
+        <v>-5.558027650878735</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.472722003732144</v>
+        <v>-4.598540150253605</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-5.704737883457888</v>
+        <v>-5.836678430459116</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.07761976076425</v>
+        <v>-4.187562824235613</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.553095876351968</v>
+        <v>-2.635756229474381</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.770747453974046</v>
+        <v>-5.140196705205831</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-6.078094188893736</v>
+        <v>-6.735164837311359</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-4.927708998659014</v>
+        <v>-5.56886531738116</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-4.785205503360451</v>
+        <v>-5.431322032610282</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-6.275955096684797</v>
+        <v>-6.667790119183806</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-7.737646399842433</v>
+        <v>-7.414876828844349</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-4.355992805501174</v>
+        <v>-3.987976273607998</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-5.52583885454689</v>
+        <v>-5.177277252630894</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-5.164082118559627</v>
+        <v>-4.80239222793638</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-8.405827545045788</v>
+        <v>-8.547962959987572</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-7.226693094276953</v>
+        <v>-7.356057054845188</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-6.401656479055966</v>
+        <v>-6.055742519077519</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.002384</t>
+          <t>X ≈ 0.002377</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.759493259852306</v>
+        <v>2.080755431343292</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2929547187406669</v>
+        <v>1.005538896343268</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.611427797919063</v>
+        <v>3.263111979501438</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.648524247952551</v>
+        <v>3.288946058943445</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.7710457005073224</v>
+        <v>1.470954802883242</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.9630524587848726</v>
+        <v>1.290095995415584</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.443600561836966</v>
+        <v>2.734841935732469</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.786435016643381</v>
+        <v>2.08583254943634</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.4325401349897078</v>
+        <v>-0.0925130046106446</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.4592105096639543</v>
+        <v>-0.1282922195279141</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.9393272268365322</v>
+        <v>-0.5938464951335263</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.504612330129831</v>
+        <v>-2.353475371882112</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.878457317113337</v>
+        <v>-2.739666141395482</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.364168609025462</v>
+        <v>-5.181733900239777</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-6.402290175961589</v>
+        <v>-6.21613696676998</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-5.804991214044428</v>
+        <v>-5.39562289562285</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-4.808230661383917</v>
+        <v>-4.418428921489173</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-6.046103699102957</v>
+        <v>-6.004751106791836</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-6.581847992563283</v>
+        <v>-6.529600466608329</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-6.016835093932492</v>
+        <v>-5.972384286269893</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-5.053858140369137</v>
+        <v>-5.033448972754364</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-5.507985836503558</v>
+        <v>-5.47966530453396</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-6.741219869915575</v>
+        <v>-6.686672073533302</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-5.833057486483419</v>
+        <v>-6.021763586015837</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.004195</t>
+          <t>X ≈ 0.004187</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>311</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1685145621879727</v>
+        <v>0.2017888545068018</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.131898245016359</v>
+        <v>-1.098225236403017</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.9689405629651304</v>
+        <v>-0.9335861392966436</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.07643332514344792</v>
+        <v>-0.04023960772454416</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.163180950061722</v>
+        <v>1.2288539799574</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.5762842613473538</v>
+        <v>-0.5108096583610831</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.352995154105429</v>
+        <v>-1.286603102955482</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.597191803837113</v>
+        <v>-2.530456551921681</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.6264152886536678</v>
+        <v>-0.559708919846166</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.082147340114055</v>
+        <v>-1.014521236573614</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.9370934461529643</v>
+        <v>-1.061600291118715</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.537730757987987</v>
+        <v>-1.663107237886017</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.08987470959414168</v>
+        <v>-0.2175644427387482</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.9543183373486812</v>
+        <v>-1.083146626691331</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.005532534585405813</v>
+        <v>0.06453347170405976</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.05355930168428813</v>
+        <v>0.01583357692678788</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.063150862687735</v>
+        <v>2.132720298470261</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.9935372215120637</v>
+        <v>1.063249369568688</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.041143474077018</v>
+        <v>-0.971663108027883</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-3.426446945337659</v>
+        <v>-3.357164564940931</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-4.291190762695734</v>
+        <v>-4.221254141267082</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-3.080972184897803</v>
+        <v>-3.010926469235642</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.841566793335282</v>
+        <v>-1.771821531673197</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.9528779075233658</v>
+        <v>-0.8830235598160883</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.006005</t>
+          <t>X ≈ 0.005996</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.386539706404356</v>
+        <v>-1.667162902905652</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.873056020781348</v>
+        <v>1.945428719797171</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.413747713557953</v>
+        <v>1.49425177602933</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.026751785985709</v>
+        <v>1.110245125007637</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.626099698384735</v>
+        <v>-1.528176926487035</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.419327242240698</v>
+        <v>-2.328052845652806</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.231409060569234</v>
+        <v>-0.7973699505957228</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.4508206076377306</v>
+        <v>0.8981028151775163</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.122042412307032</v>
+        <v>-1.691988950276276</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.261890894971849</v>
+        <v>-1.149115152628475</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.007139470993756447</v>
+        <v>-0.2171607736245278</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.020956168014962</v>
+        <v>0.8198792966117665</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.510844034495172</v>
+        <v>2.328296177124066</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.596676765944473</v>
+        <v>3.423006774361617</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.93774552690725</v>
+        <v>2.764863476781137</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>4.839995119012222</v>
+        <v>4.675039872408249</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.745117111137802</v>
+        <v>2.896385893325593</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>3.293728466284392</v>
+        <v>3.449439926346479</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.509851629216165</v>
+        <v>3.994278675691902</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.69689542483664</v>
+        <v>3.852177117238796</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>4.460884558322313</v>
+        <v>4.625420422957013</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.770550417712379</v>
+        <v>1.91799551417953</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.718528198573594</v>
+        <v>2.192470226661548</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.6621947024423775</v>
+        <v>0.8008484997540606</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.007815</t>
+          <t>X ≈ 0.007805</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.458109999207835</v>
+        <v>1.091663174633872</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.703511796428181</v>
+        <v>-0.4776815249505049</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.881581127915432</v>
+        <v>5.080184199681057</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.101672112242966</v>
+        <v>2.309617011514035</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.323179186723017</v>
+        <v>1.562303905221953</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.9689950432453927</v>
+        <v>-0.7198657111498079</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.563923948667522</v>
+        <v>1.388844041173748</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.04569988166130656</v>
+        <v>-0.1239353048139051</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.153331649163327</v>
+        <v>1.975165045825122</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.5530499574021661</v>
+        <v>0.7907267360437373</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.0670786460051</v>
+        <v>2.710876913185174</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.027654164017854</v>
+        <v>3.666695410971656</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.903162945530632</v>
+        <v>2.543533344115538</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.574368117967374</v>
+        <v>5.203112903883039</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.328660019425918</v>
+        <v>4.544969606302423</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.3782655235927592</v>
+        <v>0.6126075570520513</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.897064391427321</v>
+        <v>1.713258321309048</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.792080975331999</v>
+        <v>2.019940251232768</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.7685347167762799</v>
+        <v>0.5897410971776225</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.021694214875978</v>
+        <v>3.245722709614881</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>4.957832648853277</v>
+        <v>5.172312344117948</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>6.121547014698287</v>
+        <v>6.33103428394336</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>6.396322181180416</v>
+        <v>6.193986362680604</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>4.66748827992847</v>
+        <v>4.883586208222788</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.009625</t>
+          <t>X ≈ 0.009615</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.517968989729461</v>
+        <v>4.224321425893905</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>7.57262398355968</v>
+        <v>7.260331144398002</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.17812125958654</v>
+        <v>1.889727825704078</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.724214952043098</v>
+        <v>3.423964817497328</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.488888669843909</v>
+        <v>4.211769850568004</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.546109780025837</v>
+        <v>3.275140531047406</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.163074156446392</v>
+        <v>5.873978364010981</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.754576008102937</v>
+        <v>4.472171413639906</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.796092073125607</v>
+        <v>4.513658595554631</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>7.412087170830738</v>
+        <v>7.111529436372081</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.60170067523422</v>
+        <v>2.329409303253101</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.887578523171747</v>
+        <v>2.612457652614097</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.89303080750949</v>
+        <v>2.61289109137595</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.9767587422378199</v>
+        <v>0.7064189565023966</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.3178275032004834</v>
+        <v>0.6100734117308306</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.9128875528219282</v>
+        <v>1.204460333673822</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.7787938586729766</v>
+        <v>1.070543196696349</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>1.803753945402555</v>
+        <v>1.527500245684159</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-3.064868654377527</v>
+        <v>-3.312788148672418</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.747881355932165</v>
+        <v>-2.002346833086392</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.161138262105297</v>
+        <v>-1.421297495434473</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.237093317747906</v>
+        <v>-1.497143456843574</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-2.657233405503071</v>
+        <v>-2.908062002788476</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-2.733174744771539</v>
+        <v>-2.983894256011787</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.01144</t>
+          <t>X ≈ 0.01143</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>128</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.794628594249161</v>
+        <v>1.82790288656799</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.446796920395123</v>
+        <v>-2.413123911781781</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.8010026155187404</v>
+        <v>0.8363570391872273</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.337209302325562</v>
+        <v>6.373403019744465</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.409439517301536</v>
+        <v>4.475112547197213</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>6.159104130308322</v>
+        <v>6.224578733294592</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.386237998254295</v>
+        <v>5.452630049404242</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.107683352735776</v>
+        <v>5.174418604651208</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.711699417758368</v>
+        <v>6.77840578656587</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.156614006988981</v>
+        <v>5.224240110529422</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.649723274104275</v>
+        <v>4.717049752691302</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.026879370629374</v>
+        <v>2.094550349243306</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.441361847857813</v>
+        <v>-1.372361717612854</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.662718658892125</v>
+        <v>-1.593440594059402</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.8033501020705742</v>
+        <v>0.8734161083600398</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>2.179660151691955</v>
+        <v>2.249053030303031</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>2.045566457543075</v>
+        <v>2.115135893325601</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>5.065583041447752</v>
+        <v>5.135295189504376</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>9.187956204379525</v>
+        <v>9.257436570428659</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>7.812499999999957</v>
+        <v>7.881782380396686</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>7.269299591002003</v>
+        <v>7.339236212430656</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>9.537094535359437</v>
+        <v>9.607140251021598</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>5.124369701841566</v>
+        <v>5.194114963503651</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>7.392178362573055</v>
+        <v>7.462032710280333</v>
       </c>
     </row>
     <row r="28">
@@ -2426,161 +2426,161 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.095174037329741</v>
+        <v>-2.577017326197925</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-11.90403376250039</v>
+        <v>-12.48626220965412</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-16.50162896342863</v>
+        <v>-17.11577062038724</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-18.26805385556919</v>
+        <v>-18.89255442706406</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-16.52806048269846</v>
+        <v>-17.10068532514321</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-13.18300113284957</v>
+        <v>-12.65839999010966</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-13.9558672649036</v>
+        <v>-13.43034867399999</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-14.23442191042216</v>
+        <v>-13.70856011875308</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-12.08764268750479</v>
+        <v>-11.53941336237027</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-13.91410967722165</v>
+        <v>-13.37615882564092</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-14.69238198905359</v>
+        <v>-14.16592897071295</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-11.81358115568639</v>
+        <v>-11.25318901245879</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-11.88544079522613</v>
+        <v>-11.3125212920808</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-12.10679760626055</v>
+        <v>-11.53360016852749</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-11.71309726635048</v>
+        <v>-11.12791367887397</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-10.06540563778173</v>
+        <v>-9.469696969696969</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-10.19949933193071</v>
+        <v>-9.603614106674506</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-8.199219590131193</v>
+        <v>-7.580795236027534</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-9.035728006146691</v>
+        <v>-8.428733642337228</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-6.743421052631582</v>
+        <v>-6.114228257901146</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-7.286621461629473</v>
+        <v>-6.656774425867141</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-7.36257651727211</v>
+        <v>-6.732620387276242</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-8.140432929737379</v>
+        <v>-7.521975462028237</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-9.269005847953181</v>
+        <v>-8.661637502485483</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.01505</t>
+          <t>X ≈ 0.01504</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.018186286556855</v>
+        <v>4.587000987833825</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>7.529164618066375</v>
+        <v>8.049692543914382</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.243310307826427</v>
+        <v>2.814205140453048</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.598688133571848</v>
+        <v>-2.962040018230205</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.728349773711791</v>
+        <v>4.297106218083293</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.91551438671862</v>
+        <v>3.218249619370582</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.142648254664593</v>
+        <v>2.446300935480188</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.864093609145989</v>
+        <v>2.168089490727112</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.222595454036501</v>
+        <v>-2.853714466598717</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.413825545450479</v>
+        <v>2.702483781415488</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.688184812565773</v>
+        <v>2.976543423577382</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.719114219114296</v>
+        <v>-2.365497119111197</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-5.407708001703959</v>
+        <v>-6.020304755587567</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-5.629064812738278</v>
+        <v>-6.241383632034093</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-8.852098615878148</v>
+        <v>-9.43117249923494</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-8.257038566256767</v>
+        <v>-8.836785577291906</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-4.544978414251837</v>
+        <v>-5.173234359839</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.4782432978580076</v>
+        <v>-0.2147839244196774</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.25846902489242</v>
+        <v>2.532753026124979</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>4.727564102564145</v>
+        <v>3.985421620903097</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>6.748466257668703</v>
+        <v>5.974521022557319</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>6.672511202026065</v>
+        <v>5.898675061148147</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>5.665235086456953</v>
+        <v>4.907326988820074</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>5.589293747188485</v>
+        <v>4.83149473559677</v>
       </c>
     </row>
     <row r="30">
@@ -2593,158 +2593,158 @@
         <v>45</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.3407880724173609</v>
+        <v>-0.3075137800985317</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.768480857382748</v>
+        <v>3.80215386599609</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.551002615518769</v>
+        <v>4.586357039187256</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.6072351421189239</v>
+        <v>-0.5710414247000202</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.24971729507925</v>
+        <v>1.315390324974928</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.659104130308194</v>
+        <v>3.724578733294464</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.33068244269861</v>
+        <v>7.397074493848557</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>11.49657224162456</v>
+        <v>11.56330749353999</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>9.315866084424968</v>
+        <v>9.38257245323247</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.09758622921116</v>
+        <v>4.165212332751601</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.816389940770932</v>
+        <v>8.88371641935796</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>10.75951825951833</v>
+        <v>10.82718923813226</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>11.85724926325334</v>
+        <v>11.9262493934983</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>9.413670229996704</v>
+        <v>9.482948294829427</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>13.19918343540385</v>
+        <v>13.26924944169331</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>13.79424348502528</v>
+        <v>13.86363636363636</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>11.43792756865415</v>
+        <v>11.50749700443667</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>11.3329441525588</v>
+        <v>11.40265630061542</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>13.77128953771277</v>
+        <v>13.8407699037619</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>11.73611111111099</v>
+        <v>11.80539349150771</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>8.970688479890875</v>
+        <v>9.040625101319527</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>11.11695564647048</v>
+        <v>11.18700136213264</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>15.83617525739712</v>
+        <v>15.90592051905921</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>11.31578947368427</v>
+        <v>11.38564382139155</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.01868</t>
+          <t>X ≈ 0.01867</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>48</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8.825878594249168</v>
+        <v>8.859152886567998</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.324036412938177</v>
+        <v>4.357709421551519</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.8010026155187049</v>
+        <v>0.8363570391871917</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.996124031007717</v>
+        <v>-1.959930313588814</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2780604826984288</v>
+        <v>-0.2123874528027514</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.992437463641714</v>
+        <v>2.057912066627985</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.302904664920995</v>
+        <v>3.369296716070941</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.142316647264231</v>
+        <v>-1.075581395348799</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.100800582241575</v>
+        <v>-1.034094213434074</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.375364006988939</v>
+        <v>4.442990110529379</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.816389940770932</v>
+        <v>8.88371641935796</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.70396270396272</v>
+        <v>12.77163368257665</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.496138152142315</v>
+        <v>9.565138282387274</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>11.35811467444123</v>
+        <v>11.42739273927396</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>4.449183435404002</v>
+        <v>4.519249441693468</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>2.960910151691991</v>
+        <v>3.030303030303067</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.7434831242097317</v>
+        <v>0.8130525599922578</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.6384997081144803</v>
+        <v>0.7082118561711042</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.8546228710462955</v>
+        <v>0.9241032370954301</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>1.041666666666728</v>
+        <v>1.110949047063457</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>0.4984662576687739</v>
+        <v>0.5684028790974267</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>4.589177868692836</v>
+        <v>4.659223584354997</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>4.863953035174909</v>
+        <v>4.933698296836994</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>8.954678362573098</v>
+        <v>9.024532710280376</v>
       </c>
     </row>
     <row r="32">
@@ -2754,243 +2754,243 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.468735737106385</v>
+        <v>2.241505827744504</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-2.580725491823699</v>
+        <v>-1.034447441193542</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>10.26528832980445</v>
+        <v>12.23341586271665</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>9.551495016611376</v>
+        <v>11.52046184327394</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>12.04336808873015</v>
+        <v>14.12584784131489</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.37338984459403</v>
+        <v>8.430461086235766</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.88623799825438</v>
+        <v>4.717335931757226</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>2.607683352735776</v>
+        <v>4.43912448700415</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.363485132044076</v>
+        <v>10.36296461009529</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>7.589649721274647</v>
+        <v>9.5900489340588</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>7.864008988389983</v>
+        <v>9.864108576220723</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>7.584915084915082</v>
+        <v>9.585359172772726</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>9.317566723570756</v>
+        <v>11.4033735765048</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>11.95335276967935</v>
+        <v>14.12347117064652</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>5.58013581635624</v>
+        <v>7.582974931889417</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.4609101516919196</v>
+        <v>2.295008912655931</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-2.530326399599865</v>
+        <v>-0.7800846949097817</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-8.349595529980824</v>
+        <v>-6.767278339907385</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.295099061522421</v>
+        <v>5.213318923369876</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-2.232142857142861</v>
+        <v>-0.4821882078385613</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>2.9389424481449</v>
+        <v>4.857618565371872</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.00584453535943652</v>
+        <v>1.84059613337454</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>3.13776255898442</v>
+        <v>5.056247316444782</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.2046783625730981</v>
+        <v>2.039238592633318</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.02229</t>
+          <t>X ≈ 0.02228</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>29</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.946568249421567</v>
+        <v>4.979842541740474</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>14.95622032098419</v>
+        <v>11.54161746752857</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>10.06824399482909</v>
+        <v>6.655322556428608</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>9.354450681635875</v>
+        <v>5.942368536985846</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.989180896611884</v>
+        <v>5.606578064438594</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>9.176345509618614</v>
+        <v>9.241820112604941</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.955203515495619</v>
+        <v>1.573319704576647</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11.57320059411509</v>
+        <v>8.191659983961557</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.269889072930731</v>
+        <v>-2.111680420330686</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>3.944329524230362</v>
+        <v>0.563679765701842</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.666964653414666</v>
+        <v>4.286015269932726</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.387870749939765</v>
+        <v>4.00726586648473</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>16.60820711765952</v>
+        <v>13.22893138583552</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>12.9385744445562</v>
+        <v>9.559576647319957</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>15.72791906758787</v>
+        <v>12.34970921180831</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>9.426427393071272</v>
+        <v>6.04754440961338</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-1.052493887284562</v>
+        <v>-4.431200313570997</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>2.290798558689076</v>
+        <v>-1.087765155323218</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.9413541404479702</v>
+        <v>-4.320149636467804</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>6.142241379310349</v>
+        <v>2.763247897638109</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>2.15076510824337</v>
+        <v>-1.227574132396896</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>2.074810052600817</v>
+        <v>-1.303420093805997</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>5.797861081151858</v>
+        <v>2.419330480745074</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>12.61847146602143</v>
+        <v>9.240049951659735</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.02411</t>
+          <t>X ≈ 0.02409</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>10.3258785942492</v>
+        <v>11.74376827118339</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.990703079604877</v>
+        <v>7.562837626679759</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.5510026155187475</v>
+        <v>2.278664731494914</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>11.83720930232561</v>
+        <v>13.10417225051377</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>19.47193951730154</v>
+        <v>20.46068947027415</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>15.65910413030835</v>
+        <v>16.80150181021764</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.886237998254295</v>
+        <v>4.491091587865782</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.607683352735677</v>
+        <v>8.059033989266496</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>10.64919941775845</v>
+        <v>11.94667501733514</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>17.87536400698891</v>
+        <v>18.86606703360627</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>14.14972327410425</v>
+        <v>15.29397282961435</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>13.87062937062935</v>
+        <v>15.01522342616636</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>4.746138152142173</v>
+        <v>6.199753667002518</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.524781341107818</v>
+        <v>9.824828636709768</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>11.86585010207052</v>
+        <v>13.01283918528311</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>8.460910151691955</v>
+        <v>9.761072261072258</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>4.326816457543032</v>
+        <v>5.781001277940945</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>4.221833041447809</v>
+        <v>5.676160574119763</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>0.4379562043795104</v>
+        <v>2.045898108890185</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-7.375</v>
+        <v>-5.459563773449425</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>0.08179959100210255</v>
+        <v>1.690197750892239</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>4.005844535359437</v>
+        <v>5.460505635636984</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>4.280619701841594</v>
+        <v>5.734980348119009</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>0.2046783625730413</v>
+        <v>1.812994248741859</v>
       </c>
     </row>
   </sheetData>
@@ -3180,657 +3180,657 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.02749</t>
+          <t>X &gt; -0.02748</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3332</v>
+        <v>3336</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.05266089904439042</v>
+        <v>-0.05346991783804356</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1035127820528388</v>
+        <v>-0.1042719165465229</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1850546466345548</v>
+        <v>-0.1857609232792541</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2260365210634347</v>
+        <v>-0.2267161697668385</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.2761953678073894</v>
+        <v>-0.2775886450531644</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2214928846170494</v>
+        <v>-0.2229466095795942</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2012508043733519</v>
+        <v>-0.2027531894863017</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2238578659022608</v>
+        <v>-0.2253427318643517</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.2250162978078123</v>
+        <v>-0.2264994655976622</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.144958766471909</v>
+        <v>-0.1465621282765923</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1522199246999065</v>
+        <v>-0.1538072195392175</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2944423997055523</v>
+        <v>-0.2958693042811831</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.2948430025092819</v>
+        <v>-0.2963048009710434</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.4087913698436481</v>
+        <v>-0.4101246944778083</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.2419020679384047</v>
+        <v>-0.2434560889493724</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.3474730818409739</v>
+        <v>-0.3488835725677788</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.1942976484767271</v>
+        <v>-0.1958964877692679</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.2215462275756224</v>
+        <v>-0.2231166896099239</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.2872460731151847</v>
+        <v>-0.2887322413043094</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.2622901678657072</v>
+        <v>-0.2638014519386047</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.1880654764642244</v>
+        <v>-0.1896833742719082</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1861170723190284</v>
+        <v>-0.1877406656950029</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.2834367037990049</v>
+        <v>-0.2849362052107622</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.3715521296237725</v>
+        <v>-0.3729493041081184</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.02568</t>
+          <t>X &gt; -0.02567</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3315</v>
+        <v>3319</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.01923824217979586</v>
+        <v>-0.02026063826740199</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.06863165219014178</v>
+        <v>-0.06960774895627964</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.08328995042850096</v>
+        <v>-0.08430164344751034</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1208116871796605</v>
+        <v>-0.1218051264070539</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2293202307488542</v>
+        <v>-0.2311112395014163</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1752793080355133</v>
+        <v>-0.17712938777224</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.09095287809623898</v>
+        <v>-0.09293349975642684</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1122205800171869</v>
+        <v>-0.1141870925002593</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1435933750344205</v>
+        <v>-0.1455219278912452</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.08918991310718383</v>
+        <v>-0.09121330981265174</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1279209566649513</v>
+        <v>-0.1298890228189009</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.2994938635155009</v>
+        <v>-0.3012673481448616</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.2941504828547608</v>
+        <v>-0.2959728287239187</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.3774742979898633</v>
+        <v>-0.3792058388776738</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.236436299854816</v>
+        <v>-0.2383627377938069</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.3756832879710075</v>
+        <v>-0.377421646583052</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1909439277670231</v>
+        <v>-0.1929105588692792</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.2479049892658907</v>
+        <v>-0.2498081939542658</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.3150558438132052</v>
+        <v>-0.316871492146511</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.2608089786080185</v>
+        <v>-0.2626842160522642</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.243697696520556</v>
+        <v>-0.2456147809467808</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.2112190763378763</v>
+        <v>-0.2131793063406491</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.3104538807881099</v>
+        <v>-0.3122856389059834</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.36847397528512</v>
+        <v>-0.3702398115635575</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.02387</t>
+          <t>X &gt; -0.02386</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3295</v>
+        <v>3299</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.05748487772185484</v>
+        <v>-0.05866770343799033</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1654621299217993</v>
+        <v>-0.166530265289758</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.171554682430596</v>
+        <v>-0.172679105391083</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.144691150163105</v>
+        <v>-0.1458798967966359</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3120073746719072</v>
+        <v>-0.3141053551536075</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2286109315691291</v>
+        <v>-0.2308026354120685</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1089310838713118</v>
+        <v>-0.1113023993291691</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1286500812721201</v>
+        <v>-0.1310112596022321</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.160468255957646</v>
+        <v>-0.1627906527823484</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1615051377677901</v>
+        <v>-0.1638616854259425</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2021509701520756</v>
+        <v>-0.2044478318497625</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.3730960602747686</v>
+        <v>-0.3752001037920323</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.4214359555407725</v>
+        <v>-0.4235324124768525</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.5039629856697374</v>
+        <v>-0.5059708146698654</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.3581208422393516</v>
+        <v>-0.3603354031272588</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.5018509745569162</v>
+        <v>-0.5038669122430832</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.3152186726810768</v>
+        <v>-0.3174677061904774</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.3416325750321008</v>
+        <v>-0.3438557182112021</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.3802256138022528</v>
+        <v>-0.3823939380458796</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.3571157926644446</v>
+        <v>-0.3593052671963619</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.3063144174879469</v>
+        <v>-0.3085908620696003</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.303527621146479</v>
+        <v>-0.305812263367983</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.3747201039836767</v>
+        <v>-0.3769077637690685</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.4326509242250793</v>
+        <v>-0.4347731399772741</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.02206</t>
+          <t>X &gt; -0.02205</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3263</v>
+        <v>3267</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1276982702865723</v>
+        <v>-0.1291414278132379</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.0975769812779248</v>
+        <v>-0.1130934981564735</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1201301494020868</v>
+        <v>-0.1352736270738006</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1164915810128235</v>
+        <v>-0.1314661220692628</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3428075881219854</v>
+        <v>-0.3284452914633675</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2909111089480021</v>
+        <v>-0.2936861068880603</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.25400590418473</v>
+        <v>-0.2568705596091547</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2712431492465726</v>
+        <v>-0.2741040880079879</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.242807903779152</v>
+        <v>-0.2457029885712458</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.2058077964898501</v>
+        <v>-0.2087928824605569</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.3105941862131871</v>
+        <v>-0.313438052186747</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.5110500186836049</v>
+        <v>-0.5136667138856978</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.5794574495682099</v>
+        <v>-0.5820551282290367</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.7217814453265845</v>
+        <v>-0.724219507699928</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.5681352280027809</v>
+        <v>-0.5707993983554687</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.596870343569428</v>
+        <v>-0.5994679620633789</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.4988716158514634</v>
+        <v>-0.5015982239621621</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.4328014033365832</v>
+        <v>-0.4356164359157262</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.4433167454368387</v>
+        <v>-0.4461086618451375</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.4830501989592904</v>
+        <v>-0.4857848773226294</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.4877043894021185</v>
+        <v>-0.4904656224316923</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.4842014064476032</v>
+        <v>-0.4869730099144718</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.5894783373741177</v>
+        <v>-0.5921074967166646</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.6472983459773118</v>
+        <v>-0.6498627595696433</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.02025</t>
+          <t>X &gt; -0.02024</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3224</v>
+        <v>3228</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.06968517654561879</v>
+        <v>-0.07161634420119611</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.06598207135014889</v>
+        <v>-0.08211821772207628</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.1331268143733979</v>
+        <v>-0.1488646356896197</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2133455682046304</v>
+        <v>-0.2288452093901014</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2530065203179461</v>
+        <v>-0.2393437066536848</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2335547222518315</v>
+        <v>-0.2372204041052868</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2485969292372232</v>
+        <v>-0.2523006131535439</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2935512151655004</v>
+        <v>-0.2972213460270083</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.2344066334920214</v>
+        <v>-0.2381491008840158</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.1876378460067372</v>
+        <v>-0.1914947753435357</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.204308236553743</v>
+        <v>-0.20812766168698</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.4655881819046215</v>
+        <v>-0.4691070581640986</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.459425990052523</v>
+        <v>-0.4630339930064551</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.5079954059545884</v>
+        <v>-0.5115613476109786</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.3754118837011546</v>
+        <v>-0.3791904718067869</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.4425551948426971</v>
+        <v>-0.4462111847773187</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.3726573895631304</v>
+        <v>-0.3764116337223555</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.2116034910599893</v>
+        <v>-0.2155667461789861</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.2557570195287653</v>
+        <v>-0.2596528202301229</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.3291511771995062</v>
+        <v>-0.3329453423755453</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.3582375952390535</v>
+        <v>-0.3620366133198374</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.4157301701582341</v>
+        <v>-0.4194657861300968</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.5255818485460324</v>
+        <v>-0.529164302522986</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.5831628284938972</v>
+        <v>-0.5866816639451571</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.01844</t>
+          <t>X &gt; -0.01843</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3192</v>
+        <v>3196</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1582533285883869</v>
+        <v>-0.143800175290842</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3067455824984222</v>
+        <v>-0.3231526652788261</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3602952369555794</v>
+        <v>-0.3763295279769494</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.4654058907005663</v>
+        <v>-0.4811848496178754</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.3773286234645852</v>
+        <v>-0.3640676021493974</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4530454024019548</v>
+        <v>-0.4571263071534446</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.4605990226244856</v>
+        <v>-0.4647368973744719</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.4721171460173821</v>
+        <v>-0.4762663268556793</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.4128523440127552</v>
+        <v>-0.4170745933780751</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.3579485320004565</v>
+        <v>-0.3623058396263872</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.3775778179394038</v>
+        <v>-0.3818907272089831</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.6699449115179377</v>
+        <v>-0.6739191021282664</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.6525505771740399</v>
+        <v>-0.6566421978123742</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.6994535121088603</v>
+        <v>-0.7035076558185978</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.6214976017719707</v>
+        <v>-0.6257063565385579</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.6015898483080449</v>
+        <v>-0.6057768698218098</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.5297012042262637</v>
+        <v>-0.533991877514282</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.3973039191526269</v>
+        <v>-0.4017714875724536</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.4441207427583791</v>
+        <v>-0.4485146948009131</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.5514705882352899</v>
+        <v>-0.5557176196032714</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.5441784997647758</v>
+        <v>-0.5484826059500421</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.6328530225616618</v>
+        <v>-0.6370553399727754</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.7779459104352853</v>
+        <v>-0.7819465785670374</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.7727652464494597</v>
+        <v>-0.7767814323979749</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01663</t>
+          <t>X &gt; -0.01662</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3150</v>
+        <v>3154</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.2209520585417124</v>
+        <v>-0.1898543620925466</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2092338488088785</v>
+        <v>-0.2094720050688892</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1493128418945133</v>
+        <v>-0.1662430238446078</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3723205178069477</v>
+        <v>-0.3888920622227303</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2149291695671494</v>
+        <v>-0.2025325174511607</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.388890817591907</v>
+        <v>-0.393995848856143</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.3544442506402063</v>
+        <v>-0.3596727897124836</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.3307052728566831</v>
+        <v>-0.3359947749638508</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.2711545645425204</v>
+        <v>-0.2765184558583726</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.268170612043626</v>
+        <v>-0.2736186674939916</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.2285183451240655</v>
+        <v>-0.2339925720086384</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.5210188419615776</v>
+        <v>-0.5261546270600164</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.5829757719084014</v>
+        <v>-0.5881486961210243</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.5641708589554355</v>
+        <v>-0.5693930126493427</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.4761384983094104</v>
+        <v>-0.4815411971428034</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.432342936683078</v>
+        <v>-0.4377450557456797</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.3892798669183151</v>
+        <v>-0.3947533471807674</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.3358348926460337</v>
+        <v>-0.3225732023917942</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4178282647171017</v>
+        <v>-0.4045330305845951</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.5607958148383005</v>
+        <v>-0.5474027637274475</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.6096054200984895</v>
+        <v>-0.5960457901041494</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.6984701854527486</v>
+        <v>-0.7035774295867654</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.8491803616303457</v>
+        <v>-0.8540724374472148</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.8111946532999212</v>
+        <v>-0.8161457932072551</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.01482</t>
+          <t>X &gt; -0.01481</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3092</v>
+        <v>3096</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.09006483230174211</v>
+        <v>-0.07400906715947286</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1359443006587071</v>
+        <v>-0.1195827806763816</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.03155549240719324</v>
+        <v>0.0490819749198721</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3107006655200735</v>
+        <v>-0.2924600467936074</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.207700238246872</v>
+        <v>-0.178234447338312</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.517215046010854</v>
+        <v>-0.505572343529586</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.4352940262065985</v>
+        <v>-0.4417768937008688</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2448601115269824</v>
+        <v>-0.2516264114260096</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1205268302287479</v>
+        <v>-0.1274522063579013</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.070512281670851</v>
+        <v>-0.07760191006263994</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.00303212389765406</v>
+        <v>-0.01017908541619761</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.4246639884937693</v>
+        <v>-0.4313068626047283</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.5308692648200477</v>
+        <v>-0.5375187224437283</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.4752186588921248</v>
+        <v>-0.4819715218944509</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.3406681296170646</v>
+        <v>-0.3476804111372189</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.2750485313293467</v>
+        <v>-0.2820760799484177</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1962704007068936</v>
+        <v>-0.2034206207021754</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.1720965678515682</v>
+        <v>-0.1600677137214319</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.3757344640091915</v>
+        <v>-0.3444511352828172</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.4925710594315262</v>
+        <v>-0.4613018675051492</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.5644039631174991</v>
+        <v>-0.5327972070074622</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.5888548828693914</v>
+        <v>-0.576353856178919</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.7475083291962576</v>
+        <v>-0.7539295150239553</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.739694211812413</v>
+        <v>-0.7461391243449427</v>
       </c>
     </row>
     <row r="14">
@@ -3840,79 +3840,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3018</v>
+        <v>3022</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.03019206148660913</v>
+        <v>0.0634663538054383</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.05721608586105731</v>
+        <v>0.09088909447439875</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.09924100866987828</v>
+        <v>0.1345954323383651</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2339369427337061</v>
+        <v>-0.2161590480856006</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.02064697363751122</v>
+        <v>0.00781340330521374</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4081338393686735</v>
+        <v>-0.3979105653553887</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2723508576639375</v>
+        <v>-0.2808240171087704</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.07041691111651716</v>
+        <v>-0.07920458375463113</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.04298138065799861</v>
+        <v>-0.05180426285752304</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.06018248883712829</v>
+        <v>0.05109821863748465</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.02360904498576133</v>
+        <v>0.01460992413871764</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.3684723466757731</v>
+        <v>-0.3770030808358484</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.5158374012109306</v>
+        <v>-0.5243536344719431</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.4203607606766653</v>
+        <v>-0.4290429042904194</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.233323451648431</v>
+        <v>-0.2423605506033155</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.2136930229112224</v>
+        <v>-0.2226692286137464</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.1627634299859153</v>
+        <v>-0.1718334657758618</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.06926851329919259</v>
+        <v>-0.05875223283534581</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.283181738061721</v>
+        <v>-0.2528940080836932</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.4405195234943733</v>
+        <v>-0.4102149741006187</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.5007889558367467</v>
+        <v>-0.4701625636195814</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.5570693719253299</v>
+        <v>-0.5460085250286824</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.6269655913018539</v>
+        <v>-0.6354107559803026</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.6833269389510903</v>
+        <v>-0.6917148079194959</v>
       </c>
     </row>
     <row r="15">
@@ -3922,1719 +3922,1719 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2927</v>
+        <v>2931</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.1276436994766357</v>
+        <v>0.1609179917954648</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2676888229857326</v>
+        <v>0.301361831599074</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3554832672499018</v>
+        <v>0.3908376909183886</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.03375843960990466</v>
+        <v>-0.0166173468542965</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1974829955624031</v>
+        <v>0.2246458126418887</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2076984520905896</v>
+        <v>-0.1993859646008644</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1117225727858084</v>
+        <v>-0.1227263660743745</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1391352398489616</v>
+        <v>0.127729300746239</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.2682470368059811</v>
+        <v>0.2566666561310882</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.262570539823237</v>
+        <v>0.250839244066583</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.3185456022186415</v>
+        <v>0.3067846269265146</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.05925722217857299</v>
+        <v>0.04778691843745264</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1257964527624083</v>
+        <v>-0.1372426699937606</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.08850656349178365</v>
+        <v>-0.1000542381560336</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.04553367434387923</v>
+        <v>-0.05727653969986335</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.04369264408029494</v>
+        <v>-0.05532856656452623</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.05517535691808462</v>
+        <v>-0.06682936553003316</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.05783953699699396</v>
+        <v>-0.04917031305099329</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.216886906125211</v>
+        <v>-0.187859953088676</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.3166581371545547</v>
+        <v>-0.2876473843492633</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.39601610865666</v>
+        <v>-0.3666812500522454</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.4175081447361535</v>
+        <v>-0.4084207994558966</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.5322218282130748</v>
+        <v>-0.5432230310393251</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.5879420679017926</v>
+        <v>-0.598889329978924</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.009384</t>
+          <t>X &gt; -0.009385</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2832</v>
+        <v>2836</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2718624595596282</v>
+        <v>0.3051367518784573</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5329689512288738</v>
+        <v>0.5666419598422152</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4261341483142473</v>
+        <v>0.4614885719827342</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.01264789881680883</v>
+        <v>0.02913784962873933</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.2637963091583231</v>
+        <v>0.2896293833950381</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1260082292422382</v>
+        <v>-0.119686436821155</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.1043623396663094</v>
+        <v>0.09047641909908322</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1972827905431842</v>
+        <v>0.1831905344757274</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1887424757548573</v>
+        <v>0.1746632453233303</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.2438590843447841</v>
+        <v>0.2295069644619616</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.3628783919375422</v>
+        <v>0.3484161032357349</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.2098271186941147</v>
+        <v>0.1955034413023355</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.09143910251181353</v>
+        <v>0.07700119978613174</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1022461298402675</v>
+        <v>0.08773029201654481</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.1687736667060094</v>
+        <v>0.1539956018528343</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.2213047958075336</v>
+        <v>0.2065873371292071</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.07302724358463308</v>
+        <v>0.05847670641954039</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.03195617251064675</v>
+        <v>-0.02535621894632811</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.2388150328428509</v>
+        <v>-0.2111263038227946</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.3834626234132585</v>
+        <v>-0.3557528556850187</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.4120275694917765</v>
+        <v>-0.3840410170370561</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.5022712021141018</v>
+        <v>-0.4951354803848176</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.6653739444697635</v>
+        <v>-0.678891293105444</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.7204628803647566</v>
+        <v>-0.7339299131328829</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.007573</t>
+          <t>X &gt; -0.007575</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2727</v>
+        <v>2731</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.5699587399686905</v>
+        <v>0.6032330322875197</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.8176611852515023</v>
+        <v>0.8513341938648438</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4344270235333099</v>
+        <v>0.4697814472017967</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.2876466201098324</v>
+        <v>0.303275515190748</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.5262596047969836</v>
+        <v>0.5503630025706201</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.04130690200780407</v>
+        <v>0.0451616112545139</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.2010865936574291</v>
+        <v>0.1839597397503283</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.344909630107999</v>
+        <v>0.3274798291409624</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.4075053688354089</v>
+        <v>0.3899852615932105</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.3852252195528578</v>
+        <v>0.3674977691727008</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4617437344623383</v>
+        <v>0.4439742328080527</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.2770621191673825</v>
+        <v>0.2594682324549851</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.08800286877842467</v>
+        <v>0.07034091108378959</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.1078098707347976</v>
+        <v>0.09004187489604476</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.09270703584298445</v>
+        <v>0.07475425231326938</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.1973669598910774</v>
+        <v>0.1794258373205722</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.1949966113328472</v>
+        <v>0.1770074655376277</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.05339657129029973</v>
+        <v>0.05745594297913925</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.0600298813033362</v>
+        <v>-0.03409288438286495</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.275768949102897</v>
+        <v>-0.2281187909063505</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.2112407020382463</v>
+        <v>-0.1631667535158456</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.3386039805804657</v>
+        <v>-0.3122459628194889</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.4818436412669342</v>
+        <v>-0.4771707377046965</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.4260513770675303</v>
+        <v>-0.443153119086162</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.005763</t>
+          <t>X &gt; -0.005766</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2599</v>
+        <v>2603</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.780945515855322</v>
+        <v>0.8142198081741512</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.942901932377346</v>
+        <v>0.9765749409906874</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.726910837316062</v>
+        <v>0.7622652609845488</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.4554189427234334</v>
+        <v>0.4699613371440989</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.5874712694055901</v>
+        <v>0.6313027957631761</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.03109035304081686</v>
+        <v>0.05345062622001961</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3134968037673076</v>
+        <v>0.3140067224443968</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.3633325292964429</v>
+        <v>0.3637835625700632</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2737204905552986</v>
+        <v>0.2522485562674817</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.2885491353906318</v>
+        <v>0.266755896981735</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.3169011882147004</v>
+        <v>0.2951508246667984</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.175194004307933</v>
+        <v>0.1535435510816825</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.08271833289230557</v>
+        <v>-0.1044019474978626</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.2045852615792683</v>
+        <v>-0.2261782330015265</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.1495108810323487</v>
+        <v>-0.1714458548301394</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.04600427385867789</v>
+        <v>0.02397391637897783</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02716221244123318</v>
+        <v>0.02800523331021054</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.1930728363855252</v>
+        <v>-0.1691074016664444</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.3227045716480887</v>
+        <v>-0.275973567820138</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.5966673069535133</v>
+        <v>-0.5273849265567847</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.5792303859387644</v>
+        <v>-0.5320901417759885</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.6708182866321053</v>
+        <v>-0.6463533140955775</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.7963033750815143</v>
+        <v>-0.7944679216288932</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.849573272671222</v>
+        <v>-0.8703001748521686</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.003953</t>
+          <t>X &gt; -0.003956</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2469</v>
+        <v>2474</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7613624652169406</v>
+        <v>0.7726958128074557</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.5874772731532687</v>
+        <v>0.6394506549251986</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.8010026155187404</v>
+        <v>0.8539910577281375</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.5710802700675188</v>
+        <v>0.6247129754075331</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.6493588721402475</v>
+        <v>0.7322921118888672</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.09315011659312233</v>
+        <v>0.1534380642095385</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.2077386033369919</v>
+        <v>0.2682285983764316</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.453588959835372</v>
+        <v>0.513999418838992</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.2530719470040239</v>
+        <v>0.3136486321926313</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3095851530744937</v>
+        <v>0.3704094653680841</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.3653066410804513</v>
+        <v>0.4025336236590462</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.1905001299185471</v>
+        <v>0.2044293815013702</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.1023466963426145</v>
+        <v>-0.1122810724515233</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.2997942449875168</v>
+        <v>-0.3095307513809047</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.166499271160319</v>
+        <v>-0.1770782419224446</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.01624310346372937</v>
+        <v>-0.002599674581915679</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.1099000810740378</v>
+        <v>-0.07211168341111573</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.4979405129396355</v>
+        <v>-0.4357275377683436</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.6861845153939825</v>
+        <v>-0.6000816187386349</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.984381318236963</v>
+        <v>-0.8982802711796651</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.8971648102924448</v>
+        <v>-0.8345208611343793</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.03017327119661</v>
+        <v>-0.9912075662783266</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.0554126868224</v>
+        <v>-1.040095828735645</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.026589357151487</v>
+        <v>-1.035087338224074</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.002142</t>
+          <t>X &gt; -0.002147</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2303</v>
+        <v>2306</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7611879841237155</v>
+        <v>0.7709175924503811</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.6423690250830205</v>
+        <v>0.6524037698791147</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.106606250308872</v>
+        <v>1.117498907699343</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.8687973594437182</v>
+        <v>0.8803234349694051</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.239139863472026</v>
+        <v>1.279827080069182</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.474335631822818</v>
+        <v>0.5152361727409627</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.523624411062606</v>
+        <v>0.5650867968090836</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.4614263211476839</v>
+        <v>0.5463909229902697</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.3298571416873983</v>
+        <v>0.3716151291264254</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.6632427948677275</v>
+        <v>0.6800143319826617</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.7032096318348948</v>
+        <v>0.6945584032103298</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.4928130794681991</v>
+        <v>0.4590615949180403</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.2173128378812876</v>
+        <v>0.1576988360204084</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.02174578169763919</v>
+        <v>-0.03770173642201513</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.08276984176688984</v>
+        <v>0.02249619494012478</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.2006064640563778</v>
+        <v>0.1665091801514436</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.02312882196819288</v>
+        <v>0.01510339765830793</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.1686224900056104</v>
+        <v>-0.1505874502875599</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.3429548585271576</v>
+        <v>-0.2991549300049527</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.6331344902386036</v>
+        <v>-0.5893255987880082</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.3954238363298401</v>
+        <v>-0.3512993469795376</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.6191554646405635</v>
+        <v>-0.6006058461163093</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.6047969648250984</v>
+        <v>-0.5863219402257513</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.5248049201016727</v>
+        <v>-0.5320587901532789</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.0003317</t>
+          <t>X &gt; -0.0003371</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.8232330916037043</v>
+        <v>0.8783836557987996</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.6323577212595239</v>
+        <v>0.6397607036028319</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.116659181175301</v>
+        <v>1.172895500725687</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.9319663970826824</v>
+        <v>0.9887876351290998</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.047697093059114</v>
+        <v>1.133766393351053</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.4171608883650819</v>
+        <v>0.5034248871407456</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.7986959107122118</v>
+        <v>0.8372454340196285</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.7125414575938365</v>
+        <v>0.751341681574246</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.5135572821162313</v>
+        <v>0.6005211711812564</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.6055227371476732</v>
+        <v>0.6929901105293794</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.8600216379156294</v>
+        <v>0.9189728296143826</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.8980727986505599</v>
+        <v>0.9286849646279194</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.6208973043580244</v>
+        <v>0.622830590079495</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.3320102567705234</v>
+        <v>0.305597867479058</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.2995850418296087</v>
+        <v>0.3014764739204097</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.3163318384389484</v>
+        <v>0.3474348878583697</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.3268164575430319</v>
+        <v>0.3867566203356674</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.27002581253209</v>
+        <v>0.3589825690804815</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.1487995778735396</v>
+        <v>0.2376870521242722</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.04668674698795883</v>
+        <v>0.1355155210518291</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.3709562175080734</v>
+        <v>0.4600213762071945</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.1504228486124504</v>
+        <v>0.1914971874377827</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.18423415967289</v>
+        <v>0.2251241157194457</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.3300399826309572</v>
+        <v>0.3901396466965608</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.001479</t>
+          <t>X &gt; 0.001472</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1853</v>
+        <v>1858</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.336654456318165</v>
+        <v>1.412916327428249</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.001478941673838</v>
+        <v>1.131902969938643</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.447554339656676</v>
+        <v>1.575604351015187</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.218674819566964</v>
+        <v>1.346521299314375</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.392198137991194</v>
+        <v>1.548365235369253</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.8789317165152184</v>
+        <v>0.9826432494236315</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.453048343081889</v>
+        <v>1.554780587038657</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.390010938942631</v>
+        <v>1.49162290572643</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.108251141896304</v>
+        <v>1.210529442479853</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.358122627678597</v>
+        <v>1.459119142787451</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.448914648767349</v>
+        <v>1.51812502150851</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.309680071815997</v>
+        <v>1.346902499780946</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.263937504893043</v>
+        <v>1.299009250129124</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.096518126436898</v>
+        <v>1.131693814542743</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.9230237806034793</v>
+        <v>0.9902463934595502</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.9247720718645596</v>
+        <v>1.025459112111427</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.114302973184884</v>
+        <v>1.214469854574219</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.225069287402448</v>
+        <v>1.271093090473165</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.686068394239328</v>
+        <v>0.7334860860368835</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.7112998921251403</v>
+        <v>0.7588679562847815</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.031098404378533</v>
+        <v>1.077462800159445</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.170893079048753</v>
+        <v>1.216902091710509</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.068106217483418</v>
+        <v>1.114627611512269</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.132902863382604</v>
+        <v>1.146437984769079</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.003289</t>
+          <t>X &gt; 0.003282</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1588</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.266092565300184</v>
+        <v>1.299366857619013</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.119715036810668</v>
+        <v>1.153388045424009</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.253331124014657</v>
+        <v>1.288685547683144</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.9800664451827217</v>
+        <v>1.016260162601625</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.495853928881147</v>
+        <v>1.561526958776824</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.8648939352170686</v>
+        <v>0.9303685382033393</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.28774838214354</v>
+        <v>1.354140433293487</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.323857046882999</v>
+        <v>1.390592298798431</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.365373111905633</v>
+        <v>1.432079480713135</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.661392956013479</v>
+        <v>1.72901905955392</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.847456271585386</v>
+        <v>1.877213377612641</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.946196121259099</v>
+        <v>1.976059946474273</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.955206162217792</v>
+        <v>1.985685796547031</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.174655396523498</v>
+        <v>2.205135554461677</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.145447079400547</v>
+        <v>2.215513085690013</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>2.047811914916132</v>
+        <v>2.117204793527208</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.102635097341519</v>
+        <v>2.172204533124045</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.438457726586293</v>
+        <v>2.508169874642917</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.898913383220879</v>
+        <v>1.968393749270014</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.834068010075562</v>
+        <v>1.903350390472291</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.046535107374837</v>
+        <v>2.116471728803489</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.28544151268941</v>
+        <v>2.355487228351571</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.371299802597235</v>
+        <v>2.44104506425932</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.295358463328768</v>
+        <v>2.365212811036045</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.0051</t>
+          <t>X &gt; 0.005091</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1277</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.533396213669725</v>
+        <v>1.566670505988554</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.668071912807697</v>
+        <v>1.701744921421039</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.794542161329232</v>
+        <v>1.829896584997719</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.237365919396844</v>
+        <v>1.273559636815747</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.576872955046248</v>
+        <v>1.642545984941925</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.215877818640351</v>
+        <v>1.281352421626622</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.930873863563612</v>
+        <v>1.997265914713559</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.278787503088118</v>
+        <v>2.34552275500355</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.850452354328446</v>
+        <v>1.917158723135948</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.329553513645166</v>
+        <v>2.397179617185607</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.525604245130118</v>
+        <v>2.592930723717146</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.794670091067907</v>
+        <v>2.86234106968184</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.453264228884599</v>
+        <v>2.522264359129558</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.936684238523689</v>
+        <v>3.005962303356412</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.669295677638317</v>
+        <v>2.739361683927783</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.559578906586239</v>
+        <v>2.628971785197315</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.112251069915779</v>
+        <v>2.181820505698305</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.790353010124335</v>
+        <v>2.860065158180959</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.614933494904236</v>
+        <v>2.68441386095337</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.115211433046206</v>
+        <v>3.184493813442934</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.590021987243233</v>
+        <v>3.659958608671886</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.592375467231015</v>
+        <v>3.662421182893176</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.397299419930839</v>
+        <v>3.467044681592924</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.086432473771218</v>
+        <v>3.156286821478496</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.00691</t>
+          <t>X &gt; 0.006901</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.453581992807386</v>
+        <v>2.577035723155909</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.603473419460698</v>
+        <v>1.625609387293245</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.914545354962613</v>
+        <v>1.934764027881982</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.303738653509932</v>
+        <v>1.324584931358054</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.586254656333459</v>
+        <v>2.633193225511711</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.361472822378353</v>
+        <v>2.409059719933857</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.927432642950485</v>
+        <v>2.870410111069191</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.854851220912863</v>
+        <v>2.797748512153731</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.10234050941645</v>
+        <v>3.044785539906051</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.461357827792234</v>
+        <v>3.505168938895252</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.323770647945679</v>
+        <v>3.470903812300762</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.3536365796922</v>
+        <v>3.500479177609179</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.435118584686002</v>
+        <v>2.582866956590678</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.728694832354016</v>
+        <v>2.875662694738139</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.584696652019076</v>
+        <v>2.731394011751611</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.840930749014305</v>
+        <v>1.989706935750107</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.912810278346328</v>
+        <v>1.958564721691431</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.631719756174832</v>
+        <v>2.675923401220714</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.332909860404285</v>
+        <v>2.275165244632191</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>2.931900102986603</v>
+        <v>2.97588566919427</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.315579199652923</v>
+        <v>3.358313807497503</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>4.166503649674574</v>
+        <v>4.207442152357665</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>3.926345757454335</v>
+        <v>3.865267327326876</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.850404418185867</v>
+        <v>3.892209997022412</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.00872</t>
+          <t>X &gt; 0.00871</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.116002051039324</v>
+        <v>3.071481653691322</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.369303902650145</v>
+        <v>2.325745951231916</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.9296034385640084</v>
+        <v>0.8877269022009244</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.038855392860555</v>
+        <v>0.996690690977367</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.005547199057368</v>
+        <v>2.989667341717762</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.467060234560726</v>
+        <v>3.450606130554867</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.380065158748124</v>
+        <v>3.363588953513833</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.787381569470988</v>
+        <v>3.770309015610074</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.41737500074877</v>
+        <v>3.400837293415186</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.426804336207049</v>
+        <v>4.408743535186915</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.740944124584388</v>
+        <v>3.723899067759795</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.461850221109486</v>
+        <v>3.445149664311799</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.611707425118915</v>
+        <v>2.595960200195407</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.116002191587988</v>
+        <v>2.100908721009091</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>2.005767797543818</v>
+        <v>2.12769693027785</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2.326479424668641</v>
+        <v>2.448111249481116</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.918037308023145</v>
+        <v>2.040221509763917</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.910447581914141</v>
+        <v>2.894284915531777</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.852222322349384</v>
+        <v>2.836203693716378</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>2.902091906721537</v>
+        <v>2.886063202314539</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>2.770414131468435</v>
+        <v>2.7544759384581</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>3.517504343315537</v>
+        <v>3.500547785268175</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>3.106408453556242</v>
+        <v>3.090090990900912</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>3.579163959280919</v>
+        <v>3.56220394315708</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.01053</t>
+          <t>X &gt; 0.01052</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>552</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.666458304394126</v>
+        <v>2.699732596712956</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.7008480071411114</v>
+        <v>0.7345210157544528</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.529263485083959</v>
+        <v>0.5646179087524459</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.1777890124705053</v>
+        <v>0.213982729889409</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.529910531794286</v>
+        <v>2.595583561689963</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.441712825960494</v>
+        <v>3.507187428946764</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.487687273616615</v>
+        <v>2.554079324766562</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.477248570127045</v>
+        <v>3.543983822042478</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.97528637428011</v>
+        <v>3.041992743087611</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.469566905539658</v>
+        <v>3.537193009080099</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.106245013234705</v>
+        <v>4.173571491821733</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.645991689469952</v>
+        <v>3.713662668083884</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.521500470982808</v>
+        <v>2.590500601227767</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.481303080238305</v>
+        <v>2.550581145071028</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>2.547009522360433</v>
+        <v>2.617075528649899</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>2.779750731402096</v>
+        <v>2.849143610013172</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>2.283338196673462</v>
+        <v>2.352907632455988</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>3.265311302317322</v>
+        <v>3.335023450373946</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.749550407278115</v>
+        <v>4.819030773327249</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>4.393115942028977</v>
+        <v>4.462398322425706</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>4.031074953320882</v>
+        <v>4.101011574749535</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>5.042076419417405</v>
+        <v>5.112122135079566</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>4.954532745319831</v>
+        <v>5.024278006981916</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>5.603229087210785</v>
+        <v>5.673083434918063</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.01234</t>
+          <t>X &gt; 0.01233</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>424</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.929652179154864</v>
+        <v>2.962926471473693</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.651080438095441</v>
+        <v>1.684753446708783</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4472290306130802</v>
+        <v>0.482583454281567</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.681658622202725</v>
+        <v>-1.645464904783822</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.962505555037382</v>
+        <v>2.028178584933059</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.621368281251719</v>
+        <v>2.68684288423799</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.612653092593916</v>
+        <v>1.679045143743863</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.985041843301772</v>
+        <v>3.051777095217204</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.847312625305534</v>
+        <v>1.914018994113036</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.96026966736629</v>
+        <v>3.027895770906731</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.942176104292955</v>
+        <v>4.009502582879982</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.134780314025598</v>
+        <v>4.20245129263953</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.717836265349781</v>
+        <v>3.78683639559474</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.732328510919196</v>
+        <v>3.801606575751919</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>3.073397271881895</v>
+        <v>3.14346327817136</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>2.960910151691955</v>
+        <v>3.030303030303031</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>2.35511834433548</v>
+        <v>2.424687780118006</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>2.721833041447752</v>
+        <v>2.791545189504376</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.409654317587119</v>
+        <v>3.479134683636254</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>3.360849056603776</v>
+        <v>3.430131437000504</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>3.053497704209597</v>
+        <v>3.12343432563825</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>3.685089818378309</v>
+        <v>3.75513553404047</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>4.903261211275527</v>
+        <v>4.973006472937612</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>5.063168928610843</v>
+        <v>5.13302327631812</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.01415</t>
+          <t>X &gt; 0.01414</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.380589840449815</v>
+        <v>4.540971068386213</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.565171164711259</v>
+        <v>5.721345785187914</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.34127617174974</v>
+        <v>5.495447948278141</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.107726019650812</v>
+        <v>3.267342413683885</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.301726751344091</v>
+        <v>7.477006486591151</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.184939996569717</v>
+        <v>7.057912066627921</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.108122496734538</v>
+        <v>5.982933079707266</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.957227425684067</v>
+        <v>7.825933756166322</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.871083916238611</v>
+        <v>5.746208816868894</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.832810815499577</v>
+        <v>7.700565868105144</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9.322975553739525</v>
+        <v>9.186746722388271</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.739930282483471</v>
+        <v>8.604967015909963</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>8.223341799558646</v>
+        <v>8.087865555114455</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.305936356305445</v>
+        <v>8.169816981698176</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>7.343053749486991</v>
+        <v>7.208643381087306</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>6.722308327983747</v>
+        <v>6.590909090909093</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.980311898272518</v>
+        <v>5.850931347871011</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>5.875328482177238</v>
+        <v>5.746090644049829</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>7.003305748452512</v>
+        <v>6.871072934065076</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>6.278495440729486</v>
+        <v>6.148827834942182</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>6.039246399512685</v>
+        <v>5.909311970006463</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>6.875145447213534</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>8.669677452601441</v>
+        <v>8.532183145321824</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>9.201638848895293</v>
+        <v>9.062411498159157</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.01596</t>
+          <t>X &gt; 0.01595</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>251</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.493209271540046</v>
+        <v>4.526483563858875</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.954846505899702</v>
+        <v>4.988519514513044</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.303990663327504</v>
+        <v>6.339345086995991</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.191790975632358</v>
+        <v>5.227984693051262</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>8.41217856112624</v>
+        <v>8.477851591021917</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>8.200936799631023</v>
+        <v>8.266411402617294</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.029664293075008</v>
+        <v>7.096056344224955</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.539954269070392</v>
+        <v>9.606689520985825</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>8.386251210587048</v>
+        <v>8.45295757939455</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.206041297825585</v>
+        <v>9.273667401366026</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>11.0740260629489</v>
+        <v>11.14135254153593</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.99015128297998</v>
+        <v>12.05782226159391</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>12.4592855625008</v>
+        <v>12.52828569274576</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>12.63633512596844</v>
+        <v>12.70561319080116</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>12.37581026143312</v>
+        <v>12.44587626772259</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>11.37724481304654</v>
+        <v>11.44663769165761</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>9.25111924638766</v>
+        <v>9.320688682170186</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>7.552510332284399</v>
+        <v>7.622222480341023</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>8.167039869718202</v>
+        <v>8.236520235767337</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>6.760458167330668</v>
+        <v>6.829740547727397</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>5.818851383830726</v>
+        <v>5.888788005259379</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>6.938115451694095</v>
+        <v>7.008161167356256</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>9.603328865188182</v>
+        <v>9.673074126850267</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>10.3242002749237</v>
+        <v>10.39405462263098</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.01777</t>
+          <t>X &gt; 0.01776</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>206</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.549179565122984</v>
+        <v>5.582453857441813</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.214004050478657</v>
+        <v>5.247677059091998</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6.686924945615822</v>
+        <v>6.722279369284308</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.458568525626561</v>
+        <v>6.494762243045464</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>9.97679388623358</v>
+        <v>10.04246691612926</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>9.193084712832601</v>
+        <v>9.258559315818871</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.963907901166927</v>
+        <v>7.030299952316874</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.112537721667778</v>
+        <v>9.17927297358321</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.183180000282647</v>
+        <v>8.249886369090149</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10.32196594873651</v>
+        <v>10.38959205227695</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>11.56719900225961</v>
+        <v>11.63452548084664</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.25897888519248</v>
+        <v>12.32664986380641</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.59079834631699</v>
+        <v>12.65979847656195</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>13.3403153216904</v>
+        <v>13.40959338652313</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>12.19594718944922</v>
+        <v>12.26601319573869</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>10.84925966625506</v>
+        <v>10.91865254486613</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>8.773418399290605</v>
+        <v>8.842987835073131</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>6.726687410379796</v>
+        <v>6.79639955843642</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>6.942810573311611</v>
+        <v>7.012290939360746</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>5.673543689320397</v>
+        <v>5.742826069717125</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>5.130343280322442</v>
+        <v>5.200279901751095</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>6.025262011087598</v>
+        <v>6.095307726749759</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>8.241784750385257</v>
+        <v>8.311530012047342</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>10.10759098393232</v>
+        <v>10.1774453316396</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.01958</t>
+          <t>X &gt; 0.01957</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>158</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.553726695515024</v>
+        <v>4.587000987833854</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.484373965680824</v>
+        <v>5.518046974294165</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>8.475053248430129</v>
+        <v>8.510407672098616</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>9.027082720047112</v>
+        <v>9.063276437466016</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>13.09219268185851</v>
+        <v>13.15786571175418</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>11.38062311765009</v>
+        <v>11.44609772063636</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.076111415975824</v>
+        <v>8.142503467125771</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>12.2279365172927</v>
+        <v>12.29467176920814</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.0036297975052</v>
+        <v>11.0703361663127</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>12.12852856395096</v>
+        <v>12.1961546674914</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>12.40288783106629</v>
+        <v>12.47021430965332</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>12.12379392759139</v>
+        <v>12.19146490620533</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>13.5309482787245</v>
+        <v>13.59994840896946</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>13.94250286009522</v>
+        <v>14.01178092492795</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>14.54939440586804</v>
+        <v>14.6194604121575</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>13.24572027827423</v>
+        <v>13.3151131568853</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>11.21289240691011</v>
+        <v>11.28246184269264</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>8.576263421194582</v>
+        <v>8.645975569251206</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>8.792386584126398</v>
+        <v>8.861866950175532</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>7.080696202531641</v>
+        <v>7.14997858292837</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>6.537495793533687</v>
+        <v>6.607432414962339</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6.461540737891077</v>
+        <v>6.531586453553238</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>9.267961473993459</v>
+        <v>9.337706735655544</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>10.45784291953512</v>
+        <v>10.5276972672424</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.02139</t>
+          <t>X &gt; 0.02138</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.862463960102858</v>
+        <v>5.230120628503521</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.779320965783739</v>
+        <v>7.314698668863379</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.965636761860203</v>
+        <v>7.489582845638843</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8.877859708829639</v>
+        <v>8.389532052002551</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>13.39063870429341</v>
+        <v>12.89245125687464</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>11.95178705713759</v>
+        <v>12.27296583006878</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9.552904664920952</v>
+        <v>9.081662307468754</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>14.96540692997151</v>
+        <v>14.44861215303827</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.75489047466894</v>
+        <v>11.26429288334006</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>13.42007945414341</v>
+        <v>12.91073204601325</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>13.69443872125875</v>
+        <v>13.18479168817517</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>13.41534481778385</v>
+        <v>12.90604228472718</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>14.7298779895406</v>
+        <v>14.20223505658074</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>14.50852117850625</v>
+        <v>13.98115618013415</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>17.10162245979415</v>
+        <v>16.54881933416649</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>16.88367437933423</v>
+        <v>16.33675464320626</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>15.12356442502271</v>
+        <v>14.58993428042233</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>13.39256474876483</v>
+        <v>12.8721903507947</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>10.35665539137144</v>
+        <v>9.862275280106125</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>9.730691056910572</v>
+        <v>9.242669477170921</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>7.561474387750017</v>
+        <v>7.087220083398442</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>8.298527462188709</v>
+        <v>7.817825734892558</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>11.01232701891474</v>
+        <v>10.51165528608431</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>13.37541006989017</v>
+        <v>12.8551778715707</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.0232</t>
+          <t>X &gt; 0.02319</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4.836516892121544</v>
+        <v>5.306521307620656</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.565171164711259</v>
+        <v>6.024376088218219</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.316960062327247</v>
+        <v>7.74425177602933</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.73082632360218</v>
+        <v>9.136560914481336</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>14.74853526198238</v>
+        <v>15.11655991561827</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>12.8080403005211</v>
+        <v>13.19826294382091</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10.97134438123302</v>
+        <v>11.37368268098319</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>16.01193867188466</v>
+        <v>16.35862913096695</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.98962494967327</v>
+        <v>15.34748473393429</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>16.34344911337191</v>
+        <v>16.67983221579253</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>15.55397859325321</v>
+        <v>15.90126027900708</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>15.2748846897783</v>
+        <v>15.62251087555909</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.15039347129116</v>
+        <v>14.49934880870297</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>14.99286644749085</v>
+        <v>15.33090151120375</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>17.52542457015567</v>
+        <v>17.8306529504653</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>19.18431440701111</v>
+        <v>19.47767145135566</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>20.11405050009623</v>
+        <v>20.39638589332556</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>16.81757772229882</v>
+        <v>17.13365045266227</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>13.8422115235285</v>
+        <v>14.19164709674448</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>10.83776595744681</v>
+        <v>11.22059816987041</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>9.230735761214824</v>
+        <v>9.625420422957013</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>10.21861049280624</v>
+        <v>10.60220604049528</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>12.62104523375647</v>
+        <v>12.98194391087208</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>13.60893368172203</v>
+        <v>13.95874323659616</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.02501</t>
+          <t>X &gt; 0.025</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.847617724683985</v>
+        <v>2.880892017002814</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>5.410992934677338</v>
+        <v>5.44466594329068</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>9.768393919866568</v>
+        <v>9.803748343535055</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7.60532524435456</v>
+        <v>7.641518961773464</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>13.03715690860588</v>
+        <v>13.10282993850156</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>11.77504615929384</v>
+        <v>11.84052076228011</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>13.90073075187748</v>
+        <v>13.96712280302743</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>19.41927755563428</v>
+        <v>19.48601280754971</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>16.56224289601923</v>
+        <v>16.62894926482673</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>15.7884074852498</v>
+        <v>15.85603358879024</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>16.06276675236514</v>
+        <v>16.13009323095216</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>15.78367284889023</v>
+        <v>15.85134382750417</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>17.55773235504078</v>
+        <v>17.62673248528574</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>17.33637554400642</v>
+        <v>17.40565360883915</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>19.57599502960681</v>
+        <v>19.64606103589627</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>23.06960580386586</v>
+        <v>23.13899868247694</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>25.83406283435463</v>
+        <v>25.90363227013715</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>21.38125333130283</v>
+        <v>21.45096547935945</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>18.69882576959696</v>
+        <v>18.76830613564609</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>17.43659420289855</v>
+        <v>17.50587658329528</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>12.54556770694408</v>
+        <v>12.61550432837273</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>12.46961265130147</v>
+        <v>12.53965836696363</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>15.64293854242128</v>
+        <v>15.71268380408337</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>18.46554792779049</v>
+        <v>18.53540227549777</v>
       </c>
     </row>
   </sheetData>
@@ -5824,657 +5824,657 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.02749</t>
+          <t>X &lt; -0.02748</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-4.398759086910211</v>
+        <v>-4.365484794591382</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.733934601554537</v>
+        <v>-4.700261592941196</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.825808978684151</v>
+        <v>-1.790454555015664</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.090326929558472</v>
+        <v>-1.054133212139568</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.442954010055161</v>
+        <v>1.508627039950838</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.268432101575733</v>
+        <v>-1.202957498589463</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.04129823362976</v>
+        <v>-1.974906182479813</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.8705775168294849</v>
+        <v>-0.8038422649140529</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.8290614518068509</v>
+        <v>-0.7623550829993491</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.501447587213953</v>
+        <v>-4.433821483673512</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-4.227088320098616</v>
+        <v>-4.159761841511589</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2.740194588020685</v>
+        <v>2.807865566634618</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>3.064978731852371</v>
+        <v>3.133978862097329</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.64072337009339</v>
+        <v>8.710001434926113</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.735415319461886</v>
+        <v>0.8054813257513516</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>5.678301456039783</v>
+        <v>5.747694334650859</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-1.702169049703343</v>
+        <v>-1.632599613920817</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.3578771034797867</v>
+        <v>-0.2881649554231629</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>2.756796784089708</v>
+        <v>2.826277150138843</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>1.494565217391312</v>
+        <v>1.56384759778804</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-1.947185916244329</v>
+        <v>-1.877249294815677</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-2.023140971886939</v>
+        <v>-1.953095256224778</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>2.599460281551707</v>
+        <v>2.669205543213792</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>6.871345029239755</v>
+        <v>6.941199376947033</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.02568</t>
+          <t>X &lt; -0.02567</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>86</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-4.83691210342522</v>
+        <v>-4.803637811106391</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-5.172087618069547</v>
+        <v>-5.138414609456206</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-5.44899738448126</v>
+        <v>-5.413642960812773</v>
       </c>
       <c r="F7" s="4" t="n">
+        <v>-4.963806282581089</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-0.6484339644306942</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>-2.787049173682156</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>-5.884579252921334</v>
+      </c>
+      <c r="J7" s="4" t="n">
         <v>-4.999999999999993</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>-0.7141069943263716</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>-2.852523776668427</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>-5.950971304071281</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>-5.066735251915425</v>
-      </c>
       <c r="K7" s="4" t="n">
-        <v>-3.862428489218381</v>
+        <v>-3.795722120410879</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-5.79905459766222</v>
+        <v>-5.731428494121779</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4.361904632872474</v>
+        <v>-4.294578154285446</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.335745649699135</v>
+        <v>2.403416628313067</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.374045128886415</v>
+        <v>2.443045259131374</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.641060410875319</v>
+        <v>5.710338475708042</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.3309663811403354</v>
+        <v>0.401032387429801</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>5.577189221459399</v>
+        <v>5.646582100070475</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-1.533648658736034</v>
+        <v>-1.464079222953508</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.6869493205175132</v>
+        <v>0.7566614685741371</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>3.22865387879817</v>
+        <v>3.298134244847304</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>1.090116279069761</v>
+        <v>1.15939865946649</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.5469158700718069</v>
+        <v>0.6168524915004596</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.6918298832452123</v>
+        <v>-0.6217841675830513</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>3.071317376260168</v>
+        <v>3.141062637922253</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>5.320957432340542</v>
+        <v>5.390811780047819</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.02387</t>
+          <t>X &lt; -0.02386</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>106</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.7307251793357</v>
+        <v>-2.697450887016871</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.179108241149841</v>
+        <v>-1.145435232536499</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.675412478820881</v>
+        <v>-1.640058055152394</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.332602018429135</v>
+        <v>-3.296408301010231</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.962505555037382</v>
+        <v>2.028178584933059</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.6805185112011145</v>
+        <v>-0.6150439082148438</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.283573322500423</v>
+        <v>-4.217181271350476</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.618731741603888</v>
+        <v>-3.551996489688456</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2.633819450166165</v>
+        <v>-2.567113081358663</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.464258634520498</v>
+        <v>-2.396632530980057</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.246503140990065</v>
+        <v>-1.179176662403037</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.134780314025598</v>
+        <v>4.20245129263953</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5.840477774783743</v>
+        <v>5.909477905028702</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.44930964299467</v>
+        <v>8.518587707827393</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>4.016793498296984</v>
+        <v>4.08685950458645</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>8.38543845357875</v>
+        <v>8.454831332189826</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>2.590967400939256</v>
+        <v>2.660536836721782</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>3.429380211259073</v>
+        <v>3.499092359315696</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>4.588899600605977</v>
+        <v>4.658379966655112</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>3.83254716981132</v>
+        <v>3.901829550208049</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>2.34595053439827</v>
+        <v>2.415887155826923</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>2.269995478755661</v>
+        <v>2.340041194417822</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>4.431563098067976</v>
+        <v>4.501308359730061</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>6.242414211629701</v>
+        <v>6.312268559336978</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.02206</t>
+          <t>X &lt; -0.02205</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>138</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.436711333808347</v>
+        <v>-0.4034370414895179</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.560021558076286</v>
+        <v>-2.177062760702647</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.55044665984358</v>
+        <v>-2.176232888870324</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.264239973036737</v>
+        <v>-2.889186908313064</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.167591691214582</v>
+        <v>1.810993842161245</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.9054809419025247</v>
+        <v>0.9709555448887954</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1326148098484978</v>
+        <v>0.1990068609984448</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.5786978454893585</v>
+        <v>0.6454330974047906</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1044237706474291</v>
+        <v>-0.03771740183992733</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.8782591814168583</v>
+        <v>-0.8106330778764175</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.570013129176736</v>
+        <v>1.637339607763764</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.36338299381778</v>
+        <v>6.431053972431712</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>8.137442499968323</v>
+        <v>8.206442630213282</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>11.53927409473106</v>
+        <v>11.60855215956379</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>7.981792131056089</v>
+        <v>8.051858137345555</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>8.57685218067747</v>
+        <v>8.646245059288546</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>6.268845443050282</v>
+        <v>6.338414878832808</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>4.714586664636158</v>
+        <v>4.784298812692782</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>4.930709827567973</v>
+        <v>5.000190193617108</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>5.842391304347828</v>
+        <v>5.911673684744557</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>6.023828576509295</v>
+        <v>6.093765197937948</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>5.947873520866686</v>
+        <v>6.017919236528847</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>8.396561730827081</v>
+        <v>8.466306992489166</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>9.769895753877442</v>
+        <v>9.83975010158472</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.02025</t>
+          <t>X &lt; -0.02024</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>177</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.426930394514834</v>
+        <v>-1.393656102196005</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.596867541864043</v>
+        <v>-2.290230653354811</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.776681000300464</v>
+        <v>-1.481058691149855</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.7955590592563411</v>
+        <v>-0.5086194521656253</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.03088534145552302</v>
+        <v>-0.2826121719039065</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.4086924798611733</v>
+        <v>-0.3432178768749026</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.05161510909034206</v>
+        <v>0.01477694205960489</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.799773748215955</v>
+        <v>0.8665090001313871</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.288653689586269</v>
+        <v>-0.2219473207787672</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.062489100355698</v>
+        <v>-0.9948629968152574</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.7881298332403617</v>
+        <v>-0.7208033546533343</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.017522025996612</v>
+        <v>4.085193004610545</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.022974310334327</v>
+        <v>4.091974440579285</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.931561002124816</v>
+        <v>5.000839066957539</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>2.577714508850235</v>
+        <v>2.647780515139701</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>3.737746309884052</v>
+        <v>3.807139188495128</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>2.473709112910271</v>
+        <v>2.543278548692797</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.4561330602471685</v>
+        <v>-0.3864209121905446</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.3249618540970829</v>
+        <v>0.3944422201462174</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.641949152542374</v>
+        <v>1.711231532939102</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>2.228692246369285</v>
+        <v>2.298628867797937</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>3.282680693551534</v>
+        <v>3.352726409213695</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>5.25237111427095</v>
+        <v>5.322116375933035</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>6.30637327782734</v>
+        <v>6.376227625534618</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.01844</t>
+          <t>X &lt; -0.01843</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>209</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1354024037730142</v>
+        <v>-0.08634474376372481</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.493095424102485</v>
+        <v>1.738661802503934</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.96727055810247</v>
+        <v>2.205404658234841</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.167352842995435</v>
+        <v>3.397212543554012</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.845145258928333</v>
+        <v>1.632850642435315</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.989247670978173</v>
+        <v>3.054722273964444</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.173319337967214</v>
+        <v>3.239711389117161</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.373233591970177</v>
+        <v>3.439968843885609</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.457811857949757</v>
+        <v>2.524518226757259</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.683976447180328</v>
+        <v>1.751602550720769</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.958335714295664</v>
+        <v>2.025662192882692</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6.463930806036075</v>
+        <v>6.531601784650007</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>6.296377386591992</v>
+        <v>6.365377516836951</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.031958374600698</v>
+        <v>7.101236439433421</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>5.894558236041867</v>
+        <v>5.964624242331332</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>5.532680486620187</v>
+        <v>5.602073365231263</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>4.441648993428203</v>
+        <v>4.511218429210729</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>2.422789979246801</v>
+        <v>2.492502127303425</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>3.117382041700147</v>
+        <v>3.186862407749281</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>4.739832535885171</v>
+        <v>4.809114916281899</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>4.675101026408747</v>
+        <v>4.7450376478374</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>6.034552669330729</v>
+        <v>6.10459838499289</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>8.223203433898981</v>
+        <v>8.292948695561066</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>8.147262094630513</v>
+        <v>8.21711644233779</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01663</t>
+          <t>X &lt; -0.01662</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>251</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.8713331397037436</v>
+        <v>0.4767999453915621</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.04104295214115439</v>
+        <v>-0.03861603776602607</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.083918019401899</v>
+        <v>-0.8681884153582331</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.376891842008121</v>
+        <v>1.580912901167409</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.5756795303175082</v>
+        <v>-0.7311621563600994</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.595612066816265</v>
+        <v>1.661086669802536</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.21957133158763</v>
+        <v>1.285963382737577</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.9410166860690694</v>
+        <v>1.007751937984501</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1888819574409055</v>
+        <v>0.2555883262484073</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2086973403222743</v>
+        <v>0.2763234438627151</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.3105941862131871</v>
+        <v>-0.2432677076261598</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.378565878565887</v>
+        <v>3.446236857179819</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.238201644205716</v>
+        <v>4.307201774450675</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.016844833171362</v>
+        <v>4.086122898004085</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>2.961088197308669</v>
+        <v>3.031154203598135</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>2.36567205645386</v>
+        <v>2.435064935064936</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>1.834752965479545</v>
+        <v>1.904322401262071</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>1.178008340252532</v>
+        <v>1.005830903790084</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.190944252188331</v>
+        <v>2.015373078365215</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>3.97161354581673</v>
+        <v>3.789520475634824</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>4.623632260324747</v>
+        <v>4.43745049814499</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>5.742896328188117</v>
+        <v>5.812942043850278</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>7.611296992678213</v>
+        <v>7.681042254340298</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>7.136949278907757</v>
+        <v>7.206803626615034</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.01482</t>
+          <t>X &lt; -0.01481</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>309</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.6389776357827444</v>
+        <v>-0.7927458476091758</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.8041687152669184</v>
+        <v>-0.9597508959087619</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.715878413420171</v>
+        <v>-2.865872260175827</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.4288491737082225</v>
+        <v>0.2428297713368437</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5795074280360879</v>
+        <v>-0.8713331397037436</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.501547860211858</v>
+        <v>2.378424887140746</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.728681728157831</v>
+        <v>1.795073779307778</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.1575899591613705</v>
+        <v>-0.09085470724593847</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.402247527579256</v>
+        <v>-1.335541158771754</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.85453952998855</v>
+        <v>-1.786913426448109</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.544810487953598</v>
+        <v>-2.47748400936657</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.677703325613301</v>
+        <v>1.745374304227234</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.804015965647054</v>
+        <v>2.873016095892012</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.261115746252578</v>
+        <v>2.330393811085301</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.9590976904950139</v>
+        <v>1.029163696784479</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.2679841066758826</v>
+        <v>0.3373769852869586</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.5091964041933039</v>
+        <v>-0.4396269684107779</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.7459088940361198</v>
+        <v>-0.866011080592088</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.279380152599629</v>
+        <v>0.9575973421328783</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>2.437297734627833</v>
+        <v>2.109073377181289</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>3.188595707506906</v>
+        <v>2.852700842655771</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>3.436265247333544</v>
+        <v>3.301696702634494</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>5.005538795692694</v>
+        <v>5.075284057354779</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>4.929597456424226</v>
+        <v>4.999451804131503</v>
       </c>
     </row>
     <row r="14">
@@ -6487,76 +6487,76 @@
         <v>383</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.47773897681023</v>
+        <v>-1.722688545657029</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.195825417804457</v>
+        <v>-2.437162373320248</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.72172465720854</v>
+        <v>-2.97148357777936</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3186348535185743</v>
+        <v>-0.456493887472007</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.982605937243925</v>
+        <v>-2.198821561329922</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.061701532905722</v>
+        <v>0.9784647436572911</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.02909514111143352</v>
+        <v>0.09548719226138047</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.548160803108424</v>
+        <v>-1.481425551192991</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.766384997826052</v>
+        <v>-1.69967862901855</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.540220408595481</v>
+        <v>-2.47259430505504</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.265861141480144</v>
+        <v>-2.198534662893117</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.8316683316683324</v>
+        <v>0.8993393102822651</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.044839450843526</v>
+        <v>2.113839581088484</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.304002120328654</v>
+        <v>1.373280185161377</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-0.0640838916399602</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.3183106275288239</v>
+        <v>-0.2489177489177479</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.7121445814180092</v>
+        <v>-0.6425751456354831</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.444833625218912</v>
+        <v>-1.526636628677444</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2290789197842642</v>
+        <v>-0.01204394905182227</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.460509138381205</v>
+        <v>1.213762899877246</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>1.961695152359745</v>
+        <v>1.710177770872257</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>2.407933308205394</v>
+        <v>2.315473584354933</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.943805080431645</v>
+        <v>3.01355034209373</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>3.390056952651435</v>
+        <v>3.459911300358712</v>
       </c>
     </row>
     <row r="15">
@@ -6569,1716 +6569,1716 @@
         <v>474</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.791276217466276</v>
+        <v>-1.98109607608756</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.065900693980026</v>
+        <v>-3.247973184131048</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.768325115573688</v>
+        <v>-3.955309627479444</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.540941958178621</v>
+        <v>-1.638079234952805</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.956631911269895</v>
+        <v>-3.115107118074754</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4585429285152074</v>
+        <v>-0.510222105279837</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.021325026955786</v>
+        <v>-0.9549329758058391</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.560383874155015</v>
+        <v>-2.493648622239583</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.359203943586174</v>
+        <v>-3.292497574778672</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.29270321990181</v>
+        <v>-3.225077116361369</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.648596053626818</v>
+        <v>-3.581269575039791</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.036933654580707</v>
+        <v>-1.969262675966775</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.8505005033199495</v>
+        <v>-0.7815003730749908</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.071857314354304</v>
+        <v>-1.002579249521581</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.310620486164716</v>
+        <v>-1.24055447987525</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.345812537383672</v>
+        <v>-1.276419658772596</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.269822197919147</v>
+        <v>-1.200252762136621</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.251851169078563</v>
+        <v>-1.305093465957803</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.2793433736795095</v>
+        <v>-0.458949984193147</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.3296413502109772</v>
+        <v>0.148063893001769</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.8412932618881257</v>
+        <v>0.6559378931029656</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.9763086703805328</v>
+        <v>0.9179955141794949</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>1.673024765132709</v>
+        <v>1.742770026794794</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>2.019024354134281</v>
+        <v>2.088878701841558</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.009384</t>
+          <t>X &lt; -0.009385</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>569</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.190700812382559</v>
+        <v>-2.34102042365727</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.834471745569942</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.434986876600348</v>
+        <v>-3.587556004291031</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.521809962122759</v>
+        <v>-1.59698025551684</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.762736489703713</v>
+        <v>-2.884726021738217</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.8242583915831005</v>
+        <v>-0.8558408471249948</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.947387220659891</v>
+        <v>-1.880995169509944</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.401073214689831</v>
+        <v>-2.334337962774399</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.359557149667197</v>
+        <v>-2.292850780859695</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.607998514902484</v>
+        <v>-2.540372411362043</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.209295990344067</v>
+        <v>-3.14196951175704</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.437601802750656</v>
+        <v>-2.369930824136723</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.810779536123974</v>
+        <v>-1.741779405879015</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.857004998646936</v>
+        <v>-1.787726933814213</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.165673540661473</v>
+        <v>-2.095607534372007</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.446270233597012</v>
+        <v>-2.376877354985936</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.704707185189015</v>
+        <v>-1.635137749406489</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.18167573048207</v>
+        <v>-1.214584407693515</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.1595833386784236</v>
+        <v>-0.2981676327236684</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.5547012302284742</v>
+        <v>0.4140722227785147</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.7144885189457995</v>
+        <v>0.5720514488580264</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>1.165774236589669</v>
+        <v>1.128521829968967</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>1.967790176358264</v>
+        <v>2.037535438020349</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>2.243342685947432</v>
+        <v>2.31319703365471</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.007573</t>
+          <t>X &lt; -0.007575</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>674</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.011382083217661</v>
+        <v>-3.128402018263586</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-4.304282171132584</v>
+        <v>-4.415506609728993</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.864063854200609</v>
+        <v>-2.990735471825992</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.3961732678369</v>
+        <v>-2.450126392020223</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.352285002639377</v>
+        <v>-3.443241650151826</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.392594540297289</v>
+        <v>-1.408164629537268</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.01775018490671</v>
+        <v>-1.951358133756763</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.591725805314482</v>
+        <v>-2.52499055339905</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.845630715181066</v>
+        <v>-2.778924346373564</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.733203201282848</v>
+        <v>-2.665577097742407</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.049685883945941</v>
+        <v>-2.982359405358913</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.294806375308589</v>
+        <v>-2.227135396694656</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.499061257015825</v>
+        <v>-1.430061126770866</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.572707580605567</v>
+        <v>-1.503429515772844</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.493086382419818</v>
+        <v>-1.423020376130353</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.931999744910705</v>
+        <v>-1.862606866299629</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.918382951615023</v>
+        <v>-1.848813515832497</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.34621429583035</v>
+        <v>-1.362812269875242</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.8953771289537684</v>
+        <v>-0.9992104015063106</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.02781899109793073</v>
+        <v>-0.2215226417598402</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.274283495051364</v>
+        <v>-0.4686478348366592</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.2432332593950477</v>
+        <v>0.135061848654729</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.8147443309216911</v>
+        <v>0.7948094079480938</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.5904350391309663</v>
+        <v>0.6602893868382438</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.005763</t>
+          <t>X &lt; -0.005766</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>802</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.117879131337943</v>
+        <v>-3.210342808388909</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.885534544157501</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.280471981755106</v>
+        <v>-3.379117683377508</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.507276447364632</v>
+        <v>-2.546350066675274</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.930045594360998</v>
+        <v>-3.063129109168671</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.129977755547756</v>
+        <v>-1.201163840962828</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.026913366509973</v>
+        <v>-2.028782590000965</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.181398533120344</v>
+        <v>-2.183078297455396</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.891743510281337</v>
+        <v>-1.825037141473835</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.921162047601626</v>
+        <v>-1.853535944061186</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.01901121721086</v>
+        <v>-1.951684738623833</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.553688247236629</v>
+        <v>-1.486017268622696</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.6930678031927613</v>
+        <v>-0.6240676729478025</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.294077219686173</v>
+        <v>-0.22479915485345</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.456730543090714</v>
+        <v>-0.3866645368012485</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.102365282551219</v>
+        <v>-1.032972403940143</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-1.03964316978616</v>
+        <v>-1.042820062009433</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.3254306401442832</v>
+        <v>-0.4032438923814752</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.08926380089264541</v>
+        <v>-0.06328303254896639</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.9741271820448958</v>
+        <v>0.7439101719600032</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.9296798902539152</v>
+        <v>0.7728542248530559</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>1.227789672516543</v>
+        <v>1.145541992315124</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>1.627253118300416</v>
+        <v>1.62060157620602</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.800688337635449</v>
+        <v>1.870542685342727</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.003953</t>
+          <t>X &lt; -0.003956</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.508867168462658</v>
+        <v>-2.53208259389659</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.259562031741893</v>
+        <v>-2.390000233134849</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.901226683844314</v>
+        <v>-3.032690579860386</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.390208338482076</v>
+        <v>-2.524902065001271</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.591890269932506</v>
+        <v>-2.803850867436928</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.128129912244873</v>
+        <v>-1.286036977958062</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.416211416016203</v>
+        <v>-1.574468781626578</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.061826242146992</v>
+        <v>-2.219198416625431</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.534365150011105</v>
+        <v>-1.693039900335087</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.667859045305619</v>
+        <v>-1.826977940588833</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.820394121840231</v>
+        <v>-1.919410801679703</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.352422923927719</v>
+        <v>-1.39147553122627</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.5558895959901093</v>
+        <v>-0.5310155637666583</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.03018130563705768</v>
+        <v>-0.004231192349998025</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.3689417869368938</v>
+        <v>-0.3418616694177388</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.7784060876242833</v>
+        <v>-0.8158508158508155</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.5287985157190036</v>
+        <v>-0.629255132315464</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.5002056324541755</v>
+        <v>0.3342802322394149</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.9952981122037912</v>
+        <v>0.7638468268389573</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.783798283261802</v>
+        <v>1.549897353658757</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.562486286281022</v>
+        <v>1.393706233843972</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.915715779994635</v>
+        <v>1.8122246561663</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.975898671798646</v>
+        <v>1.938347796121676</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.899957332530178</v>
+        <v>1.928668048626236</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.002142</t>
+          <t>X &lt; -0.002147</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.011947102067055</v>
+        <v>-2.027943887625518</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.940951596654116</v>
+        <v>-1.957686692050842</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.973749859728784</v>
+        <v>-2.989944576611691</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.559187094070815</v>
+        <v>-2.577630223741586</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.326978426792238</v>
+        <v>-3.404833495968248</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.738007783049078</v>
+        <v>-1.81997572215095</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.829209156217246</v>
+        <v>-1.912234815460621</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.696114115618698</v>
+        <v>-1.870216201480488</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.423198772286881</v>
+        <v>-1.507920928235571</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.106536445499749</v>
+        <v>-2.140117387212271</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.194168128610656</v>
+        <v>-2.177163628863859</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.749280131633071</v>
+        <v>-1.681609153019139</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.154314336545546</v>
+        <v>-1.032687804569328</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.7421869846839755</v>
+        <v>-0.6197087100014329</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.8581317983819119</v>
+        <v>-0.7343737467124214</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.115176804829787</v>
+        <v>-1.045783926218711</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.7429931526110991</v>
+        <v>-0.7268025124715507</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.3407803886792848</v>
+        <v>-0.3787446655680853</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.02015420619610353</v>
+        <v>-0.07227357449883698</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.625</v>
+        <v>0.5310910839325444</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.1363946774442653</v>
+        <v>0.0428432904706284</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.6063904862238658</v>
+        <v>0.5663534662804608</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.5720586818051387</v>
+        <v>0.5321831453218309</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.4050426612980473</v>
+        <v>0.4201196074596254</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.0003317</t>
+          <t>X &lt; -0.0003371</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.629511740323288</v>
+        <v>-1.712063730642647</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.479535015633218</v>
+        <v>-1.488615745486314</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.284440422455951</v>
+        <v>-2.367580553680526</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.06443004193671</v>
+        <v>-2.148901812969271</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.240215590826722</v>
+        <v>-2.370125548040882</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.266269004020039</v>
+        <v>-1.398280536995799</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.848638775457438</v>
+        <v>-1.905790218852097</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.712197065799394</v>
+        <v>-1.770025839793277</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.404652489496684</v>
+        <v>-1.537825556717721</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.537809645705678</v>
+        <v>-1.671647678865696</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.937103073201108</v>
+        <v>-2.028092250298229</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.991646078472421</v>
+        <v>-2.040757242379733</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.544281009534423</v>
+        <v>-1.550131178690663</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.091985125957997</v>
+        <v>-1.053880668965768</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.033026302423806</v>
+        <v>-1.037866663175542</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.068325230616892</v>
+        <v>-1.117637044603335</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.083536130604003</v>
+        <v>-1.176647814539614</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.9943831747684655</v>
+        <v>-1.131675784278393</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.8092263651170555</v>
+        <v>-0.9468362931395191</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.6531954887218063</v>
+        <v>-0.7910889624389768</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.152210943234216</v>
+        <v>-1.289705229010742</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.8074084766887566</v>
+        <v>-0.870766398114398</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.8648211421674716</v>
+        <v>-0.9278305252181553</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.091478381963448</v>
+        <v>-1.18521145826741</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.001479</t>
+          <t>X &lt; 0.001472</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.888407120036504</v>
+        <v>-1.982683848125845</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.616189071001372</v>
+        <v>-1.77396469033954</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.192292403638341</v>
+        <v>-2.34850886119591</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.977487183297427</v>
+        <v>-2.132986756613342</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.180234395741948</v>
+        <v>-2.370315841549584</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.574421141604667</v>
+        <v>-1.7008851182729</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.248205023512675</v>
+        <v>-2.373874432029815</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.171304475579454</v>
+        <v>-2.296753720781254</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.837980069421114</v>
+        <v>-1.963581392921306</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.127201740284953</v>
+        <v>-2.252006682286535</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.23770456425364</v>
+        <v>-2.327237795447338</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.067792694797177</v>
+        <v>-2.120787640480529</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.000973529500904</v>
+        <v>-2.051185625067831</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.800202602373176</v>
+        <v>-1.849670497596378</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.586592057312458</v>
+        <v>-1.671800933440601</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.596967661812862</v>
+        <v>-1.720500828217872</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.822475691749119</v>
+        <v>-1.945956449016784</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.954599669434408</v>
+        <v>-2.013670522021705</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.314621115208055</v>
+        <v>-1.374006728540365</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.347920696324955</v>
+        <v>-1.407587381047506</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.724652021901186</v>
+        <v>-1.783747658537038</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.892154173484982</v>
+        <v>-1.951224016247608</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.773643864049902</v>
+        <v>-1.833097568796092</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.84958520331837</v>
+        <v>-1.871556494632351</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.003289</t>
+          <t>X &lt; 0.003282</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1813</v>
+        <v>1817</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.358045111472869</v>
+        <v>-1.384185884503196</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.337541195204281</v>
+        <v>-1.364089635394407</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.493732790918791</v>
+        <v>-1.521427391950496</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.304712095054334</v>
+        <v>-1.333568657815427</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.749251088924566</v>
+        <v>-1.80298690784366</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.204283847833757</v>
+        <v>-1.259063578591991</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.564281411259103</v>
+        <v>-1.619110267016929</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.593629557548731</v>
+        <v>-1.648725500152324</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.631041414206599</v>
+        <v>-1.686060352156133</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.881481557085536</v>
+        <v>-1.936791310235648</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.045238390736905</v>
+        <v>-2.069445599960417</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.129370629370619</v>
+        <v>-2.153603370669167</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.126668865401626</v>
+        <v>-2.151473649741988</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.316688763115934</v>
+        <v>-2.341318469196317</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-2.285631785964547</v>
+        <v>-2.342287615626809</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-2.207953110252035</v>
+        <v>-2.264217517642173</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-2.255601124874552</v>
+        <v>-2.311947440007778</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-2.548920119629763</v>
+        <v>-2.604779549936104</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.081295720812946</v>
+        <v>-2.138007995981837</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.027724270775998</v>
+        <v>-2.084410645413271</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.208949307676363</v>
+        <v>-2.265846205151725</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.418397888882986</v>
+        <v>-2.474961865525955</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-2.497770595843107</v>
+        <v>-2.553925465539251</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.431835702512394</v>
+        <v>-2.488263107000854</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.0051</t>
+          <t>X &lt; 0.005091</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2124</v>
+        <v>2128</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.135695695457358</v>
+        <v>-1.153631864710448</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.306594217692428</v>
+        <v>-1.324461121084113</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.416363351847231</v>
+        <v>-1.435048265605701</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.125477264838594</v>
+        <v>-1.145218954184756</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.325074015129637</v>
+        <v>-1.362247722947174</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.112137699757035</v>
+        <v>-1.149605796062346</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.532258031638278</v>
+        <v>-1.569514472740281</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.738111039787633</v>
+        <v>-1.775208261020481</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.483572905757292</v>
+        <v>-1.521145076709914</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.763550866724813</v>
+        <v>-1.801174221870248</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.883968817613081</v>
+        <v>-1.921203400041065</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.043228307273253</v>
+        <v>-2.080391239541733</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.829974260035762</v>
+        <v>-1.868358678809635</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.118142745115179</v>
+        <v>-2.156174457483161</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.953184122026947</v>
+        <v>-1.992020251022275</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.893686471197348</v>
+        <v>-1.932243786176365</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.625318690274895</v>
+        <v>-1.66450403641683</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-2.031688085312808</v>
+        <v>-2.070216759886442</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.929352391205221</v>
+        <v>-1.967950208755539</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-2.232142857142861</v>
+        <v>-2.270070340053557</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-2.513404922397108</v>
+        <v>-2.551220146086429</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-2.515321974518272</v>
+        <v>-2.553217730199059</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-2.401733239334902</v>
+        <v>-2.43967730986413</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.215283972643476</v>
+        <v>-2.253662778441431</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.00691</t>
+          <t>X &lt; 0.006901</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.166987284266895</v>
+        <v>-1.217221858849484</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.909786316806219</v>
+        <v>-0.9193891929553786</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.063032472200554</v>
+        <v>-1.072020457755286</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.8566682486948309</v>
+        <v>-0.8655855610059149</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.362686860811984</v>
+        <v>-1.382828089277702</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.275536392567489</v>
+        <v>-1.295829429970709</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.494636541999071</v>
+        <v>-1.47366639812536</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.464270858220928</v>
+        <v>-1.443228454172363</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.563479518846954</v>
+        <v>-1.542369652747574</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.700740739328573</v>
+        <v>-1.720133356355333</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.648884994418033</v>
+        <v>-1.709330615406856</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.659264159264154</v>
+        <v>-1.719637457630675</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.285815965022863</v>
+        <v>-1.34613883590999</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.401448167088844</v>
+        <v>-1.461632649751451</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.339561952049962</v>
+        <v>-1.399602121873478</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.048523810572199</v>
+        <v>-1.109041231992052</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.076548335234975</v>
+        <v>-1.096029030823686</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.362731818979178</v>
+        <v>-1.381957681701529</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.24582202970668</v>
+        <v>-1.224200688496204</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.486750205423171</v>
+        <v>-1.506046026828237</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.636243976609961</v>
+        <v>-1.655245307076491</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.976063359377413</v>
+        <v>-1.994775320054821</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.883098932465302</v>
+        <v>-1.860896853183569</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.852934806151183</v>
+        <v>-1.871848868666994</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.00872</t>
+          <t>X &lt; 0.00871</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2672</v>
+        <v>2675</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.021060181260999</v>
+        <v>-1.009268166063549</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.8912568313082616</v>
+        <v>-0.8795912829349106</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.5288339979235204</v>
+        <v>-0.5175005275783562</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.5907253187739698</v>
+        <v>-0.5792871472313976</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.121148554047409</v>
+        <v>-1.117175871511023</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.247959066717698</v>
+        <v>-1.243857954414288</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.219377472180817</v>
+        <v>-1.215274854013288</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.328328552026171</v>
+        <v>-1.324094959079794</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.228731360060763</v>
+        <v>-1.224614659530786</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.497681413710993</v>
+        <v>-1.493231533204352</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.313963876733716</v>
+        <v>-1.309735961594406</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.236673162902669</v>
+        <v>-1.232522129357363</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.9981779119651151</v>
+        <v>-0.9942436982531717</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.8622432673932465</v>
+        <v>-0.8584545605398404</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.8279208789066743</v>
+        <v>-0.8614013283016533</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.9196868632334159</v>
+        <v>-0.9531110584036426</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.8079353155066187</v>
+        <v>-0.8414962841539335</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.07764418035957</v>
+        <v>-1.07361706338633</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.063724781798989</v>
+        <v>-1.059727608675772</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.079035874439462</v>
+        <v>-1.075034528897788</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.039695736100761</v>
+        <v>-1.035717110944958</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.243220535695166</v>
+        <v>-1.239014493094949</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.133521712299846</v>
+        <v>-1.129455664299037</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.262387505690377</v>
+        <v>-1.258177570093451</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.01053</t>
+          <t>X &lt; 0.01052</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2849</v>
+        <v>2853</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.6796924363914627</v>
+        <v>-0.6853533721245952</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3694501771001057</v>
+        <v>-0.3756239117817799</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3618893705439774</v>
+        <v>-0.3684098362477073</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3245195230491049</v>
+        <v>-0.3312610944218974</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.7749224073846506</v>
+        <v>-0.7868999876217231</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.9519876032110375</v>
+        <v>-0.9636831963466435</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.7634479752279191</v>
+        <v>-0.7755929471114342</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9525260713480392</v>
+        <v>-0.9644799662794767</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.8563871744203979</v>
+        <v>-0.8684735718720731</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.9468504533673254</v>
+        <v>-0.9589980303844712</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.071800136098382</v>
+        <v>-1.083717867685529</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.9815202274132702</v>
+        <v>-0.9936368235315669</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.7573583513542772</v>
+        <v>-0.7700572483390715</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.7483910968074738</v>
+        <v>-0.7611623893789954</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.7569630539826093</v>
+        <v>-0.7698840314023627</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.806153201475702</v>
+        <v>-0.8188755785749819</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.7095981082832949</v>
+        <v>-0.7224952255555621</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.8990075890251035</v>
+        <v>-0.9116727188551934</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.18783216282435</v>
+        <v>-1.200051183245201</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.120531019978962</v>
+        <v>-1.132808974170999</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.047232667062467</v>
+        <v>-1.059748381406834</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.242840136685466</v>
+        <v>-1.255107997664915</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.228152227982996</v>
+        <v>-1.240384861303632</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.35376319586846</v>
+        <v>-1.36584583861552</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.01234</t>
+          <t>X &lt; 0.01233</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2977</v>
+        <v>2981</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.5741214057507946</v>
+        <v>-0.5782638910617948</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4581131924858184</v>
+        <v>-0.4624703986282697</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.3122395459222247</v>
+        <v>-0.3170406956562175</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.04000124155162865</v>
+        <v>-0.0452907489992711</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.5534276389067401</v>
+        <v>-0.5623874528027812</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.6480745007434336</v>
+        <v>-0.6568817535343499</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.500535548839899</v>
+        <v>-0.509678156066073</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.6933523973477946</v>
+        <v>-0.7022914387255454</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.5326187640598121</v>
+        <v>-0.541771115970846</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.6856523754918342</v>
+        <v>-0.6947394387193668</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.826865354658274</v>
+        <v>-0.8357224583975409</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.8526894651016406</v>
+        <v>-0.8615660055846277</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.7866597059568292</v>
+        <v>-0.795824284457737</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.7875721908640045</v>
+        <v>-0.7967797782787329</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.6900775603540765</v>
+        <v>-0.6995353966566782</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.678118324019934</v>
+        <v>-0.6874955645447471</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.5914141054596485</v>
+        <v>-0.6009367305030864</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.643068064821108</v>
+        <v>-0.652545871761113</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.7424596239235868</v>
+        <v>-0.7517730745813438</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.7369590741362018</v>
+        <v>-0.7462536330036045</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.6900124895348725</v>
+        <v>-0.6994702218856546</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.7796539540665535</v>
+        <v>-0.7890108552472626</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.9551089751228332</v>
+        <v>-0.9641890271066771</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.9777200250654658</v>
+        <v>-0.9867889938457566</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.01415</t>
+          <t>X &lt; 0.01414</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3072</v>
+        <v>3075</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.6208096125359361</v>
+        <v>-0.6389103800555915</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.8095554853595672</v>
+        <v>-0.8274159686109712</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.8094888167476597</v>
+        <v>-0.8270796533192311</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6000481362255172</v>
+        <v>-0.6177116813863677</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.044398237470382</v>
+        <v>-1.064843819965034</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.033452503995882</v>
+        <v>-1.021622365961797</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.9143447145977603</v>
+        <v>-0.9024799117859246</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.109933227575148</v>
+        <v>-1.097823388231397</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.8882155482280325</v>
+        <v>-0.8763272231428658</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.092879674151703</v>
+        <v>-1.080642132915095</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.253842366090211</v>
+        <v>-1.241499470106625</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.190330421847932</v>
+        <v>-1.177993787459002</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.128659123238897</v>
+        <v>-1.116164374774186</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.136477581669546</v>
+        <v>-1.12393086958614</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-1.029962945641209</v>
+        <v>-1.017391284636069</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.9676612768794683</v>
+        <v>-0.9552629768328771</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.8878636333955825</v>
+        <v>-0.8755154694259062</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.8762826180714143</v>
+        <v>-0.8639238140658918</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.9985078840182311</v>
+        <v>-0.9860699230777925</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.9224642392717826</v>
+        <v>-0.9101346381157782</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.8938101650955161</v>
+        <v>-0.8814021891287567</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.9830949571584569</v>
+        <v>-0.9705835871324453</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-1.177239068090103</v>
+        <v>-1.164589522842249</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-1.234123720760238</v>
+        <v>-1.221402249069214</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.01596</t>
+          <t>X &lt; 0.01595</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3150</v>
+        <v>3154</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5067718942474784</v>
+        <v>-0.508961686928977</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.6045049910130302</v>
+        <v>-0.6066062795399674</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7343963122642947</v>
+        <v>-0.7364776064820688</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.6738317071381417</v>
+        <v>-0.6760613784911769</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.9269244776495498</v>
+        <v>-0.9313442759985051</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.9116029403987511</v>
+        <v>-0.9160265630484119</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.8144250898416985</v>
+        <v>-0.8190508083693331</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.012026059772168</v>
+        <v>-1.016433130364604</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.921100740219515</v>
+        <v>-0.9256215091110036</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.9817788501539226</v>
+        <v>-0.9863028187635479</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.131971319635838</v>
+        <v>-1.136281475600455</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.203374424437044</v>
+        <v>-1.207625108747848</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.234247801669852</v>
+        <v>-1.238574197865582</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.247370557626304</v>
+        <v>-1.25170544867381</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-1.223102097992737</v>
+        <v>-1.227536310229901</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-1.147702894539833</v>
+        <v>-1.152176413087233</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.9782199694446163</v>
+        <v>-0.9829244515020363</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.8428057418222039</v>
+        <v>-0.8476953168247334</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.8932640808819272</v>
+        <v>-0.8980715017460312</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.7827362079898563</v>
+        <v>-0.7876682212498807</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.7047528986903089</v>
+        <v>-0.7098412345126022</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.7936478504273694</v>
+        <v>-0.7986344638072964</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-1.007860145825838</v>
+        <v>-1.012551042835497</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-1.065162907268167</v>
+        <v>-1.069791956809027</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.01777</t>
+          <t>X &lt; 0.01776</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3195</v>
+        <v>3199</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.5044508028918742</v>
+        <v>-0.5061481686771572</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.5433348439263597</v>
+        <v>-0.5450123004809413</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.6604401705509133</v>
+        <v>-0.66209016578172</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.6728995623711498</v>
+        <v>-0.6745932523897196</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.8964487838807926</v>
+        <v>-0.8999262968052761</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.8475874352067763</v>
+        <v>-0.8511129048776169</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.7003124376112098</v>
+        <v>-0.7040863685062035</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.8367264884352394</v>
+        <v>-0.8403558899055952</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.7775918595002054</v>
+        <v>-0.7812939645231154</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.9105506081559653</v>
+        <v>-0.9141527466134818</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.9924213642997159</v>
+        <v>-0.9959016794382052</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.035513441968071</v>
+        <v>-1.038965300087128</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.050493164139745</v>
+        <v>-1.054020596117489</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.097683557488068</v>
+        <v>-1.101172753610669</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-1.020541907916943</v>
+        <v>-1.024183642263409</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.9377785776243144</v>
+        <v>-0.9414774498965315</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.8037269528254853</v>
+        <v>-0.8076066207106223</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.6716377489302516</v>
+        <v>-0.6756935000432023</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.6870437956204327</v>
+        <v>-0.6910653022304771</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.6066348859018476</v>
+        <v>-0.6107441572242536</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.5686069130629932</v>
+        <v>-0.5728109455955348</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.6259978168457607</v>
+        <v>-0.6301391148015867</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.7706944408367846</v>
+        <v>-0.774635036496349</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.890783296268836</v>
+        <v>-0.8945826382660513</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.01958</t>
+          <t>X &lt; 0.01957</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3243</v>
+        <v>3247</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.3673241001782372</v>
+        <v>-0.3686758596093327</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.4717777779755252</v>
+        <v>-0.4730237282394114</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.6389483648734142</v>
+        <v>-0.6400811493072638</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6923647093201382</v>
+        <v>-0.6934779107728062</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.8873492625881028</v>
+        <v>-0.8898216230416125</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.8057839408354965</v>
+        <v>-0.808346228420568</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.6413693637088969</v>
+        <v>-0.6441836760859516</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.8412273560706538</v>
+        <v>-0.8438161486433486</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.7823536823030111</v>
+        <v>-0.7850138946113248</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.8326495023755101</v>
+        <v>-0.8352987579158793</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.8478197234387181</v>
+        <v>-0.8504349098853794</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.8329036554843015</v>
+        <v>-0.8355566621098731</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.8949190082757212</v>
+        <v>-0.8975688999332547</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.9138906539735885</v>
+        <v>-0.9165331639089587</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.9398079545099876</v>
+        <v>-0.9424622700183392</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.8802156557519112</v>
+        <v>-0.8829074151654766</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.780875850149279</v>
+        <v>-0.7837001546154454</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.6522820708945076</v>
+        <v>-0.655273132044961</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.6642605443889025</v>
+        <v>-0.6672251761887651</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.582268247613186</v>
+        <v>-0.5853238945955823</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.552827642516128</v>
+        <v>-0.5559560952616138</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.548855002390944</v>
+        <v>-0.551995252210169</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.6873211119685436</v>
+        <v>-0.6902754305850181</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.7450595344358462</v>
+        <v>-0.747949581065491</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.02139</t>
+          <t>X &lt; 0.02138</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3278</v>
+        <v>3281</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.3266509422548936</v>
+        <v>-0.341815636434383</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4941454052436072</v>
+        <v>-0.4788028400288269</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.5232623132475567</v>
+        <v>-0.5075254562700664</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.5836518256307528</v>
+        <v>-0.5676754413279141</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.7500805008968214</v>
+        <v>-0.7351147255300603</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.6976919861965385</v>
+        <v>-0.7131296631891928</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.603898572307159</v>
+        <v>-0.5889102780669546</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.804581371004403</v>
+        <v>-0.7893363240719182</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.6851461637782279</v>
+        <v>-0.6700165435312115</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.7431050088069284</v>
+        <v>-0.7277230912915655</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.7551688559473746</v>
+        <v>-0.7398415648557517</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.743352392288557</v>
+        <v>-0.7279614181420513</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.7862425106732189</v>
+        <v>-0.7705239290344394</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.7769218219091556</v>
+        <v>-0.7611517760709461</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.8703835456324924</v>
+        <v>-0.8543574478709672</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.8659309925563718</v>
+        <v>-0.8500557413600873</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.7995153537202881</v>
+        <v>-0.783662768474926</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.7343179938750239</v>
+        <v>-0.7184943602370311</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.6220498876094638</v>
+        <v>-0.6063796194678304</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.599862888482626</v>
+        <v>-0.5842564323886634</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.5155792569101791</v>
+        <v>-0.4999081237446958</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.5429359524454469</v>
+        <v>-0.5272166633859499</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.6464922225256231</v>
+        <v>-0.6307441163257153</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.7349189528631399</v>
+        <v>-0.7190668020634163</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.0232</t>
+          <t>X &lt; 0.02319</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3307</v>
+        <v>3310</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2807280123574003</v>
+        <v>-0.2955125799786202</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.3595522523266368</v>
+        <v>-0.3741833355512867</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.4309685383274129</v>
+        <v>-0.4451650262585929</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.4970257442629418</v>
+        <v>-0.5109813646399033</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.6651621062703228</v>
+        <v>-0.679870180348594</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.6115725614210064</v>
+        <v>-0.6263828051669478</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.5553985841765154</v>
+        <v>-0.570063067517907</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.6965598010409764</v>
+        <v>-0.7110293809170827</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.6680793299839607</v>
+        <v>-0.6825904540356333</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.7021728794910302</v>
+        <v>-0.7164563395307866</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.6816020271005385</v>
+        <v>-0.695980641530781</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.67230524823173</v>
+        <v>-0.686624394886735</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.6342114560554819</v>
+        <v>-0.6482763517591579</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.6570094336886285</v>
+        <v>-0.671000835023257</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.7252234805591016</v>
+        <v>-0.7389859705793924</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.775892261581042</v>
+        <v>-0.7897693024275299</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.801729106729745</v>
+        <v>-0.8155526053177908</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.7078379516099034</v>
+        <v>-0.721723809289351</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.6248457279875836</v>
+        <v>-0.6388681052877345</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.5408109332527857</v>
+        <v>-0.5549632442260801</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.4922185358861739</v>
+        <v>-0.5062776722659521</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.5199940865807235</v>
+        <v>-0.534013130620913</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.5899969849782636</v>
+        <v>-0.6040294792628913</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.6178193695103644</v>
+        <v>-0.6318117005957546</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.02501</t>
+          <t>X &lt; 0.025</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3332</v>
+        <v>3336</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.2016921956166655</v>
+        <v>-0.2023237433813634</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.3122188047123586</v>
+        <v>-0.3127293316745678</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.423646952032712</v>
+        <v>-0.424068936386206</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.4050341344285968</v>
+        <v>-0.4055004367513462</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.5149300738652727</v>
+        <v>-0.5160387195688116</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.4901496010349646</v>
+        <v>-0.4912829244275301</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.5297070599720399</v>
+        <v>-0.5308176094087571</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.642017961481713</v>
+        <v>-0.6430038297163705</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.583546324697565</v>
+        <v>-0.5846015246845013</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.5633688083129087</v>
+        <v>-0.5644725760377867</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.5707550517552136</v>
+        <v>-0.571842453937542</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.5635811556864141</v>
+        <v>-0.5646865085822554</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.593975518213739</v>
+        <v>-0.595079823379173</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.5883245834881734</v>
+        <v>-0.5894432838382428</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.6310071263041621</v>
+        <v>-0.6320958497864453</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.7067545189667328</v>
+        <v>-0.7077352472089231</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.7633302929810739</v>
+        <v>-0.7642482676077407</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.670917108342536</v>
+        <v>-0.6719497237212408</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.6168834719764362</v>
+        <v>-0.6179749829984118</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.5920263788968825</v>
+        <v>-0.5931427693038671</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.4879155514267381</v>
+        <v>-0.489174239800505</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.4860570843166272</v>
+        <v>-0.4873212528729525</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.5534637064992722</v>
+        <v>-0.5546395315517927</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.6116481680391459</v>
+        <v>-0.6127574575853316</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/ma/ma_ratio_20.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/ma/ma_ratio_20.xlsx
@@ -618,493 +618,493 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.02658</t>
+          <t>X ≈ -0.02653</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-6.537093382248081</v>
+        <v>-3.51849710007982</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.871940871370519</v>
+        <v>-3.763603426178776</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-19.99419326219503</v>
+        <v>-23.64511224666027</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-20.7090545763041</v>
+        <v>-24.24091098237267</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.351618587773139</v>
+        <v>-12.09302229851561</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-9.1680853847908</v>
+        <v>-11.94036116285948</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-21.64343261380758</v>
+        <v>-18.95323480925185</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-21.92684667594756</v>
+        <v>-19.2624322097089</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-16.03617285663318</v>
+        <v>-12.91844861540898</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-10.95260498014934</v>
+        <v>-7.490746305074211</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-4.823483390994369</v>
+        <v>-0.9959323725646243</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.7580193771025989</v>
+        <v>4.955405797690517</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.3611175002793274</v>
+        <v>3.845749652634957</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.446576561352032</v>
+        <v>-2.632210768501288</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-1.237857999850597</v>
+        <v>2.920454057937128</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>5.222755701355368</v>
+        <v>3.480935352986791</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.7788551947713316</v>
+        <v>-2.858437372622312</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>4.988007011499775</v>
+        <v>3.246745986360679</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>5.205042673124289</v>
+        <v>3.461886923404691</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.4819253288073995</v>
+        <v>-2.565337792256415</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>10.73010125830977</v>
+        <v>9.355872777790808</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>4.778779822711378</v>
+        <v>3.037209648604922</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>5.054638526225375</v>
+        <v>3.281642499831939</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.9019378779562572</v>
+        <v>-3.129530298637285</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.02476</t>
+          <t>X ≈ -0.02473</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>20</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6.314984761621069</v>
+        <v>6.41304418065247</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>15.91776132025109</v>
+        <v>16.10516450118561</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>14.49356070414516</v>
+        <v>14.86320827803146</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.84932824935548</v>
+        <v>4.338697235258337</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>13.45876813732808</v>
+        <v>14.00851942012407</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.676272810416421</v>
+        <v>9.195874670919956</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.937016484767845</v>
+        <v>3.433314025728002</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.660959270970729</v>
+        <v>3.130773085863424</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.702954242896155</v>
+        <v>3.259174522014632</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>11.89213624760062</v>
+        <v>12.42571229074927</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>12.1685865268223</v>
+        <v>12.70054699030604</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.89394069585687</v>
+        <v>12.42823456219436</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>20.74498051132316</v>
+        <v>21.28789215739729</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>20.53067691804371</v>
+        <v>21.04663599347902</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>19.88102840895861</v>
+        <v>20.3731179031041</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>20.47972492404077</v>
+        <v>20.93882820349128</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>20.35279089176045</v>
+        <v>20.84171911329501</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>15.26333093222749</v>
+        <v>15.72416090626564</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>10.4910559589531</v>
+        <v>10.95056704261573</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>15.67495817016716</v>
+        <v>16.16215947789861</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>10.14228980026336</v>
+        <v>10.60465621561337</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>15.06662695531926</v>
+        <v>15.5296740129403</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>10.34713385726043</v>
+        <v>10.77937639966483</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>10.27453271028038</v>
+        <v>10.62046970136158</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.02295</t>
+          <t>X ≈ -0.02292</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.136259094497454</v>
+        <v>7.014189628060564</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-5.622090209804412</v>
+        <v>-5.268816071986699</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.991544657345905</v>
+        <v>-3.505932802469879</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.617436210369746</v>
+        <v>-1.083311147290793</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.149912517469787</v>
+        <v>1.654308748019773</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.189206780589771</v>
+        <v>7.838857314605541</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>14.75029696425552</v>
+        <v>16.09490260450417</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>14.47787219044788</v>
+        <v>15.79622852350455</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.302040629165234</v>
+        <v>6.878806814210549</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.423332711826802</v>
+        <v>3.070733263900365</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>10.92277247567917</v>
+        <v>9.379538105625898</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>13.76137537045763</v>
+        <v>12.12558248912501</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>15.76064609884873</v>
+        <v>14.0382612095327</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>21.77585668936898</v>
+        <v>19.83716703987802</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>21.12672310970238</v>
+        <v>19.16342114783539</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>9.256402767846964</v>
+        <v>7.637017093950931</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>18.48110734256311</v>
+        <v>16.60759717510424</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>9.024340054935067</v>
+        <v>7.405536794127414</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>6.122481144834758</v>
+        <v>4.596320093806064</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>12.55347242913213</v>
+        <v>10.86525444592975</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>18.2596854536475</v>
+        <v>16.35683573923046</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>18.18956770436241</v>
+        <v>16.28663997337708</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>21.59363997184961</v>
+        <v>19.56453368375481</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>21.52453271028038</v>
+        <v>19.40834848924219</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.02115</t>
+          <t>X ≈ -0.02112</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.890448348317371</v>
+        <v>-3.518460909674126</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.676893632572025</v>
+        <v>-1.279875340770701</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.989643701435547</v>
+        <v>2.440998398217481</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.928526028486615</v>
+        <v>9.307464871439379</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-7.703314926479834</v>
+        <v>-5.877659728699463</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.967308891061933</v>
+        <v>-3.237152343455897</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.6351215123971912</v>
+        <v>0.9449867240459824</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.639293575720458</v>
+        <v>3.129571311114304</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.8709324617602618</v>
+        <v>0.7699280971616957</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.640543902300216</v>
+        <v>-0.02229835238734523</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-9.029898065859861</v>
+        <v>-7.221574999536443</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.201835141303825</v>
+        <v>-2.518336826018171</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-10.43334293588364</v>
+        <v>-8.613432023720556</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-18.32577183506206</v>
+        <v>-16.34079575074593</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-16.43012285730725</v>
+        <v>-14.53235272960855</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-13.28441352820221</v>
+        <v>-11.48302477130224</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-10.86319600073389</v>
+        <v>-9.095430032096687</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-18.64895998643354</v>
+        <v>-16.71691659580813</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-15.87891524474914</v>
+        <v>-14.01158284845245</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-13.13619561601972</v>
+        <v>-11.30473606965644</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-11.12043591507496</v>
+        <v>-9.377326765589203</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-6.074493993913578</v>
+        <v>-4.458396060279703</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-5.801867262285207</v>
+        <v>-4.216163907504388</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-5.879313443565195</v>
+        <v>-4.379530298637277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.01933</t>
+          <t>X ≈ -0.01931</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7.137743785876715</v>
+        <v>7.012877299226176</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>23.99119723200832</v>
+        <v>24.82970058196781</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>22.56919148150735</v>
+        <v>23.59050208517784</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>24.97357635835799</v>
+        <v>23.00889781001831</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>12.21745535598053</v>
+        <v>7.679419587320858</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>21.72588166282999</v>
+        <v>16.87799354232565</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>20.9647732734122</v>
+        <v>16.09211167774477</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>17.5848961142356</v>
+        <v>12.77820085376185</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>17.63203446196046</v>
+        <v>12.91022354284565</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>16.8682602699062</v>
+        <v>12.12183976773375</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>17.14645850732307</v>
+        <v>12.39678899084576</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>19.9864958327572</v>
+        <v>15.14326567360472</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>18.87358546198477</v>
+        <v>14.03705458170609</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>18.65907618462442</v>
+        <v>13.7939455080307</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>24.24158351577913</v>
+        <v>19.1621897856644</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>15.4904116090413</v>
+        <v>10.65952606249135</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>15.36191521499676</v>
+        <v>10.55922009994502</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>18.38163180049324</v>
+        <v>13.45479365477486</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>18.60292690252761</v>
+        <v>13.67316039351402</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>21.91643584574346</v>
+        <v>16.91806890387807</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>18.25925690062225</v>
+        <v>13.32897152718326</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>21.31229090390757</v>
+        <v>16.28634641118682</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>24.71746551737603</v>
+        <v>22.59371453017123</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>18.39953271027967</v>
+        <v>16.37804545893778</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.01752</t>
+          <t>X ≈ -0.01751</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.314649947866009</v>
+        <v>5.114971347273247</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-8.860028910568069</v>
+        <v>-10.24090366462307</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-16.15282557639097</v>
+        <v>-17.96954875495923</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-7.411933693529186</v>
+        <v>-7.7624456821558</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-12.49458324829797</v>
+        <v>-12.35978965862046</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-5.197923104050965</v>
+        <v>-5.723390799063864</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-8.35455107751509</v>
+        <v>-10.84078063495308</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-11.00999191416077</v>
+        <v>-13.31051961288036</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-10.97217120616747</v>
+        <v>-13.1865814270584</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-7.022290146902122</v>
+        <v>-9.654245399048222</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-11.48833790582571</v>
+        <v>-13.71614578677632</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-11.77032753939627</v>
+        <v>-13.9969324375429</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-5.800178015300503</v>
+        <v>-8.612882101655501</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-10.77487871667205</v>
+        <v>-13.19714435272486</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-11.45182332640082</v>
+        <v>-13.88109746547026</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-13.22416595544323</v>
+        <v>-13.32544398245501</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-10.99014246494055</v>
+        <v>-11.26407973884948</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-6.349185569948965</v>
+        <v>-4.890574709658601</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-3.75132824095067</v>
+        <v>-2.507393598252889</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.180123701325698</v>
+        <v>-0.1228906572928139</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>3.023286032670534</v>
+        <v>3.654017623532155</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>4.358436818182163</v>
+        <v>3.580006354307777</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>4.634361966863693</v>
+        <v>3.824751817750887</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>2.179294615042281</v>
+        <v>1.490034918755015</v>
       </c>
     </row>
     <row r="12">
@@ -1114,161 +1114,161 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-6.373596312313246</v>
+        <v>-6.526153268683885</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.007696810572781</v>
+        <v>-3.762549741847501</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-11.66014295789398</v>
+        <v>-11.02937521570686</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-5.536366540990883</v>
+        <v>-7.106211454299455</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.499546742784993</v>
+        <v>-4.3691420610036</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.561880487505633</v>
+        <v>3.316244399243864</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.022987657667656</v>
+        <v>1.019919212958918</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-4.83951983553532</v>
+        <v>-5.312468460146938</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-8.233572049883229</v>
+        <v>-8.201849762322155</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-10.73685799520893</v>
+        <v>-10.50528322778013</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-12.18100213218419</v>
+        <v>-13.2549332362787</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.589062881431786</v>
+        <v>-7.498441916934418</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.290741773791915</v>
+        <v>-5.592240559013547</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.235891898462171</v>
+        <v>-5.841236496821402</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-7.626937636337594</v>
+        <v>-6.522892835889678</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-8.747247625888896</v>
+        <v>-7.476338666117819</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-10.60796233300381</v>
+        <v>-9.094176566188914</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-8.997004114864872</v>
+        <v>-7.717461520755627</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-3.611663166003609</v>
+        <v>-4.48036248378498</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-5.143409224145316</v>
+        <v>-4.267754878920535</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.972211536093276</v>
+        <v>-3.322246113818103</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-7.494684037702001</v>
+        <v>-6.426813539912693</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-6.199632572316936</v>
+        <v>-7.699912619885836</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-4.55305349661618</v>
+        <v>-3.31892423803157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.01391</t>
+          <t>X ≈ -0.0139</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-5.688208015212965</v>
+        <v>-4.216080496760675</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-8.714799087509256</v>
+        <v>-7.078695507235558</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.443102732089365</v>
+        <v>-1.809593309036721</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.408427858896466</v>
+        <v>-2.984597608123543</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-7.776026401997029</v>
+        <v>-8.488779415084323</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.902246581940908</v>
+        <v>-7.029948157294683</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-7.014744367502523</v>
+        <v>-9.130770955156471</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-7.292961049573762</v>
+        <v>-9.436175244330158</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.216750655792453</v>
+        <v>-6.692313963326832</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.333436895627052</v>
+        <v>-7.486706068048065</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.022508637780433</v>
+        <v>-3.287109138725079</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.64895589646386</v>
+        <v>-4.875923638094733</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.075152450156487</v>
+        <v>-2.055541781834123</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.643461824588478</v>
+        <v>-3.614871138368152</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-4.648715796724588</v>
+        <v>-5.607664370436751</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-2.70812344121034</v>
+        <v>-3.737303926398461</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.493371731341576</v>
+        <v>-2.52943890163457</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-4.297572892609665</v>
+        <v>-3.976167497267355</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-4.083446248739008</v>
+        <v>-2.449883414444329</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-2.547580135998054</v>
+        <v>-2.236699183423106</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-3.090660616712483</v>
+        <v>-2.804276533230457</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.815591568828012</v>
+        <v>-1.565405374043436</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-5.593979377590081</v>
+        <v>-3.953033771920197</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-2.968710532962866</v>
+        <v>-2.800582930216237</v>
       </c>
     </row>
     <row r="14">
@@ -1281,76 +1281,76 @@
         <v>91</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.075333107169996</v>
+        <v>-4.142186488583739</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-6.688183350717289</v>
+        <v>-5.98789375080505</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-8.118657973134447</v>
+        <v>-8.827484727433124</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-6.643156040491363</v>
+        <v>-7.234502075246013</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-6.976096396318873</v>
+        <v>-6.416977089140559</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-6.792147980866631</v>
+        <v>-5.173797865648112</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-5.372958249876255</v>
+        <v>-4.872621382716581</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-6.744294863666923</v>
+        <v>-5.176612017971955</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-9.987279686545534</v>
+        <v>-9.423693614413132</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-6.382318765238345</v>
+        <v>-6.937843007459627</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-9.395984074444279</v>
+        <v>-9.951362271220169</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-14.05897547501202</v>
+        <v>-13.51509238288287</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-12.99272986398361</v>
+        <v>-12.44136614410927</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-11.02537016187197</v>
+        <v>-10.50227433212601</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-6.20369281387817</v>
+        <v>-5.70760838426142</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-5.612509673298234</v>
+        <v>-5.149880999694481</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-3.553888606660664</v>
+        <v>-3.062807738374175</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.3673742865490794</v>
+        <v>0.09348835038307612</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.347562306878956</v>
+        <v>-1.886694570482106</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-4.35796888136688</v>
+        <v>-3.868213581133205</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-3.803170586321308</v>
+        <v>-3.338572498043014</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-4.977542850894999</v>
+        <v>-4.51303119473716</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-3.604665940617735</v>
+        <v>-3.17243305761712</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-3.681511245763581</v>
+        <v>-3.335574254681497</v>
       </c>
     </row>
     <row r="15">
@@ -1360,1637 +1360,1637 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.144391519734612</v>
+        <v>-4.558553222728392</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-7.617948102059117</v>
+        <v>-8.819501429724838</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.718277032223597</v>
+        <v>-3.055401832847977</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.382530370284883</v>
+        <v>-1.642058172860118</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.715284783736379</v>
+        <v>-1.353029503318545</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.57862660442445</v>
+        <v>-4.212117711883032</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.487390563462746</v>
+        <v>-7.011323893569177</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.527934476694149</v>
+        <v>-3.298232793604377</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.704684267191986</v>
+        <v>1.853194207214194</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8876639278423966</v>
+        <v>0.05633298148875099</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.9360244974199574</v>
+        <v>-0.6778224605313952</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.361940016771115</v>
+        <v>-3.972385050141703</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.532985982580783</v>
+        <v>-6.091449878716084</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-5.705916633623616</v>
+        <v>-5.334362262676841</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-6.364305944367764</v>
+        <v>-6.016210134970436</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-7.874207544200424</v>
+        <v>-7.473357012915649</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-3.80754536604573</v>
+        <v>-3.549485529863048</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.7600836907437696</v>
+        <v>-0.6597013258199738</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.5067018435634552</v>
+        <v>0.5623272683342506</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.745480159947533</v>
+        <v>1.785174120299814</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.1515534780419117</v>
+        <v>0.2099057592791027</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>2.180240622801101</v>
+        <v>3.162967520287388</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>3.506831613376519</v>
+        <v>3.407623652089498</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>3.432427447122478</v>
+        <v>4.256833337726583</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.00848</t>
+          <t>X ≈ -0.008487</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-7.448205550951521</v>
+        <v>-6.772409927953355</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-6.838067479355786</v>
+        <v>-6.100029071532077</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2457948365230394</v>
+        <v>0.9207238466193033</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-7.101052289893694</v>
+        <v>-7.031250522534506</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-6.491927892495418</v>
+        <v>-6.388428168877191</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.407305668198902</v>
+        <v>-3.875589984472185</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.34098023517307</v>
+        <v>-0.9849543762170967</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.569705310579209</v>
+        <v>-2.208770971079367</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-5.425759863562824</v>
+        <v>-3.923649043434196</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.359568156157216</v>
+        <v>-1.95334664930806</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.137005343069141</v>
+        <v>-0.7610962646752668</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.46819031715382</v>
+        <v>-0.1158319700242174</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.2502321373680019</v>
+        <v>1.539645147975222</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.02760712207480509</v>
+        <v>1.292737801789464</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>2.215025369400927</v>
+        <v>3.381987863256875</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.9130450131041314</v>
+        <v>2.096261912495088</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-3.024451895023418</v>
+        <v>-1.701645258019532</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.179261116265018</v>
+        <v>-0.9115289853696424</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-4.815681241826987</v>
+        <v>-3.470743119481995</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-3.675454102452093</v>
+        <v>-2.333561620299434</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-6.128875433003266</v>
+        <v>-4.75099110207271</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-5.25200474201246</v>
+        <v>-3.902738941181894</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-5.925546881671437</v>
+        <v>-4.586177889972106</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-8.296895861148201</v>
+        <v>-7.527678446785224</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.006671</t>
+          <t>X ≈ -0.006683</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.687380855469591</v>
+        <v>-4.634176145649995</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.695553812139586</v>
+        <v>-1.142540215208733</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-5.478151109645893</v>
+        <v>-3.883897652759288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.086436942188605</v>
+        <v>-1.485715390275111</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.095623573056059</v>
+        <v>-0.2641054529917639</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.1234032790206641</v>
+        <v>0.6347841998956767</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.460667572379791</v>
+        <v>-1.648135572006659</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.4107906248898558</v>
+        <v>1.037819851991095</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.190990292553245</v>
+        <v>4.156503646811416</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.416178185681098</v>
+        <v>3.365949765060073</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.470437759305476</v>
+        <v>4.386511294144888</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.413545932569882</v>
+        <v>3.363276004583362</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.623900761771772</v>
+        <v>4.49946393479263</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.520674225344138</v>
+        <v>7.249804925342652</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>5.081464243675008</v>
+        <v>5.823273280803853</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>3.340686385843753</v>
+        <v>4.136381356497999</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>3.207107547474962</v>
+        <v>4.033907105819914</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>4.664833959482593</v>
+        <v>5.402457040841668</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4.884777576454603</v>
+        <v>5.618491321418958</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>5.857738639547449</v>
+        <v>6.585077488753868</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>7.339236212430698</v>
+        <v>7.52299089506127</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>6.482140251021598</v>
+        <v>6.69921381819244</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>5.975364963503651</v>
+        <v>6.193725464184048</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>8.243282710280376</v>
+        <v>8.289642633693539</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.004861</t>
+          <t>X ≈ -0.004879</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.610579223191074</v>
+        <v>0.934520087081161</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>7.442043807083628</v>
+        <v>6.618530216990649</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.9968790889662102</v>
+        <v>-2.036718006700909</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.49791116722605</v>
+        <v>-3.366931854174396</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.305500057686345</v>
+        <v>-1.416312687577175</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.86413791320679</v>
+        <v>-0.5240605034856998</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.191953070848655</v>
+        <v>1.652354174805978</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.517100378587557</v>
+        <v>-2.357554246851102</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.9253001866689843</v>
+        <v>-0.7478626679745162</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.721142771141125</v>
+        <v>-0.7977486452124651</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.764268126548835</v>
+        <v>-1.269539051638624</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.8223598943316048</v>
+        <v>-0.06095063302772985</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.04670623184590994</v>
+        <v>0.3136511132804003</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.372380917933313</v>
+        <v>1.552475679704152</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.06342627602118256</v>
+        <v>0.1300414649011969</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.5336100717064838</v>
+        <v>0.6899932391021153</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.948076953996804</v>
+        <v>2.074587570338842</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>4.944212107760691</v>
+        <v>4.919811664699537</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>5.939866106384379</v>
+        <v>5.880578468230482</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>6.585755248613779</v>
+        <v>6.096622178962647</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>5.268015282198142</v>
+        <v>4.787217591163881</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>5.967363119238648</v>
+        <v>5.459618754135867</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>3.916256436372045</v>
+        <v>3.467602917878089</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.290036586249364</v>
+        <v>1.814499552108813</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.003052</t>
+          <t>X ≈ -0.003074</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>168</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7971040041372959</v>
+        <v>1.807151641383399</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.4616537318077434</v>
+        <v>0.9715743451179861</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.762967882947926</v>
+        <v>-1.452126909350078</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.883844880245185</v>
+        <v>-2.040771374141663</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-6.783277153728868</v>
+        <v>-5.856857433620803</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-4.81267168741806</v>
+        <v>-4.525280074020657</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.806503577728968</v>
+        <v>-2.952050596770299</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.06938746304820853</v>
+        <v>0.8828675069342466</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.4820105459582535</v>
+        <v>0.4183230847195318</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.879285906139025</v>
+        <v>-3.330980283445925</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.605854124229438</v>
+        <v>-3.06150517904257</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.29070088122976</v>
+        <v>-3.33943689515138</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.81807672088172</v>
+        <v>-4.452077703877031</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-4.040707587661927</v>
+        <v>-4.702103809675833</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-2.916474976476565</v>
+        <v>-3.604365056542548</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-2.32382002586241</v>
+        <v>-3.046210585767383</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.269242498566371</v>
+        <v>-1.964913780371838</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-4.349614690927048</v>
+        <v>-5.068091468090891</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-4.730658667666532</v>
+        <v>-5.450251712618758</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-5.139050952936607</v>
+        <v>-5.833144395067379</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-7.467311406616915</v>
+        <v>-8.185259934237067</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-6.352681177549833</v>
+        <v>-7.074510217093547</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-7.268682655544097</v>
+        <v>-8.023692119138971</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-7.939753004005333</v>
+        <v>-8.189054108161095</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.001242</t>
+          <t>X ≈ -0.00127</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.199080440207446</v>
+        <v>-0.9631523704270677</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.7665211854859777</v>
+        <v>0.4870512588780898</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6174844419484771</v>
+        <v>0.09498421749775332</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.09868386734159174</v>
+        <v>0.3543736173496441</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.598183539316224</v>
+        <v>3.050371520556112</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.621845863636814</v>
+        <v>1.080441586212807</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.891440728621696</v>
+        <v>-1.826857944581889</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.3035124457938</v>
+        <v>-1.283063064299753</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.69451071133367</v>
+        <v>-1.157173562179693</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.5628938264913899</v>
+        <v>1.024622874953863</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.331025723810541</v>
+        <v>-0.8277100836782267</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.779799776898095</v>
+        <v>-3.229221783981203</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-4.040620822356424</v>
+        <v>-3.06612149526719</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.136353813372573</v>
+        <v>-2.465248702068493</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-2.495604062290518</v>
+        <v>-1.869035057057118</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.466541990281542</v>
+        <v>-0.8849543944379121</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-3.339470907899148</v>
+        <v>-2.693714129402537</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-4.750010755540046</v>
+        <v>-4.10687204505723</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-5.144737342614782</v>
+        <v>-4.747672024921613</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-7.131804576124914</v>
+        <v>-6.669191597998193</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-7.674350744091043</v>
+        <v>-7.238387529282221</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-7.750196705500144</v>
+        <v>-7.317390943858534</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-7.91050460171364</v>
+        <v>-7.504390283176932</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-8.855902072328327</v>
+        <v>-8.952179871286859</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0005674</t>
+          <t>X ≈ 0.000534</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.677403976712746</v>
+        <v>-3.771024528049125</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-3.554736226910677</v>
+        <v>-4.469624445699388</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.259366168255497</v>
+        <v>-2.556313525286122</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.060153411000506</v>
+        <v>-2.696239706588827</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.399832911556345</v>
+        <v>-2.971993204684935</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.580922439105194</v>
+        <v>-3.720055046585983</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-5.278260594922386</v>
+        <v>-4.707412163102092</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.558027650878735</v>
+        <v>-4.749901359122092</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.598540150253605</v>
+        <v>-4.626373712796514</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-5.836678430459116</v>
+        <v>-4.965493570464837</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.187562824235613</v>
+        <v>-3.336013041181985</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.635756229474381</v>
+        <v>-2.25204759840274</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-5.140196705205831</v>
+        <v>-4.725600386752802</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-6.735164837311359</v>
+        <v>-5.885396526580571</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-5.56886531738116</v>
+        <v>-4.295737422536241</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-5.431322032610282</v>
+        <v>-5.103535923852363</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-6.667790119183806</v>
+        <v>-6.120319134398635</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-7.414876828844349</v>
+        <v>-7.167280893905676</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-3.987976273607998</v>
+        <v>-4.225166612469806</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-5.177277252630894</v>
+        <v>-4.925383224249721</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-4.80239222793638</v>
+        <v>-5.038185250256056</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-8.547962959987572</v>
+        <v>-8.765949651527336</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-7.356057054845188</v>
+        <v>-7.614674456854416</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-6.055742519077519</v>
+        <v>-6.411493768956923</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.002377</t>
+          <t>X ≈ 0.002338</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.080755431343292</v>
+        <v>1.718968998365014</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.005538896343268</v>
+        <v>0.7292692201519628</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.263111979501438</v>
+        <v>2.469174580854286</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.288946058943445</v>
+        <v>2.998128206138915</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.470954802883242</v>
+        <v>1.238761787907094</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.290095995415584</v>
+        <v>0.6427282632442086</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.734841935732469</v>
+        <v>2.094135506083411</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.08583254943634</v>
+        <v>1.418667736736566</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.0925130046106446</v>
+        <v>0.05512797913256406</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.1282922195279141</v>
+        <v>-0.3609282502754354</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.5938464951335263</v>
+        <v>-0.0910698186172425</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.353475371882112</v>
+        <v>-1.11363464740058</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.739666141395482</v>
+        <v>-1.475997032831273</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.181733900239777</v>
+        <v>-4.340749922517183</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-6.21613696676998</v>
+        <v>-5.771341379427142</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-5.39562289562285</v>
+        <v>-4.842840918735504</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-4.418428921489173</v>
+        <v>-4.950147093056565</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-6.004751106791836</v>
+        <v>-6.959422387291987</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-6.529600466608329</v>
+        <v>-7.126700886898696</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-5.972384286269893</v>
+        <v>-6.918297240777832</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-5.033448972754364</v>
+        <v>-4.862135868259585</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-5.47966530453396</v>
+        <v>-5.316796399551329</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-6.686672073533302</v>
+        <v>-6.58052798027974</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-6.021763586015837</v>
+        <v>-5.996071652020738</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.004187</t>
+          <t>X ≈ 0.004143</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.2017888545068018</v>
+        <v>1.154773476000017</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.098225236403017</v>
+        <v>-0.3671700556226583</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.9335861392966436</v>
+        <v>0.3144533589629788</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.04023960772454416</v>
+        <v>1.005118110578607</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.2288539799574</v>
+        <v>2.337689925150833</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.5108096583610831</v>
+        <v>0.8857124370878466</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.286603102955482</v>
+        <v>-0.2141229552672712</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.530456551921681</v>
+        <v>-1.7942989552052</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.559708919846166</v>
+        <v>0.250418725156031</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.014521236573614</v>
+        <v>-0.2154121749212123</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.061600291118715</v>
+        <v>-0.5871919978804812</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.663107237886017</v>
+        <v>-1.183253876738689</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.2175644427387482</v>
+        <v>0.2759506944498682</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.083146626691331</v>
+        <v>-0.611846779185889</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.06453347170405976</v>
+        <v>0.3153409569168986</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.01583357692678788</v>
+        <v>0.2278917938065987</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.132720298470261</v>
+        <v>2.375960384981894</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.063249369568688</v>
+        <v>1.278471563172246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.971663108027883</v>
+        <v>-0.4446213878694465</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-3.357164564940931</v>
+        <v>-2.492015315545792</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-4.221254141267082</v>
+        <v>-4.35279605476687</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-3.010926469235642</v>
+        <v>-2.817740515716885</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.771821531673197</v>
+        <v>-1.608452621084332</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.8830235598160883</v>
+        <v>-0.8034785187020077</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.005996</t>
+          <t>X ≈ 0.005947</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.667162902905652</v>
+        <v>-2.029040408255788</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.945428719797171</v>
+        <v>2.314103962988511</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.49425177602933</v>
+        <v>1.397694914864189</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.110245125007637</v>
+        <v>1.133981717853004</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.528176926487035</v>
+        <v>-1.756694358667509</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.328052845652806</v>
+        <v>-2.9151165131059</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.7973699505957228</v>
+        <v>-0.4233085073678353</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.8981028151775163</v>
+        <v>1.241506047013459</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.691988950276276</v>
+        <v>-1.060649960437921</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.149115152628475</v>
+        <v>0.318634518044064</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.2171607736245278</v>
+        <v>0.9159055650801236</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.8198792966117665</v>
+        <v>1.956250515690385</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.328296177124066</v>
+        <v>3.805908356262847</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.423006774361617</v>
+        <v>4.882460818272001</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.764863476781137</v>
+        <v>4.535738242914086</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>4.675039872408249</v>
+        <v>6.082125383867208</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.896385893325593</v>
+        <v>4.329488766713062</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>3.449439926346479</v>
+        <v>4.863183574214261</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.994278675691902</v>
+        <v>5.408691247638018</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.852177117238796</v>
+        <v>4.302062576421505</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>4.625420422957013</v>
+        <v>5.726704623733596</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.91799551417953</v>
+        <v>2.668525420691523</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.192470226661548</v>
+        <v>2.910316938328172</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.8008484997540606</v>
+        <v>1.085585980432526</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.007805</t>
+          <t>X ≈ 0.007751</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.091663174633872</v>
+        <v>0.06581050333532801</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.4776815249505049</v>
+        <v>-3.067210836965977</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.080184199681057</v>
+        <v>3.921237271893077</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.309617011514035</v>
+        <v>2.509701588441871</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.562303905221953</v>
+        <v>1.854317970723777</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.7198657111498079</v>
+        <v>0.3595530685379345</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.388844041173748</v>
+        <v>1.225763520844879</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.1239353048139051</v>
+        <v>0.1036283840644074</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.975165045825122</v>
+        <v>2.698551704033193</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.7907267360437373</v>
+        <v>0.2776647784258586</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.710876913185174</v>
+        <v>3.009719284223031</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.666695410971656</v>
+        <v>3.971681463480913</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.543533344115538</v>
+        <v>3.272070613937174</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.203112903883039</v>
+        <v>5.923208449274718</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.544969606302423</v>
+        <v>4.838760017911575</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.6126075570520513</v>
+        <v>1.666389452015416</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.713258321309048</v>
+        <v>2.805454053026544</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.019940251232768</v>
+        <v>2.679610369852128</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.5897410971776225</v>
+        <v>1.644632378281564</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.245722709614881</v>
+        <v>3.524691562306153</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>5.172312344117948</v>
+        <v>5.879016263282622</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>6.33103428394336</v>
+        <v>6.22534647723554</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>6.193986362680604</v>
+        <v>6.052810183951458</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>4.883586208222788</v>
+        <v>5.055616144877284</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.009615</t>
+          <t>X ≈ 0.009556</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.224321425893905</v>
+        <v>4.770732040876226</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>7.260331144398002</v>
+        <v>8.890900797817466</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.889727825704078</v>
+        <v>3.808770905663543</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.423964817497328</v>
+        <v>5.40652614987571</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.211769850568004</v>
+        <v>6.26283157255844</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.275140531047406</v>
+        <v>4.780113615748611</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.873978364010981</v>
+        <v>7.273827591395332</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.472171413639906</v>
+        <v>5.886881112089121</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.513658595554631</v>
+        <v>5.459557710428911</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>7.111529436372081</v>
+        <v>8.514674161131168</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.329409303253101</v>
+        <v>3.644231877410029</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.612457652614097</v>
+        <v>3.91321499762546</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.61289109137595</v>
+        <v>3.348667878651405</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.7064189565023966</v>
+        <v>2.552671851074258</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.6100734117308306</v>
+        <v>2.43558306381577</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>1.204460333673822</v>
+        <v>2.994590869162515</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.070543196696349</v>
+        <v>2.335727077717962</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>1.527500245684159</v>
+        <v>3.319592583536405</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-3.312788148672418</v>
+        <v>-0.3413336179985293</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-2.002346833086392</v>
+        <v>0.9766733937296124</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.421297495434473</v>
+        <v>0.963670128583928</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.497143456843574</v>
+        <v>0.3299009351824722</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-2.908062002788476</v>
+        <v>0.008369214835958871</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-2.983894256011787</v>
+        <v>-1.278971639419382</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.01143</t>
+          <t>X ≈ 0.01136</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.82790288656799</v>
+        <v>1.438634704608234</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.413123911781781</v>
+        <v>-2.599259882819382</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.8363570391872273</v>
+        <v>0.6861326272979582</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.373403019744465</v>
+        <v>5.380076848987358</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.475112547197213</v>
+        <v>3.621194350892381</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>6.224578733294592</v>
+        <v>5.292716195424326</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.452630049404242</v>
+        <v>4.497634183191607</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.174418604651208</v>
+        <v>4.959203118031795</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.77840578656587</v>
+        <v>6.592525007267902</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.224240110529422</v>
+        <v>5.0520527553562</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.717049752691302</v>
+        <v>4.572510806082754</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.094550349243306</v>
+        <v>2.485382511212002</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.372361717612854</v>
+        <v>-0.9037694950294366</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.593440594059402</v>
+        <v>-1.157230034141115</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.8734161083600398</v>
+        <v>1.968429667612746</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>2.249053030303031</v>
+        <v>3.289672276033215</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>2.115135893325601</v>
+        <v>3.95044492449636</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>5.135295189504376</v>
+        <v>6.124290183249187</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>9.257436570428659</v>
+        <v>10.18770113110823</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>7.881782380396686</v>
+        <v>9.646404722805315</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>7.339236212430656</v>
+        <v>9.861028031845052</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>9.607140251021598</v>
+        <v>11.33895621356739</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>5.194114963503651</v>
+        <v>7.720804224570678</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>7.462032710280333</v>
+        <v>9.612717763378221</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.01324</t>
+          <t>X ≈ 0.01316</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.577017326197925</v>
+        <v>-0.3870490163198639</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-12.48626220965412</v>
+        <v>-9.210173341963078</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-17.11577062038724</v>
+        <v>-12.6067070856943</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-18.89255442706406</v>
+        <v>-15.32911821924517</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-17.10068532514321</v>
+        <v>-12.41952187981133</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-12.65839999010966</v>
+        <v>-9.043913457505326</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-13.43034867399999</v>
+        <v>-9.838995469738045</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-13.70856011875308</v>
+        <v>-11.22666644116348</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-11.53941336237027</v>
+        <v>-8.943095398026543</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-13.37615882564092</v>
+        <v>-10.82584099029502</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-14.16592897071295</v>
+        <v>-11.63241293467512</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-11.25318901245879</v>
+        <v>-8.692291857354725</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-11.3125212920808</v>
+        <v>-8.773818462352807</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-11.53360016852749</v>
+        <v>-9.436611024009565</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-11.12791367887397</v>
+        <v>-9.07625726885415</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-9.469696969696969</v>
+        <v>-7.462369820757452</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-9.603614106674506</v>
+        <v>-8.675486747186589</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-7.580795236027534</v>
+        <v>-7.757864540441346</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-8.428733642337228</v>
+        <v>-9.763420083507491</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-6.114228257901146</v>
+        <v>-7.393356767922619</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-6.656774425867141</v>
+        <v>-8.005092737964205</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-6.732620387276242</v>
+        <v>-6.310148231165648</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-7.521975462028237</v>
+        <v>-6.470138557095069</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-8.661637502485483</v>
+        <v>-6.632277551384533</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.01504</t>
+          <t>X ≈ 0.01497</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.587000987833825</v>
+        <v>1.634888064788818</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>8.049692543914382</v>
+        <v>5.201322733734081</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.814205140453048</v>
+        <v>-2.372052686838806</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-2.962040018230205</v>
+        <v>-8.044759196720584</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.297106218083293</v>
+        <v>-0.6787281567691537</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.218249619370582</v>
+        <v>-3.06194670630785</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.446300935480188</v>
+        <v>-3.857028718540569</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.168089490727112</v>
+        <v>-2.872853642084365</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.853714466598717</v>
+        <v>-6.565719322425679</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.702483781415488</v>
+        <v>-2.273013421195252</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.976543423577382</v>
+        <v>-1.983872235838717</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.365497119111197</v>
+        <v>-7.323852330631176</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-6.020304755587567</v>
+        <v>-8.878028970908986</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-6.241383632034093</v>
+        <v>-9.118273988744768</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-9.43117249923494</v>
+        <v>-12.39881333866298</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-8.836785577291906</v>
+        <v>-11.9255307756934</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-5.173234359839</v>
+        <v>-8.265641972031474</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.2147839244196774</v>
+        <v>-2.024675450077972</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.532753026124979</v>
+        <v>0.7489798718407599</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>3.985421620903097</v>
+        <v>0.9399913418118331</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>5.974521022557319</v>
+        <v>4.25050036869272</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>5.898675061148147</v>
+        <v>4.175337846737435</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>4.907326988820074</v>
+        <v>3.120271033314516</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>4.83149473559677</v>
+        <v>4.256833337726349</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.01686</t>
+          <t>X ≈ 0.01677</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.3075137800985317</v>
+        <v>6.033186031699763</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.80215386599609</v>
+        <v>9.928032060153058</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.586357039187256</v>
+        <v>10.79427415920964</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5710414247000202</v>
+        <v>6.061119096244326</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.315390324974928</v>
+        <v>7.944416983745278</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.724578733294464</v>
+        <v>10.14644713738728</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.397074493848557</v>
+        <v>11.40910161501567</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>11.56330749353999</v>
+        <v>13.22511737255516</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>9.38257245323247</v>
+        <v>11.24475002350854</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.165212332751601</v>
+        <v>6.383785317436477</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.88371641935796</v>
+        <v>10.82205308063277</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>10.82718923813226</v>
+        <v>12.6284875004574</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>11.9262493934983</v>
+        <v>11.53887526744143</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>9.482948294829427</v>
+        <v>9.245544658364643</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>13.26924944169331</v>
+        <v>12.7098292916291</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>13.86363636363636</v>
+        <v>13.25038191196775</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>11.50749700443667</v>
+        <v>11.0429904172531</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>11.40265630061542</v>
+        <v>10.90505247650047</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>13.8407699037619</v>
+        <v>13.25286494686131</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>11.80539349150771</v>
+        <v>13.4901594514419</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>9.040625101319527</v>
+        <v>10.82690268977584</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>11.18700136213264</v>
+        <v>12.87939974228863</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>15.90592051905921</v>
+        <v>17.37835337650325</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>11.38564382139155</v>
+        <v>12.96089523327762</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.01867</t>
+          <t>X ≈ 0.01858</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>48</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8.859152886567998</v>
+        <v>5.648325216620108</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.357709421551519</v>
+        <v>1.388190738639793</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.8363570391871917</v>
+        <v>-3.849718371458216</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.959930313588814</v>
+        <v>-6.449234391404637</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2123874528027514</v>
+        <v>-2.656292779604961</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.057912066627985</v>
+        <v>-2.514865490641981</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.369296716070941</v>
+        <v>0.6965269808842578</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.075581395348799</v>
+        <v>-3.591608470730769</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.034094213434074</v>
+        <v>-1.479825215460998</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.442990110529379</v>
+        <v>1.784869882701138</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.88371641935796</v>
+        <v>6.086838856616936</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.77163368257665</v>
+        <v>9.832237702939537</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.565138282387274</v>
+        <v>6.725738081385522</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>11.42739273927396</v>
+        <v>8.500124158125594</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>4.519249441693468</v>
+        <v>3.195480404256756</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>3.030303030303067</v>
+        <v>1.646141009811799</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.8130525599922578</v>
+        <v>-0.5754886831275883</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.7082118561711042</v>
+        <v>-0.7885731672437117</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.9241032370954301</v>
+        <v>-0.6115308523747842</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>1.110949047063457</v>
+        <v>-0.4478660971321204</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>0.5684028790974267</v>
+        <v>-1.052529934337521</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>4.659223584354997</v>
+        <v>3.038974210373858</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>4.933698296836994</v>
+        <v>3.282608695652179</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>9.024532710280376</v>
+        <v>7.287136368029373</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.02048</t>
+          <t>X ≈ 0.02038</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.241505827744504</v>
+        <v>4.697741897166544</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.034447441193542</v>
+        <v>4.372151025985978</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>12.23341586271665</v>
+        <v>11.7562457267552</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>11.52046184327394</v>
+        <v>8.164721207178289</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>14.12584784131489</v>
+        <v>7.68995297838714</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>8.430461086235766</v>
+        <v>2.008010013801353</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4.717335931757226</v>
+        <v>1.33245405478371</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.43912448700415</v>
+        <v>-2.17079879808545</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>10.36296461009529</v>
+        <v>1.075778485582468</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.5900489340588</v>
+        <v>3.079639222439923</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.864108576220723</v>
+        <v>3.351874237044257</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>9.585359172772726</v>
+        <v>3.115134300311396</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>11.4033735765048</v>
+        <v>4.839996432675846</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>14.12347117064652</v>
+        <v>7.511200656534704</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>7.582974931889417</v>
+        <v>0.8308016331123014</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>2.295008912655931</v>
+        <v>-2.347202503314925</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.7800846949097817</v>
+        <v>-3.313809390198315</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-6.767278339907385</v>
+        <v>-7.367497318035653</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>5.213318923369876</v>
+        <v>4.664203092158374</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.4821882078385613</v>
+        <v>-1.175502632807998</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>4.857618565371872</v>
+        <v>4.25050036869272</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>1.84059613337454</v>
+        <v>1.145034816434411</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>5.056247316444782</v>
+        <v>4.418972332015862</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>2.039238592633318</v>
+        <v>1.226530307423324</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.02228</t>
+          <t>X ≈ 0.02218</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.979842541740474</v>
+        <v>7.869203629032263</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>11.54161746752857</v>
+        <v>11.02731465047124</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.655322556428608</v>
+        <v>9.521504477151119</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.942368536985846</v>
+        <v>8.761691564057188</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>5.606578064438594</v>
+        <v>4.496178066814963</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>9.241820112604941</v>
+        <v>11.79596881567024</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.573319704576647</v>
+        <v>4.109145732008898</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.191659983961557</v>
+        <v>10.36114493145737</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-2.111680420330686</v>
+        <v>-3.37811365885846</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.563679765701842</v>
+        <v>-0.853852654077798</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4.286015269932726</v>
+        <v>2.989810931955049</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4.00726586648473</v>
+        <v>-0.7744942368019565</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>13.22893138583552</v>
+        <v>5.086060074318702</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.559576647319957</v>
+        <v>1.266397441457066</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>12.34970921180831</v>
+        <v>3.820850202429106</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>6.04754440961338</v>
+        <v>-2.676997564465466</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-4.431200313570997</v>
+        <v>-9.756324404761905</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-1.087765155323218</v>
+        <v>-6.150369224209228</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-4.320149636467804</v>
+        <v>-6.783286426197307</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>2.763247897638109</v>
+        <v>3.029653796068146</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-1.227574132396896</v>
+        <v>1.328422446614795</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-1.303420093805997</v>
+        <v>1.253259924659567</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>2.419330480745074</v>
+        <v>5.068322981366414</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>9.240049951659735</v>
+        <v>12.04904112993415</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.02409</t>
+          <t>X ≈ 0.02399</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>11.74376827118339</v>
+        <v>13.1240399385561</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>7.562837626679759</v>
+        <v>12.87813310285219</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.278664731494914</v>
+        <v>7.919735297256885</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>13.10417225051377</v>
+        <v>18.43844420955978</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>20.46068947027415</v>
+        <v>25.57029347686787</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>16.80150181021764</v>
+        <v>22.02352337916221</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.491091587865782</v>
+        <v>10.11733025581842</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8.059033989266496</v>
+        <v>13.51611351611356</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>11.94667501733514</v>
+        <v>17.34774612950135</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>18.86606703360627</v>
+        <v>23.95910204168942</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>15.29397282961435</v>
+        <v>20.5276333525901</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>15.01522342616636</v>
+        <v>20.2510513981188</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.199753667002518</v>
+        <v>11.7287518732606</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>9.824828636709768</v>
+        <v>15.18422151553114</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>13.01283918528311</v>
+        <v>18.20577083734984</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>9.761072261072258</v>
+        <v>15.06337115246575</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>5.781001277940945</v>
+        <v>7.552083333333321</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>5.676160574119763</v>
+        <v>7.419199228171721</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>2.045898108890185</v>
+        <v>3.92995775161377</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-5.459563773449425</v>
+        <v>-3.262863210734679</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>1.690197750892239</v>
+        <v>3.577099695292048</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>5.460505635636984</v>
+        <v>7.205640877040416</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>5.734980348119009</v>
+        <v>7.449275362318836</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>1.812994248741859</v>
+        <v>3.583432664325649</v>
       </c>
     </row>
   </sheetData>
@@ -3180,657 +3180,657 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.02748</t>
+          <t>X &gt; -0.02743</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3336</v>
+        <v>3360</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.05346991783804356</v>
+        <v>-0.01025900715286809</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1042719165465229</v>
+        <v>0.02577749473076807</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1857609232792541</v>
+        <v>-0.05949504222187585</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2267161697668385</v>
+        <v>-0.04391388818291375</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.2775886450531644</v>
+        <v>-0.0958580253297967</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2229466095795942</v>
+        <v>-0.07041780891747607</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2027531894863017</v>
+        <v>-0.04948447125688915</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2253427318643517</v>
+        <v>-0.07108149880662751</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.2264994655976622</v>
+        <v>-0.01521683346164338</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1465621282765923</v>
+        <v>0.06505387378229699</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1538072195392175</v>
+        <v>0.08753716390206989</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2958693042811831</v>
+        <v>-0.02376078060805042</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.2963048009710434</v>
+        <v>0.005667174797622465</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.4101246944778083</v>
+        <v>-0.07679617872097566</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.2434560889493724</v>
+        <v>0.1192961168590401</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.3488835725677788</v>
+        <v>-0.01426586697649412</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.1958964877692679</v>
+        <v>0.07757585882585261</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.2231166896099239</v>
+        <v>0.02169477184374102</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.2887322413043094</v>
+        <v>0.04574664600596634</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.2638014519386047</v>
+        <v>0.01035650124846654</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.1896833742719082</v>
+        <v>0.1443181179966473</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1877406656950029</v>
+        <v>0.08686237218225301</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.2849362052107622</v>
+        <v>0.05068367333739587</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.3729493041081184</v>
+        <v>-0.0938160129229999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.02567</t>
+          <t>X &gt; -0.02563</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3319</v>
+        <v>3344</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.02026063826740199</v>
+        <v>0.006526821042953657</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.06960774895627964</v>
+        <v>0.04390850392172041</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.08430164344751034</v>
+        <v>0.05335480086156252</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1218051264070539</v>
+        <v>0.07186121753090902</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2311112395014163</v>
+        <v>-0.03845532545809505</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.17712938777224</v>
+        <v>-0.01362382157804376</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.09293349975642684</v>
+        <v>0.04096409495360831</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1141870925002593</v>
+        <v>0.02074314574313973</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1455219278912452</v>
+        <v>0.04652111764814748</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.09121330981265174</v>
+        <v>0.1012060277481197</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1298890228189009</v>
+        <v>0.092721228669852</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.3012673481448616</v>
+        <v>-0.04758454414057667</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.2959728287239187</v>
+        <v>-0.01270642557480528</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.3792058388776738</v>
+        <v>-0.06456931465503857</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.2383627377938069</v>
+        <v>0.1058934472845081</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.377421646583052</v>
+        <v>-0.03098931778971092</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1929105588692792</v>
+        <v>0.09162376902416725</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.2498081939542658</v>
+        <v>0.006263904788639252</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.316871492146511</v>
+        <v>0.02940147721459141</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.2626842160522642</v>
+        <v>0.02268039738963523</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.2456147809467808</v>
+        <v>0.1002436937871067</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.2131793063406491</v>
+        <v>0.07274587803668453</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.3122856389059834</v>
+        <v>0.03522454019627475</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.3702398115635575</v>
+        <v>-0.07929106418752241</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.02386</t>
+          <t>X &gt; -0.02382</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3299</v>
+        <v>3324</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.05866770343799033</v>
+        <v>-0.03202021481511252</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.166530265289758</v>
+        <v>-0.05272961880550042</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.172679105391083</v>
+        <v>-0.03575382415149164</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1458798967966359</v>
+        <v>0.04618831730390838</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3141053551536075</v>
+        <v>-0.1229738257323589</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2308026354120685</v>
+        <v>-0.06903596653891952</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1113023993291691</v>
+        <v>0.02055284386591438</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1310112596022321</v>
+        <v>0.002030570892841865</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1627906527823484</v>
+        <v>0.0271910730972067</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1638616854259425</v>
+        <v>0.0270513570922688</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2044478318497625</v>
+        <v>0.01686186788985822</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.3752001037920323</v>
+        <v>-0.1226496410499394</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.4235324124768525</v>
+        <v>-0.1408688719224145</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.5059708146698654</v>
+        <v>-0.1915922106125265</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.3603354031272588</v>
+        <v>-0.01605134486843696</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.5038669122430832</v>
+        <v>-0.1571615050417066</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.3174677061904774</v>
+        <v>-0.03322638346843121</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.3438557182112021</v>
+        <v>-0.08830827933577723</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.3823939380458796</v>
+        <v>-0.03630950693342783</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.3593052671963619</v>
+        <v>-0.07442838167479238</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.3085908620696003</v>
+        <v>0.03704024901077929</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.305812263367983</v>
+        <v>-0.02025609630088354</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.3769077637690685</v>
+        <v>-0.02942137953578339</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.4347731399772741</v>
+        <v>-0.1436698894916688</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.02205</t>
+          <t>X &gt; -0.02202</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3267</v>
+        <v>3291</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1291414278132379</v>
+        <v>-0.1026750081347316</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1130934981564735</v>
+        <v>-0.0004261083360503903</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1352736270738006</v>
+        <v>-0.0009571343050893688</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1314661220692628</v>
+        <v>0.05751420072281377</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3284452914633675</v>
+        <v>-0.1407952553688929</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2936861068880603</v>
+        <v>-0.148331158966073</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.2568705596091547</v>
+        <v>-0.1406302439800484</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2741040880079879</v>
+        <v>-0.1563433374742758</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2457029885712458</v>
+        <v>-0.04151245757940814</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.2087928824605569</v>
+        <v>-0.003468698491033706</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.313438052186747</v>
+        <v>-0.07702093850494407</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.5136667138856978</v>
+        <v>-0.245466918563082</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.5820551282290367</v>
+        <v>-0.2830479338148493</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.724219507699928</v>
+        <v>-0.3924275358225486</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.5707993983554687</v>
+        <v>-0.20837057679163</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.5994679620633789</v>
+        <v>-0.2353164408565789</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.5015982239621621</v>
+        <v>-0.2000897008287836</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.4356164359157262</v>
+        <v>-0.1634516665810821</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.4461086618451375</v>
+        <v>-0.08276249290256033</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.4857848773226294</v>
+        <v>-0.1841243808577033</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.4904656224316923</v>
+        <v>-0.1266040084116611</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.4869730099144718</v>
+        <v>-0.1837710067534388</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.5921074967166646</v>
+        <v>-0.2258967721485448</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.6498627595696433</v>
+        <v>-0.3397247684033147</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.02024</t>
+          <t>X &gt; -0.02021</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3228</v>
+        <v>3251</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.07161634420119611</v>
+        <v>-0.06064749781127432</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.08211821772207628</v>
+        <v>0.01531611537893696</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.1488646356896197</v>
+        <v>-0.03100272683074223</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2288452093901014</v>
+        <v>-0.05629632736966528</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2393437066536848</v>
+        <v>-0.07020941134143754</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2372204041052868</v>
+        <v>-0.1103265919468228</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2523006131535439</v>
+        <v>-0.1539875736389362</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2972213460270083</v>
+        <v>-0.1967729240456535</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.2381491008840158</v>
+        <v>-0.05149634628738653</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.1914947753435357</v>
+        <v>-0.003237020190248074</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.20812766168698</v>
+        <v>0.01088498657695425</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.4691070581640986</v>
+        <v>-0.2175017397571182</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.4630339930064551</v>
+        <v>-0.1805516669442824</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.5115613476109786</v>
+        <v>-0.1962003046330878</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.3791904718067869</v>
+        <v>-0.03212963981449235</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.4462111847773187</v>
+        <v>-0.09692568932848644</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.3764116337223555</v>
+        <v>-0.09064226519337382</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.2155667461789861</v>
+        <v>0.04022061799877008</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.2596528202301229</v>
+        <v>0.08861641027245781</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.3329453423755453</v>
+        <v>-0.04729741452366909</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.3620366133198374</v>
+        <v>-0.01278398063956132</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.4194657861300968</v>
+        <v>-0.1311764198137197</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.529164302522986</v>
+        <v>-0.1768008984437657</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.5866816639451571</v>
+        <v>-0.2900193789202703</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.01843</t>
+          <t>X &gt; -0.01841</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3196</v>
+        <v>3218</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.143800175290842</v>
+        <v>-0.1331851977187455</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3231526652788261</v>
+        <v>-0.2391508477650817</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3763295279769494</v>
+        <v>-0.2732369278239943</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.4811848496178754</v>
+        <v>-0.2928256643907403</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.3640676021493974</v>
+        <v>-0.14968043587713</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4571263071534446</v>
+        <v>-0.2845387002224484</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.4647368973744719</v>
+        <v>-0.3205883428420577</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.4762663268556793</v>
+        <v>-0.3298289012574784</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.4170745933780751</v>
+        <v>-0.1844164073008656</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.3623058396263872</v>
+        <v>-0.1275774595940717</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.3818907272089831</v>
+        <v>-0.1161301881094516</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.6739191021282664</v>
+        <v>-0.375023593281341</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.6566421978123742</v>
+        <v>-0.3263506123157711</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.7035076558185978</v>
+        <v>-0.3396666849369794</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.6257063565385579</v>
+        <v>-0.2289638663653975</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.6057768698218098</v>
+        <v>-0.2072311299158329</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.533991877514282</v>
+        <v>-0.1998546511627879</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.4017714875724536</v>
+        <v>-0.09734336901603058</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.4485146948009131</v>
+        <v>-0.05069059763523853</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.5557176196032714</v>
+        <v>-0.2212741356259897</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.5484826059500421</v>
+        <v>-0.1496012372455766</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.6370553399727754</v>
+        <v>-0.2995351063963838</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.7819465785670374</v>
+        <v>-0.4103083593338468</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.7767814323979749</v>
+        <v>-0.4609473278479683</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01662</t>
+          <t>X &gt; -0.01661</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3154</v>
+        <v>3172</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1898543620925466</v>
+        <v>-0.2092933947772622</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2094720050688892</v>
+        <v>-0.09410651309437412</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1662430238446078</v>
+        <v>-0.01660693285293036</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3888920622227303</v>
+        <v>-0.1845020449653987</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2025325174511607</v>
+        <v>0.02738924389782937</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.393995848856143</v>
+        <v>-0.205665056922733</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.3596727897124836</v>
+        <v>-0.1680256551254402</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.3359947749638508</v>
+        <v>-0.1415843322995158</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.2765184558583726</v>
+        <v>0.004139579744787625</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2736186674939916</v>
+        <v>0.01057724570696905</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.2339925720086384</v>
+        <v>0.0810957631952931</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.5261546270600164</v>
+        <v>-0.1774801485032711</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.5881486961210243</v>
+        <v>-0.2061802313228256</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.5693930126493427</v>
+        <v>-0.1532089381783877</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.4815411971428034</v>
+        <v>-0.03098210547043578</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.4377450557456797</v>
+        <v>-0.01699222978442805</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.3947533471807674</v>
+        <v>-0.03940245884450633</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.3225732023917942</v>
+        <v>-0.02783244793483419</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4045330305845951</v>
+        <v>-0.01506375714708952</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.5474027637274475</v>
+        <v>-0.2227008821591951</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.5960457901041494</v>
+        <v>-0.2047609054661876</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.7035774295867654</v>
+        <v>-0.3557957959273921</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.8540724374472148</v>
+        <v>-0.4717247427342031</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.8161457932072551</v>
+        <v>-0.4892402608062696</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.01481</t>
+          <t>X &gt; -0.0148</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3096</v>
+        <v>3106</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.07400906715947286</v>
+        <v>-0.07506520685780771</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1195827806763816</v>
+        <v>-0.01615504719042349</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.0490819749198721</v>
+        <v>0.2174055290493087</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2924600467936074</v>
+        <v>-0.03742129125771498</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.178234447338312</v>
+        <v>0.1208119953863971</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.505572343529586</v>
+        <v>-0.2805027981033561</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.4417768937008688</v>
+        <v>-0.1932685274028358</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2516264114260096</v>
+        <v>-0.03170720659510096</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1274522063579013</v>
+        <v>0.1785102483141472</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.07760191006263994</v>
+        <v>0.2340308166181586</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.01017908541619761</v>
+        <v>0.3644756453476745</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.4313068626047283</v>
+        <v>-0.02191560352050459</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.5375187224437283</v>
+        <v>-0.09173078456571204</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.4819715218944509</v>
+        <v>-0.03234293081507644</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.3476804111372189</v>
+        <v>0.1069657722525861</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.2820760799484177</v>
+        <v>0.14151287800631</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.2034206207021754</v>
+        <v>0.153004202805441</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.1600677137214319</v>
+        <v>0.1355659805281988</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.3444511352828172</v>
+        <v>0.07982024670291565</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.4613018675051492</v>
+        <v>-0.1367467405667071</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.5327972070074622</v>
+        <v>-0.1385168540330852</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.576353856178919</v>
+        <v>-0.2267915553919693</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.7539295150239553</v>
+        <v>-0.3181315682680008</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.7461391243449427</v>
+        <v>-0.429111753885195</v>
       </c>
     </row>
     <row r="14">
@@ -3840,79 +3840,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3022</v>
+        <v>3030</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.0634663538054383</v>
+        <v>0.02880184331797153</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.09088909447439875</v>
+        <v>0.1609911821704557</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.1345954323383651</v>
+        <v>0.2682477441300151</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2161590480856006</v>
+        <v>0.03650128302670907</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.00781340330521374</v>
+        <v>0.3367621429757719</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3979105653553887</v>
+        <v>-0.1112097791929472</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2808240171087704</v>
+        <v>0.03090645098306766</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.07920458375463113</v>
+        <v>0.2041804405560086</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.05180426285752304</v>
+        <v>0.3508477532926051</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.05109821863748465</v>
+        <v>0.4276862632302425</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.01460992413871764</v>
+        <v>0.4560665508227615</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.3770030808358484</v>
+        <v>0.09983509305627081</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.5243536344719431</v>
+        <v>-0.04247347902366982</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.4290429042904194</v>
+        <v>0.05751586250968899</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.2423605506033155</v>
+        <v>0.2503030299570028</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.2226692286137464</v>
+        <v>0.2388033325062224</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.1718334657758618</v>
+        <v>0.2202866041049276</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.05875223283534581</v>
+        <v>0.2386985694102037</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.2528940080836932</v>
+        <v>0.1432715596557799</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.4102149741006187</v>
+        <v>-0.08407466609242675</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.4701625636195814</v>
+        <v>-0.07165291488489345</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.5460085250286824</v>
+        <v>-0.1932157632409712</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.6354107559803026</v>
+        <v>-0.2269591037539556</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.6917148079194959</v>
+        <v>-0.3696293085382791</v>
       </c>
     </row>
     <row r="15">
@@ -3922,1719 +3922,1719 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2931</v>
+        <v>2939</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.1609179917954648</v>
+        <v>0.1579477903077873</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.301361831599074</v>
+        <v>0.3513785686627173</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3908376909183886</v>
+        <v>0.5498781132733441</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.0166173468542965</v>
+        <v>0.2616327241981296</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.2246458126418887</v>
+        <v>0.5458775802410187</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1993859646008644</v>
+        <v>0.04554269303142178</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1227263660743745</v>
+        <v>0.182733954510347</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.127729300746239</v>
+        <v>0.3707854469275773</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.2566666561310882</v>
+        <v>0.6534960229289482</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.250839244066583</v>
+        <v>0.6557445019620545</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.3067846269265146</v>
+        <v>0.7783108593650923</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.04778691843745264</v>
+        <v>0.521392901940402</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1372426699937606</v>
+        <v>0.3414323503478087</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1000542381560336</v>
+        <v>0.3844777229084002</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.05727653969986335</v>
+        <v>0.4347773200876119</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.05532856656452623</v>
+        <v>0.4056526942722272</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.06682936553003316</v>
+        <v>0.3219407671418821</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.04917031305099329</v>
+        <v>0.2431947007240822</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.187859953088676</v>
+        <v>0.206125223433439</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.2876473843492633</v>
+        <v>0.03309329623105839</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.3666812500522454</v>
+        <v>0.02950043049359863</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.4084207994558966</v>
+        <v>-0.05946169578056981</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.5432230310393251</v>
+        <v>-0.1357586512866007</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.598889329978924</v>
+        <v>-0.2777950145270367</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.009385</t>
+          <t>X &gt; -0.009389</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2836</v>
+        <v>2840</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.3051367518784573</v>
+        <v>0.3223610298467321</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5666419598422152</v>
+        <v>0.6710676953670642</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4614885719827342</v>
+        <v>0.6755551254796828</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.02913784962873933</v>
+        <v>0.3279937801167137</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.2896293833950381</v>
+        <v>0.6120718764636948</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.119686436821155</v>
+        <v>0.1939611367238712</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.09047641909908322</v>
+        <v>0.4335127316088858</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1831905344757274</v>
+        <v>0.4986843222137267</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1746632453233303</v>
+        <v>0.6116755580542161</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.2295069644619616</v>
+        <v>0.676639481020807</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.3484161032357349</v>
+        <v>0.8290704363614907</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1955034413023355</v>
+        <v>0.6780422037911507</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.07700119978613174</v>
+        <v>0.5656771886144796</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.08773029201654481</v>
+        <v>0.5838316519833811</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.1539956018528343</v>
+        <v>0.6596532912322459</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.2065873371292071</v>
+        <v>0.6803083143467319</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.05847670641954039</v>
+        <v>0.45689541622761</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.02535621894632811</v>
+        <v>0.2746688931986725</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.2111263038227946</v>
+        <v>0.19370832116401</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.3557528556850187</v>
+        <v>-0.02798276066430105</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.3840410170370561</v>
+        <v>0.02321165318733875</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.4951354803848176</v>
+        <v>-0.1717928550730718</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.678891293105444</v>
+        <v>-0.2592779639747107</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.7339299131328829</v>
+        <v>-0.4358683268063004</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.007575</t>
+          <t>X &gt; -0.007585</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2731</v>
+        <v>2732</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6032330322875197</v>
+        <v>0.6028278173439432</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.8513341938648438</v>
+        <v>0.9387391634582585</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4697814472017967</v>
+        <v>0.6658632433848624</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.303275515190748</v>
+        <v>0.618915590031186</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.5503630025706201</v>
+        <v>0.8888119953863907</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0451616112545139</v>
+        <v>0.354836510475387</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1839597397503283</v>
+        <v>0.4895868339680547</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3274798291409624</v>
+        <v>0.6057140336616271</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.3899852615932105</v>
+        <v>0.7909636462536085</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.3674977691727008</v>
+        <v>0.7806067218976409</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4439742328080527</v>
+        <v>0.8919320775444888</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.2594682324549851</v>
+        <v>0.7094252238394887</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.07034091108378959</v>
+        <v>0.527174794906216</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.09004187489604476</v>
+        <v>0.555807543572314</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.07475425231326938</v>
+        <v>0.5520353798930557</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.1794258373205722</v>
+        <v>0.6243335747420389</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.1770074655376277</v>
+        <v>0.5422257210660817</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.05745594297913925</v>
+        <v>0.3215610494524697</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.03409288438286495</v>
+        <v>0.3385695054940925</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.2281187909063505</v>
+        <v>0.06316018107823851</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.1631667535158456</v>
+        <v>0.2119429480512025</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.3122459628194889</v>
+        <v>-0.02430303907755871</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.4771707377046965</v>
+        <v>-0.08822921140966145</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.443153119086162</v>
+        <v>-0.1555185856065435</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.005766</t>
+          <t>X &gt; -0.005781</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2603</v>
+        <v>2599</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.8142198081741512</v>
+        <v>0.8708237877472556</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.9765749409906874</v>
+        <v>1.045245572601274</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7622652609845488</v>
+        <v>0.8986905612714153</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.4699613371440989</v>
+        <v>0.7266169830210742</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.6313027957631761</v>
+        <v>0.947810849035605</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.05345062622001961</v>
+        <v>0.3405105994738946</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3140067224443968</v>
+        <v>0.5989816319652093</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.3637835625700632</v>
+        <v>0.5836016543473477</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2522485562674817</v>
+        <v>0.618737089857234</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.266755896981735</v>
+        <v>0.6483055965645832</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.2951508246667984</v>
+        <v>0.7131021291767112</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.1535435510816825</v>
+        <v>0.5736183158599033</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1044019474978626</v>
+        <v>0.3238987442694778</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.2261782330015265</v>
+        <v>0.2132520792493224</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.1714458548301394</v>
+        <v>0.2822875380996166</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.02397391637897783</v>
+        <v>0.4446096982612531</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02800523331021054</v>
+        <v>0.3635440649782495</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.1691074016664444</v>
+        <v>0.06155367474882922</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.275973567820138</v>
+        <v>0.06837727713009656</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.5273849265567847</v>
+        <v>-0.2705893387066283</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.5320901417759885</v>
+        <v>-0.1621891708223373</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.6463533140955775</v>
+        <v>-0.3683691191148526</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.7944679216288932</v>
+        <v>-0.4096989966555142</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.8703001748521686</v>
+        <v>-0.5876872820924675</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.003956</t>
+          <t>X &gt; -0.003976</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2474</v>
+        <v>2465</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7726958128074557</v>
+        <v>0.8673611897307225</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.6394506549251986</v>
+        <v>0.7422759408170236</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.8539910577281375</v>
+        <v>1.058262467197693</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.6247129754075331</v>
+        <v>0.9491466155501627</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.7322921118888672</v>
+        <v>1.076327098084747</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.1534380642095385</v>
+        <v>0.3875095965516167</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.2682285983764316</v>
+        <v>0.5417191894740725</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.513999418838992</v>
+        <v>0.7434859913699015</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.3136486321926313</v>
+        <v>0.6930268941369278</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3704094653680841</v>
+        <v>0.726914630397502</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.4025336236590462</v>
+        <v>0.8208805949898021</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.2044293815013702</v>
+        <v>0.6081141532436547</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.1122810724515233</v>
+        <v>0.3244558162989009</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3095307513809047</v>
+        <v>0.1404504717600972</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.1770782419224446</v>
+        <v>0.2905637952227735</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.002599674581915679</v>
+        <v>0.4312703901587582</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.07211168341111573</v>
+        <v>0.2705299352750785</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.4357275377683436</v>
+        <v>-0.202546353913803</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.6000816187386349</v>
+        <v>-0.2475801101345922</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.8982802711796651</v>
+        <v>-0.616717672730033</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.8345208611343793</v>
+        <v>-0.4312441428735099</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.9912075662783266</v>
+        <v>-0.6851846870724927</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.040095828735645</v>
+        <v>-0.6204732183786348</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.035087338224074</v>
+        <v>-0.7182726921464138</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.002147</t>
+          <t>X &gt; -0.002172</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2306</v>
+        <v>2297</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7709175924503811</v>
+        <v>0.7986259716734168</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.6524037698791147</v>
+        <v>0.7255053130753808</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.117498907699343</v>
+        <v>1.24186952651857</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.8803234349694051</v>
+        <v>1.167825859027843</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.279827080069182</v>
+        <v>1.583412427351838</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.5152361727409627</v>
+        <v>0.7468255149913858</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5650867968090836</v>
+        <v>0.7972495874231527</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.5463909229902697</v>
+        <v>0.7332917838754298</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.3716151291264254</v>
+        <v>0.7131184222092557</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.6800143319826617</v>
+        <v>1.023704506551482</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.6945584032103298</v>
+        <v>1.104833929790601</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.4590615949180403</v>
+        <v>0.8968336030174342</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.1576988360204084</v>
+        <v>0.6738061129421666</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.03770173642201513</v>
+        <v>0.4946294527271107</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.02249619494012478</v>
+        <v>0.5754345166405272</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.1665091801514436</v>
+        <v>0.6856094428168333</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.01510339765830793</v>
+        <v>0.4340277777777786</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.1505874502875599</v>
+        <v>0.1533141507364988</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.2991549300049527</v>
+        <v>0.1329374472086187</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.5893255987880082</v>
+        <v>-0.2351940813705795</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.3512993469795376</v>
+        <v>0.1358758627638679</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.6006058461163093</v>
+        <v>-0.2178765943238972</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.5863219402257513</v>
+        <v>-0.07901010330343183</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.5320587901532789</v>
+        <v>-0.17186813059201</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.0003371</t>
+          <t>X &gt; -0.000368</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2076</v>
+        <v>2063</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.8783836557987996</v>
+        <v>0.998459288227707</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.6397607036028319</v>
+        <v>0.7525524525238367</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.172895500725687</v>
+        <v>1.371957341502018</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.9887876351290998</v>
+        <v>1.260093345480925</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.133766393351053</v>
+        <v>1.417019587889996</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5034248871407456</v>
+        <v>0.7089844288712612</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.8372454340196285</v>
+        <v>1.094894358382525</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.751341681574246</v>
+        <v>0.962000962000964</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.6005211711812564</v>
+        <v>0.9252601208747961</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.6929901105293794</v>
+        <v>1.023600338734632</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.9189728296143826</v>
+        <v>1.324036692345963</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.9286849646279194</v>
+        <v>1.364839885401182</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.622830590079495</v>
+        <v>1.098015061231543</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.305597867479058</v>
+        <v>0.8303596942308289</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.3014764739204097</v>
+        <v>0.8527034842824364</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.3474348878583697</v>
+        <v>0.8637538625539136</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.3867566203356674</v>
+        <v>0.7887983091787376</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.3589825690804815</v>
+        <v>0.6365344948061775</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.2376870521242722</v>
+        <v>0.6865305720164088</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.1355155210518291</v>
+        <v>0.49459526370498</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.4600213762071945</v>
+        <v>0.9723167904123429</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.1914971874377827</v>
+        <v>0.5874003604948754</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.2251241157194457</v>
+        <v>0.7632288506909362</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.3901396466965608</v>
+        <v>0.8240567105726058</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.001472</t>
+          <t>X &gt; 0.001436</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1858</v>
+        <v>1844</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.412916327428249</v>
+        <v>1.564900153609827</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.131902969938643</v>
+        <v>1.37275675876618</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.575604351015187</v>
+        <v>1.838492764401479</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.346521299314375</v>
+        <v>1.729961533335185</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.548365235369253</v>
+        <v>1.938274360977793</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.9826432494236315</v>
+        <v>1.234992913212437</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.554780587038657</v>
+        <v>1.783996922485095</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.49162290572643</v>
+        <v>1.640366801657123</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.210529442479853</v>
+        <v>1.58459190480864</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.459119142787451</v>
+        <v>1.734886437495312</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.51812502150851</v>
+        <v>1.877480776750858</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.346902499780946</v>
+        <v>1.794394309996122</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.299009250129124</v>
+        <v>1.789648349251365</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.131693814542743</v>
+        <v>1.62794679420788</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.9902463934595502</v>
+        <v>1.464150641870987</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.025459112111427</v>
+        <v>1.572450426123851</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.214469854574219</v>
+        <v>1.609349675850893</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.271093090473165</v>
+        <v>1.563343372315877</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.7334860860368835</v>
+        <v>1.269861202928823</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.7588679562847815</v>
+        <v>1.138291190419771</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.077462800159445</v>
+        <v>1.686145395025349</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.216902091710509</v>
+        <v>1.698237482313125</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.114627611512269</v>
+        <v>1.758218451749741</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.146437984769079</v>
+        <v>1.683376425874648</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.003282</t>
+          <t>X &gt; 0.00324</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1588</v>
+        <v>1578</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.299366857619013</v>
+        <v>1.538929106268327</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.153388045424009</v>
+        <v>1.481228042208116</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.288685547683144</v>
+        <v>1.732180113465844</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.016260162601625</v>
+        <v>1.516189457944947</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.561526958776824</v>
+        <v>2.056189661634825</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.9303685382033393</v>
+        <v>1.33482966662914</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.354140433293487</v>
+        <v>1.73171754147296</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.390592298798431</v>
+        <v>1.677738126922563</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.432079480713135</v>
+        <v>1.842410285182424</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.72901905955392</v>
+        <v>2.088173324027004</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.877213377612641</v>
+        <v>2.209315034271704</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.976059946474273</v>
+        <v>2.284594375057928</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.985685796547031</v>
+        <v>2.340131030895215</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.205135554461677</v>
+        <v>2.63407691248981</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.215513085690013</v>
+        <v>2.683821667007429</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>2.117204793527208</v>
+        <v>2.653862021645139</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.172204533124045</v>
+        <v>2.715069663512097</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.508169874642917</v>
+        <v>3.000007308979818</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.968393749270014</v>
+        <v>2.68525126369822</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.903350390472291</v>
+        <v>2.496372636996803</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.116471728803489</v>
+        <v>2.789974809495433</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.355487228351571</v>
+        <v>2.880746362272532</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.44104506425932</v>
+        <v>3.16386265385357</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.365212811036045</v>
+        <v>2.977884150031919</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.005091</t>
+          <t>X &gt; 0.005045</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1277</v>
+        <v>1269</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.566670505988554</v>
+        <v>1.632470548153997</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.701744921421039</v>
+        <v>1.931310794162187</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.829896584997719</v>
+        <v>2.077394902387333</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.273559636815747</v>
+        <v>1.640634726925413</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.642545984941925</v>
+        <v>1.987644680211304</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.281352421626622</v>
+        <v>1.44418918115101</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.997265914713559</v>
+        <v>2.205527402381335</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.34552275500355</v>
+        <v>2.523175052357928</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.917158723135948</v>
+        <v>2.230058348262141</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.397179617185607</v>
+        <v>2.649093670106588</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.592930723717146</v>
+        <v>2.890261191036892</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.86234106968184</v>
+        <v>3.129011325258979</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.522264359129558</v>
+        <v>2.842756502890175</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.005962303356412</v>
+        <v>3.424455494623601</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.739361683927783</v>
+        <v>3.26054392029188</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.628971785197315</v>
+        <v>3.244582904546718</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.181820505698305</v>
+        <v>2.797642371995813</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.860065158180959</v>
+        <v>3.419199228171735</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.68441386095337</v>
+        <v>3.447371554741885</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.184493813442934</v>
+        <v>3.711039207001257</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.659958608671886</v>
+        <v>4.529231071951735</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.662421182893176</v>
+        <v>4.26832118126287</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.467044681592924</v>
+        <v>4.325915782266357</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.156286821478496</v>
+        <v>3.898641490172807</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.006901</t>
+          <t>X &gt; 0.006849</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.577035723155909</v>
+        <v>2.771018893070668</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.625609387293245</v>
+        <v>1.812281100136644</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.934764027881982</v>
+        <v>2.288747894375426</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.324584931358054</v>
+        <v>1.798178689457217</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.633193225511711</v>
+        <v>3.151948451598209</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.409059719933857</v>
+        <v>2.799717088146188</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.870410111069191</v>
+        <v>3.022965014813671</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.797748512153731</v>
+        <v>2.921710559185094</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.044785539906051</v>
+        <v>3.253305456649244</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.505168938895252</v>
+        <v>3.373750906440094</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.470903812300762</v>
+        <v>3.504187888777587</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.500479177609179</v>
+        <v>3.493681783606249</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.582866956590678</v>
+        <v>2.543264036087315</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.875662694738139</v>
+        <v>2.971088136753593</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.731394011751611</v>
+        <v>2.864021718732701</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.989706935750107</v>
+        <v>2.362247898063806</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.958564721691431</v>
+        <v>2.321314102564102</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.675923401220714</v>
+        <v>2.970191699082058</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.275165244632191</v>
+        <v>2.837498385773145</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>2.97588566919427</v>
+        <v>3.527260246055498</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.358313807497503</v>
+        <v>4.156876176201386</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>4.207442152357665</v>
+        <v>4.765778334085148</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>3.865267327326876</v>
+        <v>4.766096827747127</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.892209997022412</v>
+        <v>4.773362263346179</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.00871</t>
+          <t>X &gt; 0.008653</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.071481653691322</v>
+        <v>3.657911629897484</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.325745951231916</v>
+        <v>3.412004794193614</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.8877269022009244</v>
+        <v>1.753542186245497</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.996690690977367</v>
+        <v>1.56490849349381</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.989667341717762</v>
+        <v>3.57737188771479</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.450606130554867</v>
+        <v>3.599715991694026</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.363588953513833</v>
+        <v>3.612170991574366</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.770309015610074</v>
+        <v>3.845608556241118</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.400837293415186</v>
+        <v>3.435179457849856</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.408743535186915</v>
+        <v>4.388791488875476</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.723899067759795</v>
+        <v>3.666297623329761</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.445149664311799</v>
+        <v>3.33697132614391</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.595960200195407</v>
+        <v>2.304327448836119</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.100908721009091</v>
+        <v>2.003246223595092</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>2.12769693027785</v>
+        <v>2.216610945750872</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2.448111249481116</v>
+        <v>2.590382560074168</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.040221509763917</v>
+        <v>2.162590579710148</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.894284915531777</v>
+        <v>3.065457731573083</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.836203693716378</v>
+        <v>3.228575170122227</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>2.886063202314539</v>
+        <v>3.528102379685265</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>2.7544759384581</v>
+        <v>3.592278808831814</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>3.500547785268175</v>
+        <v>4.287264224053686</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>3.090090990900912</v>
+        <v>4.344252531268623</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>3.56220394315708</v>
+        <v>4.680826354311968</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.01052</t>
+          <t>X &gt; 0.01046</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.699732596712956</v>
+        <v>3.295739168869858</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.7345210157544528</v>
+        <v>1.628873185741483</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.5646179087524459</v>
+        <v>1.084658657562159</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.213982729889409</v>
+        <v>0.3146365653258769</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.595583561689963</v>
+        <v>2.703376826647499</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.507187428946764</v>
+        <v>3.215550219501708</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.554079324766562</v>
+        <v>2.420468207268989</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.543983822042478</v>
+        <v>3.18126712442875</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.041992743087611</v>
+        <v>2.776336353828668</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.537193009080099</v>
+        <v>3.046004219177718</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.173571491821733</v>
+        <v>3.673479020638183</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.713662668083884</v>
+        <v>3.149430203970837</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.590500601227767</v>
+        <v>1.964442108950784</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.550581145071028</v>
+        <v>1.824433155742774</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>2.617075528649899</v>
+        <v>2.145345474598848</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>2.849143610013172</v>
+        <v>2.458831128570878</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>2.352907632455988</v>
+        <v>2.106242519449431</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>3.335023450373946</v>
+        <v>2.982748388843191</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.819030773327249</v>
+        <v>4.390418212074259</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>4.462398322425706</v>
+        <v>4.358476540569022</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>4.101011574749535</v>
+        <v>4.44777145203976</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>5.112122135079566</v>
+        <v>5.575206094431771</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>5.024278006981916</v>
+        <v>5.755385465162156</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>5.673083434918063</v>
+        <v>6.620469701362715</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.01233</t>
+          <t>X &gt; 0.01226</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.962926471473693</v>
+        <v>3.864780679296807</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.684753446708783</v>
+        <v>2.924429399148494</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.482583454281567</v>
+        <v>1.206772334293952</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.645464904783822</v>
+        <v>-1.237481716366119</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.028178584933059</v>
+        <v>2.422145328719729</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.68684288423799</v>
+        <v>2.579078934717813</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.679045143743863</v>
+        <v>1.783996922485095</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.051777095217204</v>
+        <v>2.636483886483887</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.914018994113036</v>
+        <v>1.607005388760584</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.027895770906731</v>
+        <v>2.43132426391162</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.009502582879982</v>
+        <v>3.398003722960397</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.20245129263953</v>
+        <v>3.352903249970574</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.78683639559474</v>
+        <v>2.843300296393657</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.801606575751919</v>
+        <v>2.738054418201251</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>3.14346327817136</v>
+        <v>2.199554831133774</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>3.030303030303031</v>
+        <v>2.204250349419709</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>2.424687780118006</v>
+        <v>1.541154371584696</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>2.791545189504376</v>
+        <v>2.020138195307879</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.479134683636254</v>
+        <v>2.61405361218025</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>3.430131437000504</v>
+        <v>2.738185007294724</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>3.12343432563825</v>
+        <v>2.789077630674242</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>3.75513553404047</v>
+        <v>3.809116390468596</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>4.973006472937612</v>
+        <v>5.153155013941962</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>5.13302327631812</v>
+        <v>5.703605093286704</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.01414</t>
+          <t>X &gt; 0.01407</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>330</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.540971068386213</v>
+        <v>5.037254928694132</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.721345785187914</v>
+        <v>6.270638033818663</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.495447948278141</v>
+        <v>5.015943931927083</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.267342413683885</v>
+        <v>2.64839380412478</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.477006486591151</v>
+        <v>6.51484749834497</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.057912066627921</v>
+        <v>5.784207139846018</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.982933079707266</v>
+        <v>4.989125127613299</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.825933756166322</v>
+        <v>6.45935261319876</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.746208816868894</v>
+        <v>4.516275605723109</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.700565868105144</v>
+        <v>6.087088015829217</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9.186746722388271</v>
+        <v>7.542754983096259</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.604967015909963</v>
+        <v>6.674457052293604</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>8.087865555114455</v>
+        <v>6.046808802593439</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.169816981698176</v>
+        <v>6.095310646204844</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>7.208643381087306</v>
+        <v>5.30894544052439</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>6.590909090909093</v>
+        <v>4.86989409331705</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.850931347871011</v>
+        <v>4.358470558882232</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>5.746090644049829</v>
+        <v>4.716496525469026</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>6.871072934065076</v>
+        <v>6.027235752506257</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>6.148827834942182</v>
+        <v>5.532034405915255</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>5.909311970006463</v>
+        <v>5.765651883844242</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>6.599580270979864</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>8.532183145321824</v>
+        <v>8.358366271409757</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>9.062411498159157</v>
+        <v>9.1053181862112</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.01595</t>
+          <t>X &gt; 0.01587</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.526483563858875</v>
+        <v>6.072757887274015</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.988519514513044</v>
+        <v>6.596081820800912</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.339345086995991</v>
+        <v>7.264464641986258</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.227984693051262</v>
+        <v>5.902831673947269</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>8.477851591021917</v>
+        <v>8.704196610771007</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>8.266411402617294</v>
+        <v>8.476514832153718</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.096056344224955</v>
+        <v>7.681432819921</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.606689520985825</v>
+        <v>9.299589299589286</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>8.45295757939455</v>
+        <v>7.889056670811861</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.273667401366026</v>
+        <v>8.631466714054056</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>11.14135254153593</v>
+        <v>10.44216326711994</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>12.05782226159391</v>
+        <v>10.93481208187941</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>12.52828569274576</v>
+        <v>10.5891507336594</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>12.70561319080116</v>
+        <v>10.72553205684168</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>12.44587626772259</v>
+        <v>10.69826332984228</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>11.44663769165761</v>
+        <v>9.981545140407178</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>9.320688682170186</v>
+        <v>8.200591763942931</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>7.622222480341023</v>
+        <v>6.768157561505063</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>8.236520235767337</v>
+        <v>7.633661455317494</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>6.829740547727397</v>
+        <v>6.929612729772813</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>5.888788005259379</v>
+        <v>6.226784953672961</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>7.008161167356256</v>
+        <v>7.337393182705817</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>9.673074126850267</v>
+        <v>9.952569169960476</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>10.39405462263098</v>
+        <v>10.58094400966311</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.01776</t>
+          <t>X &gt; 0.01767</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>206</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.582453857441813</v>
+        <v>6.081786417429306</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.247677059091998</v>
+        <v>5.835879581725436</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6.722279369284308</v>
+        <v>6.459119752134328</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.494762243045464</v>
+        <v>5.866717553326104</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>10.04246691612926</v>
+        <v>8.8775443897526</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>9.258559315818871</v>
+        <v>8.095510859600438</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.030299952316874</v>
+        <v>6.830945279292607</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.17927297358321</v>
+        <v>8.403959108184452</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.249886369090149</v>
+        <v>7.123437313643208</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10.38959205227695</v>
+        <v>9.144287226874567</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>11.63452548084664</v>
+        <v>10.35548937762914</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.32664986380641</v>
+        <v>10.54839099123298</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.65979847656195</v>
+        <v>10.37246600993243</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>13.40959338652313</v>
+        <v>11.06319908464955</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>12.26601319573869</v>
+        <v>10.23931381428898</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>10.91865254486613</v>
+        <v>9.235742576022005</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>8.842987835073131</v>
+        <v>7.552083333333321</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>6.79639955843642</v>
+        <v>5.824302896433295</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>7.012290939360746</v>
+        <v>6.351610173266224</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>5.742826069717125</v>
+        <v>5.43278896317841</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>5.200279901751095</v>
+        <v>5.177243528445601</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>6.095307726749759</v>
+        <v>6.072954792898081</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>8.311530012047342</v>
+        <v>8.258336850991988</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>10.1774453316396</v>
+        <v>10.03794542951805</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.01957</t>
+          <t>X &gt; 0.01948</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>158</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.587000987833854</v>
+        <v>6.213470832865006</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.518046974294165</v>
+        <v>7.187076192283094</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>8.510407672098616</v>
+        <v>9.590918675757372</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>9.063276437466016</v>
+        <v>9.608272574510124</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>13.15786571175418</v>
+        <v>12.38149492221567</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>11.44609772063636</v>
+        <v>11.3189163330918</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.142503467125771</v>
+        <v>8.694566028176155</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>12.29467176920814</v>
+        <v>12.04818217013337</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.0703361663127</v>
+        <v>9.737086689573594</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>12.1961546674914</v>
+        <v>11.38005958459814</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>12.47021430965332</v>
+        <v>11.65229459920248</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>12.19146490620533</v>
+        <v>10.76595654717022</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>13.59994840896946</v>
+        <v>11.48033272240237</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>14.01178092492795</v>
+        <v>11.84185475853024</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>14.6194604121575</v>
+        <v>12.37921257176713</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>13.3151131568853</v>
+        <v>11.54144431765548</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>11.28246184269264</v>
+        <v>10.02121913580246</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>8.645975569251206</v>
+        <v>7.833277903119978</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>8.861866950175532</v>
+        <v>8.466994788650837</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>7.14997858292837</v>
+        <v>7.219317082766423</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>6.607432414962339</v>
+        <v>7.069832934860727</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6.531586453553238</v>
+        <v>6.994670412905442</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>9.337706735655544</v>
+        <v>9.769950467804073</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>10.5276972672424</v>
+        <v>10.87363425832473</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.02138</t>
+          <t>X &gt; 0.02128</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>5.230120628503521</v>
+        <v>6.613623271889402</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.314698668863379</v>
+        <v>7.930216436185532</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.489582845638843</v>
+        <v>9.019272334293952</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8.389532052002551</v>
+        <v>9.989370135485728</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>12.89245125687464</v>
+        <v>13.62006199538639</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>12.27296583006878</v>
+        <v>13.77699560138448</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9.081662307468754</v>
+        <v>10.63816358915176</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>14.44861215303827</v>
+        <v>15.80199314574314</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.26429288334006</v>
+        <v>12.02367205542725</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>12.91073204601325</v>
+        <v>13.57137056020791</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>13.18479168817517</v>
+        <v>13.84360557481224</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>12.90604228472718</v>
+        <v>12.78577362034095</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>14.20223505658074</v>
+        <v>13.23338150289018</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>13.98115618013415</v>
+        <v>12.98514744145707</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>16.54881933416649</v>
+        <v>15.42799305957201</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>16.33675464320626</v>
+        <v>15.20804707839167</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>14.58993428042233</v>
+        <v>13.54166666666666</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>12.8721903507947</v>
+        <v>11.84628256150506</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>9.862275280106125</v>
+        <v>9.470931796524852</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>9.242669477170921</v>
+        <v>9.435549487678074</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>7.087220083398442</v>
+        <v>7.814136732329089</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>7.817825734892558</v>
+        <v>8.538974210373802</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>10.51165528608431</v>
+        <v>11.18260869565217</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>12.8551778715707</v>
+        <v>13.42046970136271</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.02319</t>
+          <t>X &gt; 0.02309</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>5.306521307620656</v>
+        <v>6.251187704879094</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>6.024376088218219</v>
+        <v>7.036208704226766</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.74425177602933</v>
+        <v>8.874298107489821</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>9.136560914481336</v>
+        <v>10.34375157878469</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>15.11655991561827</v>
+        <v>16.25376044899464</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>13.19826294382091</v>
+        <v>14.34883838488962</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11.37368268098319</v>
+        <v>12.52282853760536</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>16.35862913096695</v>
+        <v>17.37254726945449</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>15.34748473393429</v>
+        <v>16.46954834408704</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>16.67983221579253</v>
+        <v>17.7353525189708</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>15.90126027900708</v>
+        <v>16.97665969852359</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>15.62251087555909</v>
+        <v>16.70007774405229</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.49934880870297</v>
+        <v>15.58518562660152</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.33090151120375</v>
+        <v>16.36787940021996</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>17.8306529504653</v>
+        <v>18.77850852348954</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>19.47767145135566</v>
+        <v>20.37074037736075</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>20.39638589332556</v>
+        <v>20.26685996563574</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>17.13365045266227</v>
+        <v>17.0411923553195</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>14.19164709674448</v>
+        <v>14.16287107731063</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>11.22059816987041</v>
+        <v>11.28467401721497</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>9.625420422957013</v>
+        <v>9.686301680782691</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>10.60220604049528</v>
+        <v>10.64206699387895</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>12.98194391087208</v>
+        <v>12.94755714926043</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>13.95874323659616</v>
+        <v>13.8163459900225</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.025</t>
+          <t>X &gt; 0.02489</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.880892017002814</v>
+        <v>3.600230414746541</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>5.44466594329068</v>
+        <v>4.782895007614108</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>9.803748343535055</v>
+        <v>9.242486620008243</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7.641518961773464</v>
+        <v>7.221512992628583</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>13.10282993850156</v>
+        <v>12.66024056681496</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>11.84052076228011</v>
+        <v>11.38860274424162</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>13.96712280302743</v>
+        <v>13.45066358915176</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>19.48601280754971</v>
+        <v>18.86002886002885</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>16.62894926482673</v>
+        <v>16.1308149125701</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>15.85603358879024</v>
+        <v>15.33476341735076</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>16.13009323095216</v>
+        <v>15.60699843195509</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>15.85134382750417</v>
+        <v>15.33041647748379</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>17.62673248528574</v>
+        <v>17.07266721717588</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>17.40565360883915</v>
+        <v>16.82443315574277</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>19.64606103589627</v>
+        <v>18.99942163100058</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>23.13899868247694</v>
+        <v>22.4178685069631</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>25.90363227013715</v>
+        <v>25.17113095238096</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>21.45096547935945</v>
+        <v>20.75253256150506</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>18.76830613564609</v>
+        <v>18.10985193150799</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>17.50587658329528</v>
+        <v>16.89586694799553</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>12.61550432837273</v>
+        <v>12.04270816090052</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>12.53965836696363</v>
+        <v>11.96754563894523</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>15.71268380408337</v>
+        <v>15.06832298136647</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>18.53540227549777</v>
+        <v>17.76332684421987</v>
       </c>
     </row>
   </sheetData>
@@ -5824,657 +5824,657 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.02748</t>
+          <t>X &lt; -0.02743</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-4.365484794591382</v>
+        <v>-4.971198156682028</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.700261592941196</v>
+        <v>-5.217104992385899</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.790454555015664</v>
+        <v>-0.7575133799917637</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.054133212139568</v>
+        <v>0.0786558497714438</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.508627039950838</v>
+        <v>2.66024056681497</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.202957498589463</v>
+        <v>-0.03996868432980705</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.974906182479813</v>
+        <v>-2.263622125133956</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.8038422649140529</v>
+        <v>-1.139971139971145</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.7623550829993491</v>
+        <v>-1.012042230287037</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.433821483673512</v>
+        <v>-4.665236582649229</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-4.159761841511589</v>
+        <v>-4.393001568044895</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2.807865566634618</v>
+        <v>2.473273620340947</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>3.133978862097329</v>
+        <v>2.786952931461606</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.710001434926113</v>
+        <v>8.253004584314205</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.8054813257513516</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>5.747694334650859</v>
+        <v>6.703582792677381</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-1.632599613920817</v>
+        <v>-0.5431547619047592</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.2881649554231629</v>
+        <v>0.7525325615050633</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>2.826277150138843</v>
+        <v>3.824137645793691</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>1.56384759778804</v>
+        <v>2.610152662281251</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-1.877249294815677</v>
+        <v>-0.814434696242337</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-1.953095256224778</v>
+        <v>-0.8895972181976219</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>2.669205543213792</v>
+        <v>3.639751552795033</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>6.941199376947033</v>
+        <v>7.763326844219854</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.02567</t>
+          <t>X &lt; -0.02563</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>86</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-4.803637811106391</v>
+        <v>-4.705417425785022</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-5.138414609456206</v>
+        <v>-4.951324261488892</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-5.413642960812773</v>
+        <v>-5.043227665706048</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.963806282581089</v>
+        <v>-4.472839166839847</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.6484339644306942</v>
+        <v>-0.0972345162415138</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.787049173682156</v>
+        <v>-2.265882305592271</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-5.884579252921334</v>
+        <v>-5.386545713173817</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-4.999999999999993</v>
+        <v>-4.528675458908019</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.795722120410879</v>
+        <v>-3.237955851549501</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-5.731428494121779</v>
+        <v>-5.196798044443248</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4.294578154285446</v>
+        <v>-3.761772332164504</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.403416628313067</v>
+        <v>2.938389899410708</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.443045259131374</v>
+        <v>2.986288479634361</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.710338475708042</v>
+        <v>6.22642651122451</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.401032387429801</v>
+        <v>0.8931093386417714</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>5.646582100070475</v>
+        <v>6.105576148159116</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-1.464079222953508</v>
+        <v>-0.9750484496124017</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.7566614685741371</v>
+        <v>1.217648840574824</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>3.298134244847304</v>
+        <v>3.757692463069439</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>1.15939865946649</v>
+        <v>1.646697512779582</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.6168524915004596</v>
+        <v>1.079253011398848</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.6217841675830513</v>
+        <v>-0.1587002082308473</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>3.141062637922253</v>
+        <v>3.573306370070782</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>5.390811780047819</v>
+        <v>5.736748771130159</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.02386</t>
+          <t>X &lt; -0.02382</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>106</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.697450887016871</v>
+        <v>-2.599230501695502</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.145435232536499</v>
+        <v>-0.9583448845691862</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.640058055152394</v>
+        <v>-1.26964276004567</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.296408301010231</v>
+        <v>-2.80544118526899</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.028178584933059</v>
+        <v>2.579378033122239</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.6150439082148438</v>
+        <v>-0.09387704012495846</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.217181271350476</v>
+        <v>-3.719147731602959</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.551996489688456</v>
+        <v>-3.080671948596482</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2.567113081358663</v>
+        <v>-2.009346812497284</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.396632530980057</v>
+        <v>-1.862002081301526</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.179176662403037</v>
+        <v>-0.6463708402820956</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.20245129263953</v>
+        <v>4.737424563737171</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5.909477905028702</v>
+        <v>6.452721125531689</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.518587707827393</v>
+        <v>9.034675743343861</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>4.08685950458645</v>
+        <v>4.57893645579842</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>8.454831332189826</v>
+        <v>8.913825380278467</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>2.660536836721782</v>
+        <v>3.149567610062888</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>3.499092359315696</v>
+        <v>3.960079731316384</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>4.658379966655112</v>
+        <v>5.117938184877246</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>3.901829550208049</v>
+        <v>4.389128403521141</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>2.415887155826923</v>
+        <v>2.878287675725311</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>2.340041194417822</v>
+        <v>2.803125153770026</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>4.501308359730061</v>
+        <v>4.933552091878589</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>6.312268559336978</v>
+        <v>6.658205550419318</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.02205</t>
+          <t>X &lt; -0.02202</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.4034370414895179</v>
+        <v>-0.3052166561681489</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.177062760702647</v>
+        <v>-1.989972412735334</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.176232888870324</v>
+        <v>-1.805817593763599</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.889186908313064</v>
+        <v>-2.398219792571822</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.810993842161245</v>
+        <v>2.362193290350426</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.9709555448887954</v>
+        <v>1.799702435916849</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1990068609984448</v>
+        <v>1.004620423684131</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.6454330974047906</v>
+        <v>1.419124440707172</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.03771740183992733</v>
+        <v>0.1082044295279658</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.8106330778764175</v>
+        <v>-0.687847065691372</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.637339607763764</v>
+        <v>1.74266133020793</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.431053972431712</v>
+        <v>6.502050598758217</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>8.206442630213282</v>
+        <v>8.26485632303406</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>11.60855215956379</v>
+        <v>11.61374456375922</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>8.051858137345555</v>
+        <v>8.053892340147549</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>8.646245059288546</v>
+        <v>8.615196358967211</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>6.338414878832808</v>
+        <v>6.353042565947241</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>4.784298812692782</v>
+        <v>4.781309539922333</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>5.000190193617108</v>
+        <v>4.995771767068106</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>5.911673684744557</v>
+        <v>5.929782672558744</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>6.093765197937948</v>
+        <v>6.081762631609664</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>6.017919236528847</v>
+        <v>6.006600109654379</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>8.466306992489166</v>
+        <v>8.408507976227718</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>9.83975010158472</v>
+        <v>9.685217902801561</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.02024</t>
+          <t>X &lt; -0.02021</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.393656102196005</v>
+        <v>-1.028660247663673</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.290230653354811</v>
+        <v>-1.833226301244643</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.481058691149855</v>
+        <v>-0.8532835316278309</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5086194521656253</v>
+        <v>0.2302919231952245</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2826121719039065</v>
+        <v>0.5133930009729895</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3432178768749026</v>
+        <v>0.6703266069710736</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.01477694205960489</v>
+        <v>0.9925630304925406</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.8665090001313871</v>
+        <v>1.804961022838114</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.2219473207787672</v>
+        <v>0.2569122788909297</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.9948629968152574</v>
+        <v>-0.5391392163284081</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.7208033546533343</v>
+        <v>-0.2669042017240741</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.085193004610545</v>
+        <v>4.484446804698486</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.091974440579285</v>
+        <v>4.486873123001899</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>5.000839066957539</v>
+        <v>5.355957497322997</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>2.647780515139701</v>
+        <v>2.997825461806649</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>3.807139188495128</v>
+        <v>4.117788698503396</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>2.543278548692797</v>
+        <v>2.896589851024203</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.3864209121905446</v>
+        <v>-0.02959034352286238</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.3944422201462174</v>
+        <v>0.7435311014999968</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.711231532939102</v>
+        <v>2.075435982313167</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>2.298628867797937</v>
+        <v>2.625309916686625</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>3.352726409213695</v>
+        <v>3.667465830485526</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>5.322116375933035</v>
+        <v>5.587077969395189</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>6.376227625534618</v>
+        <v>6.542257410859925</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.01843</t>
+          <t>X &lt; -0.01841</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.08634474376372481</v>
+        <v>0.2309581775497804</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.738661802503934</v>
+        <v>2.343541907883647</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.205404658234841</v>
+        <v>2.97564025882226</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.397212543554012</v>
+        <v>3.798332399636671</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.632850642435315</v>
+        <v>1.63598180670715</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.054722273964444</v>
+        <v>3.208009752327875</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.239711389117161</v>
+        <v>3.356323966510253</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.439968843885609</v>
+        <v>3.523101636309178</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.524518226757259</v>
+        <v>2.235936206370646</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.751602550720769</v>
+        <v>1.439884711151308</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.025662192882692</v>
+        <v>1.712119725755642</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6.531601784650007</v>
+        <v>6.15251890335982</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>6.365377516836951</v>
+        <v>5.981023012324137</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.101236439433421</v>
+        <v>6.676185177306131</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>5.964624242331332</v>
+        <v>5.522332682213523</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>5.602073365231263</v>
+        <v>5.140240474618082</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>4.511218429210729</v>
+        <v>4.092963836477985</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>2.492502127303425</v>
+        <v>2.073287278486191</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>3.186862407749281</v>
+        <v>2.759447618839516</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>4.809114916281899</v>
+        <v>4.389128403521141</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>4.7450376478374</v>
+        <v>4.293382015347959</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>6.10459838499289</v>
+        <v>5.633313833015315</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>8.292948695561066</v>
+        <v>8.235438884331423</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>8.21711644233779</v>
+        <v>8.073299890041959</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01662</t>
+          <t>X &lt; -0.01661</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.4767999453915621</v>
+        <v>1.108536062587071</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.03861603776602607</v>
+        <v>0.08743542843358654</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.8681884153582331</v>
+        <v>-0.7796617742331833</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.580912901167409</v>
+        <v>1.728711220757049</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.7311621563600994</v>
+        <v>-0.8724283146911276</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.661086669802536</v>
+        <v>1.610086686655798</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.285963382737577</v>
+        <v>0.8150046744230792</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.007751937984501</v>
+        <v>0.51008423101446</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2555883262484073</v>
+        <v>-0.5247775569758559</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2763234438627151</v>
+        <v>-0.54563525374558</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.2432677076261598</v>
+        <v>-1.04859403759086</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.446236857179819</v>
+        <v>2.550793000185905</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.307201774450675</v>
+        <v>3.373885378859164</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.086122898004085</v>
+        <v>3.125651317426055</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3.031154203598135</v>
+        <v>2.055900036316196</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>2.435064935064936</v>
+        <v>1.842010256686244</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>1.904322401262071</v>
+        <v>1.350532945736425</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>1.005830903790084</v>
+        <v>0.8300519413500211</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.015373078365215</v>
+        <v>1.819707966945408</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>3.789520475634824</v>
+        <v>3.58468200890362</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>4.43745049814499</v>
+        <v>4.180028205197303</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>5.812942043850278</v>
+        <v>5.267656380916442</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>7.681042254340298</v>
+        <v>7.449275362318836</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>7.206803626615034</v>
+        <v>6.899539468804569</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.01481</t>
+          <t>X &lt; -0.0148</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.7927458476091758</v>
+        <v>-0.4562069750241733</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.9597508959087619</v>
+        <v>-0.7021138107280436</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.865872260175827</v>
+        <v>-2.882733838545555</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2428297713368437</v>
+        <v>-0.08007430895871437</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.8713331397037436</v>
+        <v>-1.590200350292619</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.378424887140746</v>
+        <v>1.961794984100528</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.795073779307778</v>
+        <v>0.8580709965591637</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.09085470724593847</v>
+        <v>-0.6814173480840182</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.335541158771754</v>
+        <v>-2.096698314943126</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.786913426448109</v>
+        <v>-2.584107834853818</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.47748400936657</v>
+        <v>-3.546440721484046</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.745374304227234</v>
+        <v>0.4979649783656441</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.873016095892012</v>
+        <v>1.543566688075359</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.330393811085301</v>
+        <v>1.295332626642249</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.029163696784479</v>
+        <v>0.3045362694485547</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.3373769852869586</v>
+        <v>-0.06008563765771413</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.4396269684107779</v>
+        <v>-0.78125</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.866011080592088</v>
+        <v>-0.914134105161601</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.9575973421328783</v>
+        <v>0.5348960232187352</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>2.109073377181289</v>
+        <v>1.984050369512296</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2.852700842655771</v>
+        <v>2.651173769366125</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>3.301696702634494</v>
+        <v>2.884653222719479</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>5.075284057354779</v>
+        <v>4.362855609232433</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>4.999451804131503</v>
+        <v>4.818000565560247</v>
       </c>
     </row>
     <row r="14">
@@ -6484,79 +6484,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.722688545657029</v>
+        <v>-1.17354942137743</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.437162373320248</v>
+        <v>-1.918209374288281</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.97148357777936</v>
+        <v>-2.674150358972881</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.456493887472007</v>
+        <v>-0.6356298645142644</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.198821561329922</v>
+        <v>-2.911188004613606</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.9784647436572911</v>
+        <v>0.2457456013844848</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.09548719226138047</v>
+        <v>-1.049336410848234</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.481425551192991</v>
+        <v>-2.354256854256853</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.69967862901855</v>
+        <v>-2.976327944572752</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.47259430505504</v>
+        <v>-3.52237943979209</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.198534662893117</v>
+        <v>-3.500144425187756</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.8993393102822651</v>
+        <v>-0.5267263796590598</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.113839581088484</v>
+        <v>0.8583815028901753</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.373280185161377</v>
+        <v>0.360147441457066</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.0640838916399602</v>
+        <v>-0.8220069404279897</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.2489177489177479</v>
+        <v>-0.7607029216083276</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.6425751456354831</v>
+        <v>-1.114583333333343</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.526636628677444</v>
+        <v>-1.497467438494937</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.01204394905182227</v>
+        <v>-0.03300521134916323</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.213762899877246</v>
+        <v>1.181581233709821</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>1.710177770872257</v>
+        <v>1.614136732329086</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>2.315473584354933</v>
+        <v>2.038974210373802</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>3.01355034209373</v>
+        <v>2.782608695652179</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>3.459911300358712</v>
+        <v>3.370469701362708</v>
       </c>
     </row>
     <row r="15">
@@ -6566,1719 +6566,1719 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.98109607608756</v>
+        <v>-1.720764379932461</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.247973184131048</v>
+        <v>-2.672914902556855</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.955309627479444</v>
+        <v>-3.823715470584098</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.638079234952805</v>
+        <v>-1.867809090583521</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.115107118074754</v>
+        <v>-3.569029145143141</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.510222105279837</v>
+        <v>-0.764437698004528</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.9549329758058391</v>
+        <v>-1.763185698017281</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.493648622239583</v>
+        <v>-2.882770092546068</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.292497574778672</v>
+        <v>-4.180503097322244</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.225077116361369</v>
+        <v>-4.161890641421415</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.581269575039791</v>
+        <v>-4.704319577937248</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.969262675966775</v>
+        <v>-2.944241654608135</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.7815003730749908</v>
+        <v>-1.615141918698427</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.002579249521581</v>
+        <v>-1.659709992351488</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.24055447987525</v>
+        <v>-1.730866410896425</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.276419658772596</v>
+        <v>-1.576894367636839</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.200252762136621</v>
+        <v>-1.477108791581806</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.305093465957803</v>
+        <v>-1.20266092118333</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.458949984193147</v>
+        <v>-0.3772007306974317</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.148063893001769</v>
+        <v>0.2447176899216359</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.6559378931029656</v>
+        <v>0.6956031274411032</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.9179955141794949</v>
+        <v>0.82410659326586</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>1.742770026794794</v>
+        <v>1.678739041884363</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>2.088878701841558</v>
+        <v>2.127598010935017</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.009385</t>
+          <t>X &lt; -0.009389</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.34102042365727</v>
+        <v>-2.195825381309248</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.704216531773994</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.587556004291031</v>
+        <v>-3.691876314354701</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.59698025551684</v>
+        <v>-1.828523265529505</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.884726021738217</v>
+        <v>-3.199323597833946</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.8558408471249948</v>
+        <v>-1.347474737598574</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.880995169509944</v>
+        <v>-2.651031326102476</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.334337962774399</v>
+        <v>-2.955951769511096</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.292850780859695</v>
+        <v>-3.167005910674447</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.540372411362043</v>
+        <v>-3.454582829622595</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.14196951175704</v>
+        <v>-4.029805442136905</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.369930824136723</v>
+        <v>-3.119946718642105</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.741779405879015</v>
+        <v>-2.370432056431859</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.787726933814213</v>
+        <v>-2.279683067017515</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.095607534372007</v>
+        <v>-2.453362872631381</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.376877354985936</v>
+        <v>-2.570024955506632</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.635137749406489</v>
+        <v>-1.826447740113004</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.214584407693515</v>
+        <v>-1.111874218155947</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.2981676327236684</v>
+        <v>-0.21944588931526</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.4140722227785147</v>
+        <v>0.5036151320149003</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.5720514488580264</v>
+        <v>0.6141367323290865</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>1.128521829968967</v>
+        <v>1.216940312068715</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>2.037535438020349</v>
+        <v>1.969049373618283</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>2.31319703365471</v>
+        <v>2.484876481023733</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.007575</t>
+          <t>X &lt; -0.007585</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>674</v>
+        <v>698</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.128402018263586</v>
+        <v>-2.902512930102063</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-4.415506609728993</v>
+        <v>-4.073433848714757</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.990735471825992</v>
+        <v>-2.974754056576231</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.450126392020223</v>
+        <v>-2.635629864514272</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.443241650151826</v>
+        <v>-3.693734499606457</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.408164629537268</v>
+        <v>-1.742793080563942</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.951358133756763</v>
+        <v>-2.39460861715196</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.52499055339905</v>
+        <v>-2.84279553620528</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.778924346373564</v>
+        <v>-3.287932529099969</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.665577097742407</v>
+        <v>-3.224385170451114</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.982359405358913</v>
+        <v>-3.525216058425578</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.227135396694656</v>
+        <v>-2.65566620773928</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.430061126770866</v>
+        <v>-1.764827666164265</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.503429515772844</v>
+        <v>-1.72652877630798</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.423020376130353</v>
+        <v>-1.549084304324843</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.862606866299629</v>
+        <v>-1.847379139373373</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.848813515832497</v>
+        <v>-1.80799307545368</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.362812269875242</v>
+        <v>-1.081278326747089</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.9992104015063106</v>
+        <v>-0.7235496239566217</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.2215226417598402</v>
+        <v>0.06410272368117376</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.4686478348366592</v>
+        <v>-0.2168088264101655</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.135061848654729</v>
+        <v>0.4243610298580478</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.7948094079480938</v>
+        <v>0.9545284664258205</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.6602893868382438</v>
+        <v>0.9356559477810578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.005766</t>
+          <t>X &lt; -0.005781</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>802</v>
+        <v>831</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.210342808388909</v>
+        <v>-3.183775053469454</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.608892845251589</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.379117683377508</v>
+        <v>-3.1247624378883</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.546350066675274</v>
+        <v>-2.454357355510673</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.063129109168671</v>
+        <v>-3.146764927690533</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.201163840962828</v>
+        <v>-1.361955962995786</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.028782590000965</v>
+        <v>-2.277374918670141</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.183078297455396</v>
+        <v>-2.221284531753859</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.825037141473835</v>
+        <v>-2.093355622069751</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.853535944061186</v>
+        <v>-2.167385456639266</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.951684738623833</v>
+        <v>-2.25616127235984</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.486017268622696</v>
+        <v>-1.690384622739678</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.6240676729478025</v>
+        <v>-0.7595487016826326</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.22479915485345</v>
+        <v>-0.2857611024659192</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.3866645368012485</v>
+        <v>-0.3662307671427953</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.032972403940143</v>
+        <v>-0.8879592392978566</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-1.042820062009433</v>
+        <v>-0.8715027075812287</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.4032438923814752</v>
+        <v>-0.04169126520974231</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.06328303254896639</v>
+        <v>0.2931079053776671</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.7439101719600032</v>
+        <v>1.109379067644838</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.7728542248530559</v>
+        <v>1.023282340030647</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>1.145541992315124</v>
+        <v>1.429467591841913</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>1.62060157620602</v>
+        <v>1.793439020561927</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.870542685342727</v>
+        <v>2.112647800039014</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.003956</t>
+          <t>X &lt; -0.003976</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>931</v>
+        <v>965</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.53208259389659</v>
+        <v>-2.614791676564209</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.390000233134849</v>
+        <v>-2.188946360512091</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.032690579860386</v>
+        <v>-2.977111963226704</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.524902065001271</v>
+        <v>-2.584957682508062</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.803850867436928</v>
+        <v>-2.909117611238862</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.286036977958062</v>
+        <v>-1.246482377890139</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.574468781626578</v>
+        <v>-1.730683561107305</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.219198416625431</v>
+        <v>-2.242857890526288</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.693039900335087</v>
+        <v>-1.907675094831816</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.826977940588833</v>
+        <v>-1.978337989014889</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.919410801679703</v>
+        <v>-2.120610746431275</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.39147553122627</v>
+        <v>-1.464550213855944</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.5310155637666583</v>
+        <v>-0.6105304142082773</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.004231192349998025</v>
+        <v>-0.02974893159992575</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.3418616694177388</v>
+        <v>-0.2973955414642617</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.8158508158508155</v>
+        <v>-0.668734009691228</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.629255132315464</v>
+        <v>-0.4617335924006909</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.3342802322394149</v>
+        <v>0.6489056184998887</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.7638468268389573</v>
+        <v>1.070621731656018</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.549897353658757</v>
+        <v>1.803342891740911</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.393706233843972</v>
+        <v>1.546779219375715</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.8122246561663</v>
+        <v>1.989751412446338</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.938347796121676</v>
+        <v>2.026132011714353</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.928668048626236</v>
+        <v>2.071246903435252</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.002147</t>
+          <t>X &lt; -0.002172</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1099</v>
+        <v>1133</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.027943887625518</v>
+        <v>-1.960904408251196</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.957686692050842</v>
+        <v>-1.721690995652637</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.989944576611691</v>
+        <v>-2.754495271339849</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.577630223741586</v>
+        <v>-2.507876560549519</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.404833495968248</v>
+        <v>-3.353868780627721</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.81997572215095</v>
+        <v>-1.738367373019756</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.912234815460621</v>
+        <v>-1.915620612083906</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.870216201480488</v>
+        <v>-1.779234788943533</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.507920928235571</v>
+        <v>-1.56304462594963</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.140117387212271</v>
+        <v>-2.182573614549376</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.177163628863859</v>
+        <v>-2.263383613184224</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.681609153019139</v>
+        <v>-1.745614287867348</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.032687804569328</v>
+        <v>-1.183542592431984</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.6197087100014329</v>
+        <v>-0.7256866273867146</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.7343737467124214</v>
+        <v>-0.7900122361031876</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.045783926218711</v>
+        <v>-1.023059497071699</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.7268025124715507</v>
+        <v>-0.6856336422477156</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.3787446655680853</v>
+        <v>-0.2006889742407481</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.07227357449883698</v>
+        <v>0.1020345062148209</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.5310910839325444</v>
+        <v>0.6696659645130012</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.0428432904706284</v>
+        <v>0.1022214631322669</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.5663534662804608</v>
+        <v>0.6448877143455576</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.5321831453218309</v>
+        <v>0.5354771863847461</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.4201196074596254</v>
+        <v>0.5498606987148733</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.0003371</t>
+          <t>X &lt; -0.000368</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1329</v>
+        <v>1367</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.712063730642647</v>
+        <v>-1.793355591084357</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.488615745486314</v>
+        <v>-1.345061645506661</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.367580553680526</v>
+        <v>-2.26950503796882</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.148901812969271</v>
+        <v>-2.019851924412009</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.370125548040882</v>
+        <v>-2.256217244379684</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.398280536995799</v>
+        <v>-1.255351691958609</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.905790218852097</v>
+        <v>-1.904127925113052</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.770025839793277</v>
+        <v>-1.696978141747721</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.537825556717721</v>
+        <v>-1.495896342524475</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.671647678865696</v>
+        <v>-1.633571831891572</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.028092250298229</v>
+        <v>-2.019712823139479</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.040757242379733</v>
+        <v>-2.003683219454217</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.550131178690663</v>
+        <v>-1.509211767043993</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.053880668965768</v>
+        <v>-1.025916933085725</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.037866663175542</v>
+        <v>-0.9765424195794168</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.117637044603335</v>
+        <v>-1.00046151707285</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.176647814539614</v>
+        <v>-1.031189039258713</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.131675784278393</v>
+        <v>-0.8714615862637771</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.9468362931395191</v>
+        <v>-0.7301522486571344</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.7910889624389768</v>
+        <v>-0.5887186931372881</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.289705229010742</v>
+        <v>-1.156163194518022</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.870766398114398</v>
+        <v>-0.719255489699357</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.9278305252181553</v>
+        <v>-0.8413854521166613</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.18521145826741</v>
+        <v>-1.076677335945256</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.001472</t>
+          <t>X &lt; 0.001436</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1547</v>
+        <v>1586</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.982683848125845</v>
+        <v>-2.067422710533698</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.77396469033954</v>
+        <v>-1.778483312558187</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.34850886119591</v>
+        <v>-2.309098187390518</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.132986756613342</v>
+        <v>-2.113617285897917</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.370315841549584</v>
+        <v>-2.355492598697936</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.7008851182729</v>
+        <v>-1.598083113980763</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.373874432029815</v>
+        <v>-2.296028282303823</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.296753720781254</v>
+        <v>-2.125379174559505</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.963581392921306</v>
+        <v>-1.934398562479437</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.252006682286535</v>
+        <v>-2.099933033739127</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.327237795447338</v>
+        <v>-2.20600823351058</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.120787640480529</v>
+        <v>-2.041228271210123</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.051185625067831</v>
+        <v>-1.958138043137566</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.849670497596378</v>
+        <v>-1.701958485402955</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.671800933440601</v>
+        <v>-1.438337331348549</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.720500828217872</v>
+        <v>-1.570602038884495</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.945956449016784</v>
+        <v>-1.73753415300547</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.013670522021705</v>
+        <v>-1.744314853375137</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.374006728540365</v>
+        <v>-1.214594114249543</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.407587381047506</v>
+        <v>-1.189162776378446</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.783747658537038</v>
+        <v>-1.693555575363227</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.951224016247608</v>
+        <v>-1.831769799714465</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.833097568796092</v>
+        <v>-1.777290421623988</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.871556494632351</v>
+        <v>-1.813326011121518</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.003282</t>
+          <t>X &lt; 0.00324</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1817</v>
+        <v>1852</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.384185884503196</v>
+        <v>-1.525413172435506</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.364089635394407</v>
+        <v>-1.420395781252573</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.521427391950496</v>
+        <v>-1.623733858490112</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.333568657815427</v>
+        <v>-1.379164347272891</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.80298690784366</v>
+        <v>-1.841107142079906</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.259063578591991</v>
+        <v>-1.277447494624148</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.619110267016929</v>
+        <v>-1.665364473449429</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.648725500152324</v>
+        <v>-1.616675860736343</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.686060352156133</v>
+        <v>-1.650733992088952</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.936791310235648</v>
+        <v>-1.852833003506987</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.069445599960417</v>
+        <v>-1.904572070976094</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.153603370669167</v>
+        <v>-1.911175623719529</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.151473649741988</v>
+        <v>-1.892158453913282</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.341318469196317</v>
+        <v>-2.086396835000819</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-2.342287615626809</v>
+        <v>-2.066607372393435</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-2.264217517642173</v>
+        <v>-2.045260157029496</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-2.311947440007778</v>
+        <v>-2.203136249100076</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-2.604779549936104</v>
+        <v>-2.498007395298394</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.138007995981837</v>
+        <v>-2.067562446770332</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.084410645413271</v>
+        <v>-2.014963042748064</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.265846205151725</v>
+        <v>-2.150442101364213</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.474961865525955</v>
+        <v>-2.33359598401065</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-2.553925465539251</v>
+        <v>-2.467931261151278</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.488263107000854</v>
+        <v>-2.414087534058453</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.005091</t>
+          <t>X &lt; 0.005045</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2128</v>
+        <v>2161</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.153631864710448</v>
+        <v>-1.144102742870743</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.324461121084113</v>
+        <v>-1.2735358711518</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.435048265605701</v>
+        <v>-1.349783529048615</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.145218954184756</v>
+        <v>-1.039786908394184</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.362247722947174</v>
+        <v>-1.24390519500178</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.149605796062346</v>
+        <v>-0.969233594177247</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.569514472740281</v>
+        <v>-1.461454819728907</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.775208261020481</v>
+        <v>-1.648333670545611</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.521145076709914</v>
+        <v>-1.381580142629204</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.801174221870248</v>
+        <v>-1.622333164919354</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.921203400041065</v>
+        <v>-1.720297132267817</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.080391239541733</v>
+        <v>-1.811779595762708</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.868358678809635</v>
+        <v>-1.584700403634585</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.156174457483161</v>
+        <v>-1.879209337811794</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.992020251022275</v>
+        <v>-1.728416010303043</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.932243786176365</v>
+        <v>-1.722410464412583</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.66450403641683</v>
+        <v>-1.548641639673001</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-2.070216759886442</v>
+        <v>-1.959174981299192</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.967950208755539</v>
+        <v>-1.837262499641618</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-2.270070340053557</v>
+        <v>-2.085424782023637</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-2.551220146086429</v>
+        <v>-2.467769792427966</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-2.553217730199059</v>
+        <v>-2.404107696150959</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-2.43967730986413</v>
+        <v>-2.345572701848972</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.253662778441431</v>
+        <v>-2.183787586929739</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.006901</t>
+          <t>X &lt; 0.006849</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2432</v>
+        <v>2462</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.217221858849484</v>
+        <v>-1.256103053484935</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9193891929553786</v>
+        <v>-0.8330679767699323</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.072020457755286</v>
+        <v>-1.013256017265384</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.8655855610059149</v>
+        <v>-0.7733932356650044</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.382828089277702</v>
+        <v>-1.310458373482675</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.295829429970709</v>
+        <v>-1.212486353197839</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.47366639812536</v>
+        <v>-1.336354666426331</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.443228454172363</v>
+        <v>-1.294191919191924</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.542369652747574</v>
+        <v>-1.34670959296902</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.720133356355333</v>
+        <v>-1.38915441948339</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.709330615406856</v>
+        <v>-1.401241094562245</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.719637457630675</v>
+        <v>-1.352883975109904</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.34613883590999</v>
+        <v>-0.9243154914233855</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.461632649751451</v>
+        <v>-1.050697400135135</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.399602121873478</v>
+        <v>-0.9611214814515421</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.109041231992052</v>
+        <v>-0.7653739207959731</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.096029030823686</v>
+        <v>-0.8286369482805327</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.381957681701529</v>
+        <v>-1.123990590403956</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.224200688496204</v>
+        <v>-0.950145747498631</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.506046026828237</v>
+        <v>-1.304202681806018</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.655245307076491</v>
+        <v>-1.465473340782211</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.994775320054821</v>
+        <v>-1.784340168180222</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.860896853183569</v>
+        <v>-1.70317521986366</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.871848868666994</v>
+        <v>-1.784079445672212</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.00871</t>
+          <t>X &lt; 0.008653</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2675</v>
+        <v>2701</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.009268166063549</v>
+        <v>-1.144102742870743</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.8795912829349106</v>
+        <v>-1.038441278838462</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.5175005275783562</v>
+        <v>-0.5749854205066427</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.5792871472313976</v>
+        <v>-0.4823236214407629</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.117175871511023</v>
+        <v>-1.033139224125797</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.243857954414288</v>
+        <v>-1.077729444826247</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.215274854013288</v>
+        <v>-1.112945878303861</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.324094959079794</v>
+        <v>-1.175381530542467</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.224614659530786</v>
+        <v>-0.9898364567859304</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.493231533204352</v>
+        <v>-1.246925904064582</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.309735961594406</v>
+        <v>-1.0117142141548</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.232522129357363</v>
+        <v>-0.8810395969859641</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.9942436982531717</v>
+        <v>-0.5520220513489988</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.8584545605398404</v>
+        <v>-0.4300228658365342</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.8614013283016533</v>
+        <v>-0.4457574032195453</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.9531110584036426</v>
+        <v>-0.5508732289019278</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.8414962841539335</v>
+        <v>-0.5066603418486935</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.07361706338633</v>
+        <v>-0.7876377457885368</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.059727608675772</v>
+        <v>-0.7212688174209916</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.075034528897788</v>
+        <v>-0.8769156193075816</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.035717110944958</v>
+        <v>-0.8149636008808372</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.239014493094949</v>
+        <v>-1.075242746308916</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.129455664299037</v>
+        <v>-1.016724884503319</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.258177570093451</v>
+        <v>-1.178863878792782</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.01052</t>
+          <t>X &lt; 0.01046</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2853</v>
+        <v>2880</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.6853533721245952</v>
+        <v>-0.7744606381452002</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3756239117817799</v>
+        <v>-0.4136633665143634</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3684098362477073</v>
+        <v>-0.2994603526866584</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3312610944218974</v>
+        <v>-0.1108636712340569</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.7868999876217231</v>
+        <v>-0.5750826685082728</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.9636831963466435</v>
+        <v>-0.7109268422896946</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.7755929471114342</v>
+        <v>-0.5853974372005339</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9644799662794767</v>
+        <v>-0.7321618143678492</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.8684735718720731</v>
+        <v>-0.584759589263939</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.9589980303844712</v>
+        <v>-0.6324106789451562</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.083717867685529</v>
+        <v>-0.7223666474099772</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.9936368235315669</v>
+        <v>-0.5822819352146098</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.7700572483390715</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.7611623893789954</v>
+        <v>-0.2440192252096054</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.7698840314023627</v>
+        <v>-0.2664513848724326</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.8188755785749819</v>
+        <v>-0.3301473660527705</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.7224952255555621</v>
+        <v>-0.3298611111111143</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.9116727188551934</v>
+        <v>-0.5321896607171652</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.200051183245201</v>
+        <v>-0.6996718780158275</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.132808974170999</v>
+        <v>-0.762863210734622</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.059748381406834</v>
+        <v>-0.7053077121153564</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.255107997664915</v>
+        <v>-0.9888035674039699</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.240384861303632</v>
+        <v>-0.953502415458928</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.36584583861552</v>
+        <v>-1.185085854192835</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.01233</t>
+          <t>X &lt; 0.01226</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2981</v>
+        <v>3009</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.5782638910617948</v>
+        <v>-0.6793364268858326</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4624703986282697</v>
+        <v>-0.5103878684502234</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.3170406956562175</v>
+        <v>-0.2568745686540481</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.0452907489992711</v>
+        <v>0.1297776901576952</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.5623874528027812</v>
+        <v>-0.3924607921508922</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.6568817535343499</v>
+        <v>-0.4492146108171156</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.509678156066073</v>
+        <v>-0.3635984340654872</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7022914387255454</v>
+        <v>-0.483984790554139</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.541771115970846</v>
+        <v>-0.2709678383663103</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.6947394387193668</v>
+        <v>-0.3842652299647256</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.8357224583975409</v>
+        <v>-0.4915924491000752</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.8615660055846277</v>
+        <v>-0.4503144195261655</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.795824284457737</v>
+        <v>-0.3359706565782616</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.7967797782787329</v>
+        <v>-0.2852013957522317</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.6995353966566782</v>
+        <v>-0.1700135849462612</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.6874955645447471</v>
+        <v>-0.1734936192827519</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.6009367305030864</v>
+        <v>-0.1444836655592425</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.652545871761113</v>
+        <v>-0.2441451793587248</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.7517730745813438</v>
+        <v>-0.2290185003857133</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.7462536330036045</v>
+        <v>-0.3134353775858543</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.6994702218856546</v>
+        <v>-0.2496506430861984</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.7890108552472626</v>
+        <v>-0.4577035304899866</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.9641890271066771</v>
+        <v>-0.5795175501949927</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.9867889938457566</v>
+        <v>-0.7221690490527024</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.01414</t>
+          <t>X &lt; 0.01407</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3075</v>
+        <v>3100</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.6389103800555915</v>
+        <v>-0.6694325066017726</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.8274159686109712</v>
+        <v>-0.7699080018363063</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.8270796533192311</v>
+        <v>-0.6262665349640031</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6177116813863677</v>
+        <v>-0.3335733092443505</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.064843819965034</v>
+        <v>-0.7520751791555469</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.021622365961797</v>
+        <v>-0.706022887361506</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.9024799117859246</v>
+        <v>-0.6471170477089672</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.097823388231397</v>
+        <v>-0.8053508053508125</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.8763272231428658</v>
+        <v>-0.5306407865424987</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.080642132915095</v>
+        <v>-0.6968804056646007</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.241499470106625</v>
+        <v>-0.8250236522409011</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.177993787459002</v>
+        <v>-0.696829472442559</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.116164374774186</v>
+        <v>-0.5874947857696142</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.12393086958614</v>
+        <v>-0.5592047983109012</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-1.017391284636069</v>
+        <v>-0.4356872498060156</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.9552629768328771</v>
+        <v>-0.3900132664359219</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.8755154694259062</v>
+        <v>-0.3972130465141319</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.8639238140658918</v>
+        <v>-0.4656433972445271</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.9860699230777925</v>
+        <v>-0.5089961878235414</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.9101346381157782</v>
+        <v>-0.5199978832737457</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.8814021891287567</v>
+        <v>-0.4751317175581207</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.9705835871324453</v>
+        <v>-0.6280148289556564</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-1.164589522842249</v>
+        <v>-0.7523800176661055</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-1.221402249069214</v>
+        <v>-0.8956593308953487</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.01595</t>
+          <t>X &lt; 0.01587</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3154</v>
+        <v>3177</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.508961686928977</v>
+        <v>-0.6143461142678177</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.6066062795399674</v>
+        <v>-0.6243731628119633</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7364776064820688</v>
+        <v>-0.6715573429232222</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.6760613784911769</v>
+        <v>-0.525911996175715</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.9313442759985051</v>
+        <v>-0.7528311529359684</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.9160265630484119</v>
+        <v>-0.7668014500584306</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.8190508083693331</v>
+        <v>-0.7288155448300415</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.016433130364604</v>
+        <v>-0.8592788253805281</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.9256215091110036</v>
+        <v>-0.6823719006167082</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.9863028187635479</v>
+        <v>-0.7384598418021397</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.136281475600455</v>
+        <v>-0.8568048084739672</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.207625108747848</v>
+        <v>-0.8642499497407599</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.238574197865582</v>
+        <v>-0.7981730397064908</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.25170544867381</v>
+        <v>-0.7766450113731267</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-1.227536310229901</v>
+        <v>-0.7355289530066003</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-1.152176413087233</v>
+        <v>-0.6773695882749919</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.9829244515020363</v>
+        <v>-0.5925707547169807</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.8476953168247334</v>
+        <v>-0.5053290737150675</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.8980715017460312</v>
+        <v>-0.4795460918523133</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.7876682212498807</v>
+        <v>-0.4850854329568435</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.7098412345126022</v>
+        <v>-0.3607060349665048</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.7986344638072964</v>
+        <v>-0.5116706464994323</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-1.012551042835497</v>
+        <v>-0.6585492653295688</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-1.069791956809027</v>
+        <v>-0.7707799051843409</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.01776</t>
+          <t>X &lt; 0.01767</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3199</v>
+        <v>3224</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.5061481686771572</v>
+        <v>-0.5179353700859082</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.5450123004809413</v>
+        <v>-0.469607969495236</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.66209016578172</v>
+        <v>-0.5033882586646712</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.6745932523897196</v>
+        <v>-0.4301927313662972</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.8999262968052761</v>
+        <v>-0.6268863976914787</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.8511129048776169</v>
+        <v>-0.6074228684764122</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.7040863685062035</v>
+        <v>-0.5505732692279537</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.8403558899055952</v>
+        <v>-0.6525865789707552</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.7812939645231154</v>
+        <v>-0.5072685386321538</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.9141527466134818</v>
+        <v>-0.6359665645212829</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.9959016794382052</v>
+        <v>-0.6866769329276892</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.038965300087128</v>
+        <v>-0.667017491458374</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.054020596117489</v>
+        <v>-0.6180745070230813</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.101172753610669</v>
+        <v>-0.6314081829619056</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-1.024183642263409</v>
+        <v>-0.5388492087886902</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.9414774498965315</v>
+        <v>-0.4733617378463251</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.8076066207106223</v>
+        <v>-0.4222994783596761</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.6756935000432023</v>
+        <v>-0.3382638438249685</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.6910653022304771</v>
+        <v>-0.2787442878908379</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.6107441572242536</v>
+        <v>-0.2810775825281766</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.5728109455955348</v>
+        <v>-0.1977628648199712</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.6301391148015867</v>
+        <v>-0.3165744567061779</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.774635036496349</v>
+        <v>-0.3956858779912338</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.8945826382660513</v>
+        <v>-0.5705972961558956</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.01957</t>
+          <t>X &lt; 0.01948</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3247</v>
+        <v>3272</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.3686758596093327</v>
+        <v>-0.4261779594879158</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.4730237282394114</v>
+        <v>-0.4430347803594756</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.6400811493072638</v>
+        <v>-0.5558531600778238</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6934779107728062</v>
+        <v>-0.523030960071182</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.8898216230416125</v>
+        <v>-0.6600464521021863</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.808346228420568</v>
+        <v>-0.638541852939511</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.6441836760859516</v>
+        <v>-0.533497239358752</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.8438161486433486</v>
+        <v>-0.699473185762038</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.7850138946113248</v>
+        <v>-0.5239506205861701</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.8352987579158793</v>
+        <v>-0.6016477324750156</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.8504349098853794</v>
+        <v>-0.5865274687986144</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.8355566621098731</v>
+        <v>-0.5102529202325741</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.8975688999332547</v>
+        <v>-0.509180291433907</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.9165331639089587</v>
+        <v>-0.4954691641595375</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.9424622700183392</v>
+        <v>-0.4880374747791336</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.8829074151654766</v>
+        <v>-0.445817425425119</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.7837001546154454</v>
+        <v>-0.4275604325699689</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.655273132044961</v>
+        <v>-0.3467040797163037</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.6672251761887651</v>
+        <v>-0.2849136082957315</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.5853238945955823</v>
+        <v>-0.2840676212520137</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.5559560952616138</v>
+        <v>-0.2102907485869423</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.551995252210169</v>
+        <v>-0.2673788745376271</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.6902754305850181</v>
+        <v>-0.3417420528965565</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.747949581065491</v>
+        <v>-0.4553249196641787</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.02138</t>
+          <t>X &lt; 0.02128</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3281</v>
+        <v>3305</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.341815636434383</v>
+        <v>-0.3696943972835243</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4788028400288269</v>
+        <v>-0.3890149115882409</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.5075254562700664</v>
+        <v>-0.4239077740418864</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.5676754413279141</v>
+        <v>-0.4279236634305903</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.7351147255300603</v>
+        <v>-0.5664123346346912</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.7131296631891928</v>
+        <v>-0.6036519889769707</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.5889102780669546</v>
+        <v>-0.508360213198344</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.7893363240719182</v>
+        <v>-0.7059747566076808</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.6700165435312115</v>
+        <v>-0.5008229701983211</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.7277230912915655</v>
+        <v>-0.5561550730852147</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.7398415648557517</v>
+        <v>-0.5382288897428111</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.7279614181420513</v>
+        <v>-0.4657728491822866</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.7705239290344394</v>
+        <v>-0.446629061552926</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.7611517760709461</v>
+        <v>-0.4055530416347253</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.8543574478709672</v>
+        <v>-0.4659966716270247</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.8500557413600873</v>
+        <v>-0.4608539790101318</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.783662768474926</v>
+        <v>-0.456378437594438</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.7184943602370311</v>
+        <v>-0.4203815860160915</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.6063796194678304</v>
+        <v>-0.2361491049404592</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.5842564323886634</v>
+        <v>-0.2936303745126736</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.4999081237446958</v>
+        <v>-0.1657907162803482</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.5272166633859499</v>
+        <v>-0.2532846345007087</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.6307441163257153</v>
+        <v>-0.2942213103974254</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.7190668020634163</v>
+        <v>-0.4385318114965884</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.02319</t>
+          <t>X &lt; 0.02309</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3310</v>
+        <v>3333</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2955125799786202</v>
+        <v>-0.2947125445587488</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.3741833355512867</v>
+        <v>-0.2862980943658755</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.4451650262585929</v>
+        <v>-0.3324345828199355</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.5109813646399033</v>
+        <v>-0.3418630884928007</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.679870180348594</v>
+        <v>-0.511426668098089</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.6263828051669478</v>
+        <v>-0.4871699462132497</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.570063067517907</v>
+        <v>-0.4597841720422693</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.7110293809170827</v>
+        <v>-0.598658168081883</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.6825904540356333</v>
+        <v>-0.5136636673923505</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.7164563395307866</v>
+        <v>-0.5459826665623382</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.695980641530781</v>
+        <v>-0.4958108926115514</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.686624394886735</v>
+        <v>-0.456472269046202</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.6482763517591579</v>
+        <v>-0.3880299803634131</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.671000835023257</v>
+        <v>-0.3795324867511383</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.7389859705793924</v>
+        <v>-0.4158130445572539</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.7897693024275299</v>
+        <v>-0.4653572167295437</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.8155526053177908</v>
+        <v>-0.5217689620758534</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.721723809289351</v>
+        <v>-0.4574105352304798</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.6388681052877345</v>
+        <v>-0.2852520657530064</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.5549632442260801</v>
+        <v>-0.2628299140276695</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.5062776722659521</v>
+        <v>-0.1532493587980142</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.534013130620913</v>
+        <v>-0.240635984528744</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.6040294792628913</v>
+        <v>-0.2491849456195609</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.6318117005957546</v>
+        <v>-0.3336257081782392</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.025</t>
+          <t>X &lt; 0.02489</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3336</v>
+        <v>3360</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.2023237433813634</v>
+        <v>-0.1876163822637196</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.3127293316745678</v>
+        <v>-0.1812006247251787</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.424068936386206</v>
+        <v>-0.2665343796959903</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.4055004367513462</v>
+        <v>-0.1918428822657461</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.5160387195688116</v>
+        <v>-0.3030199075434652</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.4912829244275301</v>
+        <v>-0.3072443334882351</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.5308176094087571</v>
+        <v>-0.3752173702796924</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.6430038297163705</v>
+        <v>-0.4857734419345832</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.5846015246845013</v>
+        <v>-0.3707723890171906</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.5644725760377867</v>
+        <v>-0.3498838855538011</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.571842453937542</v>
+        <v>-0.3275236128545203</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.5646865085822554</v>
+        <v>-0.2906646951987923</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.595079823379173</v>
+        <v>-0.290980704170039</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.5894432838382428</v>
+        <v>-0.254837721747684</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.6320958497864453</v>
+        <v>-0.2665750615321727</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.7077352472089231</v>
+        <v>-0.3408691923921765</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.7642482676077407</v>
+        <v>-0.4570246757746759</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.6719497237212408</v>
+        <v>-0.394229173491965</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.6179749829984118</v>
+        <v>-0.2514301742020564</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.5931427693038671</v>
+        <v>-0.2869086592747152</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.489174239800505</v>
+        <v>-0.1233000800408206</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.4873212528729525</v>
+        <v>-0.1808354267469596</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.5546395315517927</v>
+        <v>-0.1873407241633558</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.6127574575853316</v>
+        <v>-0.3021493462563285</v>
       </c>
     </row>
   </sheetData>
